--- a/docs/evaluation_results_III.xlsx
+++ b/docs/evaluation_results_III.xlsx
@@ -554,7 +554,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>9.67</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -597,11 +597,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>The candidate brings 7 years of direct experience as a Digital Delivery Manager within the charity sector, perfectly matching the required skillset and domain background.</t>
+          <t>The candidate has 7 years of direct experience as a Digital Delivery Manager in the charity sector, making them an ideal match for the role.</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -611,11 +611,11 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>[10/10] Significant experience delivering complex projects: 7 Jahre Berufserfahrung als Digital Delivery Manager / Produ
-[9/10] Experience working closely with Product Managers a: Führte 4 agile Squads (18 Personen) bei UNICEF UK, coachter 
-[9/10] Strong stakeholder management, planning, and organ: Explizite Skills in Stakeholder Management, Product Roadmapp
-[9/10] Ability to manage competing priorities, build coll: Erfahrung in der Steuerung von 3 konkurrierenden Workstreams
-[10/10] Experience with agile delivery methodologies, cont: Ausgewiesener Experte mit CSM, SAFe 5 Agilist, Agile Deliver</t>
+          <t>[10/10] Significant experience delivering complex projects: 7 Jahre Berufserfahrung als Digital Delivery Manager/Product
+[10/10] Experience working closely with Product Managers a: Führung von 4 multidisziplinären agilen Squads (18 Personen)
+[10/10] Strong stakeholder management, planning, and organ: Nachgewiesene Skills in Stakeholder Management, Risk Managem
+[9/10] Ability to manage competing priorities, build coll: Steuerung von 3 zeitgleichen Product Workstreams bei NSPCC; 
+[10/10] Experience with agile delivery methodologies, cont: Zertifiziert als CSM und SAFe 5 Agilist; fundierte Erfahrung</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -625,9 +625,9 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>**Strengths**: Proven track record directly at UNICEF UK leading the digital fundraising platform overhaul (increasing donations by 34%) and managing 4 agile squads (18 people). Brings 7 years of digital delivery experience across charity and public sectors (NSPCC, Cabinet Office) with strong expertise in Scrum, Kanban, and handling competing workstreams.
-**Gaps**: The profile lacks explicit mention of managing User Acceptance Testing (UAT) sign-off processes and specific coordination with external agency partners.
-**Recommendation**: The candidate fully satisfies all essential requirements and brings direct domain experience within UNICEF UK. Highly recommended for an immediate interview.</t>
+          <t>**Strengths**: Directly relevant experience currently leading UNICEF UK's digital fundraising platform overhaul across 4 agile squads (18 people), driving a 34% increase in donations. Possesses 7 years of charity and public sector expertise (NSPCC, GDS), demonstrating strong mastery of Scrum, Kanban, and cross-functional delivery.
+**Gaps**: CV lacks explicit details on coordinating formal UAT readiness/sign-off processes. Motivation for transitioning between internal roles at UNICEF UK should be explored during interview.
+**Recommendation**: An outstanding candidate who fully satisfies all essential requirements with existing UNICEF UK domain knowledge and a proven track record. Highly recommended for immediate interview.</t>
         </is>
       </c>
       <c r="S2" t="inlineStr"/>
@@ -638,7 +638,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.7000000000000001</v>
+        <v>1.05</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -652,24 +652,24 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CAND-007</t>
+          <t>SYNTH-001</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Freelance Senior Visual Designer</t>
+          <t>Senior Creative Producer (Film &amp; Photography)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Senior Visual Designer with over 10 years of experience delivering branding, digital campaigns, web design, and motion graphics across global agencies and brands. Specialises in creative strategy, user interface design, and digital product systems with extensive experience leading design projects across the US, LATAM, and UK.</t>
+          <t>Award-winning Senior Creative Producer with 9 years specialising in documentary film, charity campaigns, and editorial photography for international NGOs. Proven track record managing end-to-end productions from concept to broadcast, leading cross-functional creative teams and delivering compelling visual storytelling.</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -677,11 +677,11 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>The candidate's experience is focused on hands-on visual design and creative execution rather than digital project delivery management and Agile team leadership.</t>
+          <t>While the candidate has relevant charity sector experience, film and creative production management lacks the required background in digital software and tech product delivery.</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
@@ -724,25 +724,23 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SYNTH-001</t>
+          <t>CAND-001</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Senior Creative Producer (Film &amp; Photography)</t>
+          <t>Lead Designer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Award-winning Senior Creative Producer with 9 years specialising in documentary film, charity campaigns, and editorial photography for international NGOs. Proven track record managing end-to-end productions from concept to broadcast, leading cross-functional creative teams and delivering compelling visual storytelling.</t>
+          <t>Lead Designer with over 20 years of multi-sector experience building brand identities and leading creative teams across financial services, technology, NGOs, and specialist sectors. Specialist in end-to-end campaign creative direction, design systems, and multi-channel delivery aligned to commercial objectives.</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9</v>
-      </c>
-      <c r="I4" t="b">
-        <v>1</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
@@ -753,7 +751,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>While the candidate has valuable charity sector experience, film and photography production lacks the required background in digital technology, software products, and agile delivery methodologies.</t>
+          <t>While the candidate has extensive experience leading creative teams and NGO exposure, a design background lacks the specific agile product delivery and technical project management required for a Delivery Manager role.</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -796,21 +794,21 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>SYNTH-003</t>
+          <t>CAND-003</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Head of Finance Business Partnering</t>
+          <t>Senior Designer (Brand Design &amp; UI/UX)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>CIMA-qualified Head of Finance Business Partnering with 12 years in charity and public sector finance. Expert in management accounting, financial planning &amp; analysis, and strategic finance partnering with senior leadership teams. Experienced in leading finance transformation projects and implementing ERP systems.</t>
+          <t>Senior Brand &amp; Visual Designer with 7+ years of experience delivering brand identity, packaging, digital campaigns, and UI/UX design across consumer, B2B, and SaaS sectors. Specialist in multi-brand asset management, print production, AI workflow integration, and high-impact visual communications.</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I5" t="b">
         <v>1</v>
@@ -825,7 +823,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>The candidate has a background strictly in finance and accounting, lacking the required experience in digital, technology, or online product delivery.</t>
+          <t>The candidate has a purely creative visual and UI/UX design background without the required hands-on experience in digital delivery management, agile project governance, or operational team leadership.</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -868,24 +866,24 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SYNTH-005</t>
+          <t>CAND-007</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Deputy General Counsel</t>
+          <t>Freelance Senior Visual Designer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Qualified solicitor and Deputy General Counsel with 14 years of in-house and private practice experience in the charity, media, and technology sectors. Expert in commercial contracts, employment law, GDPR/data protection, charity governance, and IP/brand protection. Experienced advising Boards and Trustees.</t>
+          <t>Senior Visual Designer with over 10 years of experience delivering branding, digital campaigns, web design, and motion graphics across global agencies and brands. Specialises in creative strategy, user interface design, and digital product systems with extensive experience leading design projects across the US, LATAM, and UK.</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -897,7 +895,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Although the candidate has relevant sector experience in charity and technology, their background is strictly legal and governance-focused, lacking the hands-on digital product delivery and Agile project management experience required for this role.</t>
+          <t>While the candidate has strong digital design experience, they lack the hands-on agile project delivery, governance, and delivery management expertise required for this role.</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -926,7 +924,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.35</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -940,21 +938,21 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CAND-004</t>
+          <t>CAND-008</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Work Placement Officer</t>
+          <t>Lead Digital Designer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Education administration professional and law graduate with over a year of experience in compliance, admissions support, and stakeholder coordination. Possesses expertise in contract review, data accuracy, and business engagement with plans to pursue SQE qualifications.</t>
+          <t>Lead Digital Designer with over 18 years of experience directing and executing digital design, motion creative, UI, and branding for global integrated campaigns. Demonstrates strong craft leadership and expertise in managing design teams, brand guardianship, and integrating generative AI tools into creative workflows across consumer, tech, and financial sectors.</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
@@ -963,11 +961,11 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>The candidate lacks the required significant experience in digital product delivery, holding only one year of junior background in education administration and legal compliance.</t>
+          <t>The candidate's background is strictly focused on creative design and brand leadership rather than digital product delivery management and project execution.</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -996,7 +994,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.35</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1010,21 +1008,21 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CAND-006</t>
+          <t>SYNTH-003</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lead Visual Artist</t>
+          <t>Head of Finance Business Partnering</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Senior Brand and Visual Designer with over 6 years of experience leading brand creation and visual systems across physical and digital touchpoints. Specialist in translating strategic positioning into cohesive visual identities, campaign design, and design systems within the tech and wearables sector.</t>
+          <t>CIMA-qualified Head of Finance Business Partnering with 12 years in charity and public sector finance. Expert in management accounting, financial planning &amp; analysis, and strategic finance partnering with senior leadership teams. Experienced in leading finance transformation projects and implementing ERP systems.</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I8" t="b">
         <v>1</v>
@@ -1035,11 +1033,11 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>The candidate's experience is strictly focused on visual design and branding, lacking the necessary digital project management and team delivery capabilities required for this role.</t>
+          <t>The candidate's background is exclusively in strategic finance and FP&amp;A, lacking the essential experience required in digital product delivery and leading multidisciplinary tech teams.</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -1068,7 +1066,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.35</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1082,21 +1080,21 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>SYNTH-004</t>
+          <t>SYNTH-005</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Head of Internal Audit &amp; Risk</t>
+          <t>Deputy General Counsel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>CIIA-qualified Head of Internal Audit and Risk with 11 years in the charity and financial services sectors. Specialist in enterprise risk management (ERM), internal audit delivery, and governance frameworks. Experienced in audit committee reporting, fraud prevention, and regulatory compliance.</t>
+          <t>Qualified solicitor and Deputy General Counsel with 14 years of in-house and private practice experience in the charity, media, and technology sectors. Expert in commercial contracts, employment law, GDPR/data protection, charity governance, and IP/brand protection. Experienced advising Boards and Trustees.</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I9" t="b">
         <v>1</v>
@@ -1107,11 +1105,11 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>The candidate's background is strictly focused on internal audit, risk, and compliance, lacking any required experience in digital product delivery, technology environments, or agile methodologies.</t>
+          <t>While the candidate possesses relevant sector experience in charity and tech, their background is strictly legal and lacks required hands-on experience in digital project delivery and agile product management.</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -1140,7 +1138,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1154,34 +1152,36 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CAND-001</t>
+          <t>SYNTH-006</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lead Designer</t>
+          <t>Senior Procurement Manager</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lead Designer with over 20 years of multi-sector experience building brand identities and leading creative teams across financial services, technology, NGOs, and specialist sectors. Specialist in end-to-end campaign creative direction, design systems, and multi-channel delivery aligned to commercial objectives.</t>
+          <t>CIPS-qualified Senior Procurement Manager with 8 years leading procurement functions in charity and public sector organisations. Expert in strategic sourcing, supplier relationship management, and contract management. Delivered £4.5m of savings over 5 years through category management and competitive tendering. Experienced in EU procurement regulations and PCR 2015.</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>23</v>
-      </c>
-      <c r="I10" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="I10" t="b">
+        <v>1</v>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>API timeout</t>
+          <t>The candidate's experience is strictly focused on procurement and contract management, lacking the required digital product delivery and agile environment experience.</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
@@ -1210,7 +1210,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1224,24 +1224,36 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CAND-002</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
+          <t>CAND-006</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Lead Visual Artist</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Senior Brand and Visual Designer with over 6 years of experience leading brand creation and visual systems across physical and digital touchpoints. Specialist in translating strategic positioning into cohesive visual identities, campaign design, and design systems within the tech and wearables sector.</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>6</v>
+      </c>
+      <c r="I11" t="b">
+        <v>1</v>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>No candidate profile or work experience details are provided to assess suitability for the role.</t>
+          <t>The candidate's profile is strictly focused on creative visual design and brand systems, lacking the necessary digital project management and agile delivery experience required for a Delivery Manager role.</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
@@ -1270,7 +1282,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1284,21 +1296,21 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CAND-003</t>
+          <t>SYNTH-004</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Senior Designer (Brand Design &amp; UI/UX)</t>
+          <t>Head of Internal Audit &amp; Risk</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Senior Brand &amp; Visual Designer with 7+ years of experience delivering brand identity, packaging, digital campaigns, and UI/UX design across consumer, B2B, and SaaS sectors. Specialist in multi-brand asset management, print production, AI workflow integration, and high-impact visual communications.</t>
+          <t>CIIA-qualified Head of Internal Audit and Risk with 11 years in the charity and financial services sectors. Specialist in enterprise risk management (ERM), internal audit delivery, and governance frameworks. Experienced in audit committee reporting, fraud prevention, and regulatory compliance.</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I12" t="b">
         <v>1</v>
@@ -1309,11 +1321,11 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>API timeout</t>
+          <t>The candidate's profile is strictly focused on internal audit, governance, and risk compliance, lacking any demonstrated experience in digital product delivery or working with tech product teams.</t>
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
@@ -1356,7 +1368,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CAND-005</t>
+          <t>CAND-002</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -1373,7 +1385,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>API timeout</t>
+          <t>No profile or work history is provided to assess suitability for the role.</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
@@ -1416,21 +1428,21 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CAND-008</t>
+          <t>CAND-004</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lead Digital Designer</t>
+          <t>Work Placement Officer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lead Digital Designer with over 18 years of experience directing and executing digital design, motion creative, UI, and branding for global integrated campaigns. Demonstrates strong craft leadership and expertise in managing design teams, brand guardianship, and integrating generative AI tools into creative workflows across consumer, tech, and financial sectors.</t>
+          <t>Education administration professional and law graduate with over a year of experience in compliance, admissions support, and stakeholder coordination. Possesses expertise in contract review, data accuracy, and business engagement with plans to pursue SQE qualifications.</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
@@ -1443,7 +1455,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>API timeout</t>
+          <t>The candidate lacks the required digital and product delivery experience, holding only one year of junior administrative background in the education and legal sectors.</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
@@ -1486,7 +1498,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CAND-009</t>
+          <t>CAND-005</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
@@ -1503,7 +1515,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>No candidate details or work experience were provided to assess suitability for the Delivery Manager role.</t>
+          <t>The candidate profile contains no information or career history to evaluate their suitability for the Delivery Manager role.</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
@@ -1546,25 +1558,13 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>SYNTH-006</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Senior Procurement Manager</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>CIPS-qualified Senior Procurement Manager with 8 years leading procurement functions in charity and public sector organisations. Expert in strategic sourcing, supplier relationship management, and contract management. Delivered £4.5m of savings over 5 years through category management and competitive tendering. Experienced in EU procurement regulations and PCR 2015.</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>8</v>
-      </c>
-      <c r="I16" t="b">
-        <v>1</v>
-      </c>
+          <t>CAND-009</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>API timeout</t>
+          <t>There is no profile or experience information provided to evaluate the candidate's suitability for the Delivery Manager role.</t>
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
@@ -1888,7 +1888,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>7.681</v>
+        <v>7.94</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1931,11 +1931,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>With 14 years of legal experience, direct charity governance background, and current Deputy General Counsel standing, this candidate represents a highly logical and strong progression into the General Counsel role.</t>
+          <t>The candidate has 14 years of legal experience, currently serves as Deputy General Counsel, and possesses direct expertise in charity governance and board advisory, making this an ideal step-up for the General Counsel role at UNICEF UK.</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>6.33</v>
+        <v>6.8</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -1944,16 +1944,16 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Kein Nachweis über einen durchgeführten oder erfolgreichen Criminal Records Check (DBS Check) im Profil., Fehlende finale Gesamtverantwortung als General Counsel (bisher 'Second-in-command' als Deputy General Counsel).</t>
+          <t>Kein Nachweis über eine erfolgte Überprüfung des Strafregisters (Criminal Records Check / DBS Check) im Profil vorhanden., Bisher noch keine Erstverantwortung als Gesamtleiter / General Counsel (bislang Deputy General Counsel).</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>[7/10] Significant senior-level experience leading legal : 14 Jahre Berufserfahrung, aktuell Deputy General Counsel bei
-[8/10] Track record of supporting executive and board-lev: Skills in Board Secretariat und Board-Level Communication so
-[9/10] Strong commercial acumen combined with sound judge: Erfahrung bei Clifford Chance (M&amp;A/JVs für FTSE 100), Verhan
-[7/10] Ability to balance legal risk with organisational : Nachgewiesene Skills in Strategic Legal Advice, Risk Managem
-[7/10] Influential and collaborative leadership skills, a: Leitung eines Teams aus 4 Anwälten und 2 Paralegals bei WWF-</t>
+          <t xml:space="preserve">[8/10] Significant senior-level experience leading legal : 14 Berufsjahre; aktuell Deputy General Counsel bei WWF-UK (S
+[8/10] Track record of supporting executive and board-lev: Nachgewiesene Skills in 'Board-Level Communication', 'Strate
+[9/10] Strong commercial acumen combined with sound judge: Umfangreiche kommerzielle Erfahrung: Verhandlung von £50m+ V
+[8/10] Ability to balance legal risk with organisational : Fähigkeiten in 'Strategic Legal Advice' und 'Risk Management
+[8/10] Influential and collaborative leadership skills, a: Führungserfahrung als Deputy General Counsel bei WWF-UK mit </t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -1963,9 +1963,9 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>**Strengths**: Directly relevant charity governance and team leadership experience as Deputy General Counsel at WWF-UK (managing 6 staff and advising the Board), backed by top-tier commercial expertise from Clifford Chance and Channel 4 (£50m+ negotiations).
-**Gaps**: Represents a step-up from 'second-in-command' to ultimate General Counsel accountability; no explicit record of a criminal records check (DBS) provided in the profile.
-**Recommendation**: An outstanding candidate combining elite commercial training with directly transferable charity leadership. Recommend interviewing to assess readiness for top-level GC ownership and verifying DBS status.</t>
+          <t>**Strengths**: 14 years' legal experience, including direct sector leadership as Deputy General Counsel at WWF-UK managing a 6-person team and advising Trustees. Exceptional commercial acumen backed by Magic Circle training (Clifford Chance) and managing £50m+ contracts at Channel 4.
+**Gaps**: Seeking a step-up to full General Counsel level (currently second-in-command). No current evidence of a completed criminal records check in profile.
+**Recommendation**: Highly qualified candidate offering an ideal blend of top-tier commercial rigor and proven charity governance experience. Highly recommended for interview, subject to verifying criminal records check status.</t>
         </is>
       </c>
       <c r="S2" t="inlineStr"/>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>While the candidate has relevant charity sector and governance experience, they lack the required professional legal qualifications and practicing background essential for a General Counsel role.</t>
+          <t>While the candidate has relevant charity sector and governance experience, they lack the legal qualifications and formal legal practice background required for a General Counsel position.</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
@@ -2091,7 +2091,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>The candidate has a finance background (CIMA), whereas a General Counsel position strictly requires a qualified legal professional with extensive legal and governance experience.</t>
+          <t>The candidate has a background in finance and accounting rather than the required legal qualifications and legal leadership experience needed for a General Counsel role.</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -2120,7 +2120,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -2134,34 +2134,36 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CAND-001</t>
+          <t>SYNTH-006</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lead Designer</t>
+          <t>Senior Procurement Manager</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lead Designer with over 20 years of multi-sector experience building brand identities and leading creative teams across financial services, technology, NGOs, and specialist sectors. Specialist in end-to-end campaign creative direction, design systems, and multi-channel delivery aligned to commercial objectives.</t>
+          <t>CIPS-qualified Senior Procurement Manager with 8 years leading procurement functions in charity and public sector organisations. Expert in strategic sourcing, supplier relationship management, and contract management. Delivered £4.5m of savings over 5 years through category management and competitive tendering. Experienced in EU procurement regulations and PCR 2015.</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>23</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="I5" t="b">
+        <v>1</v>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>The candidate has a creative background in design and brand identity, completely lacking the requisite legal qualifications and governance leadership experience required for a General Counsel position.</t>
+          <t>The candidate is a procurement specialist and lacks the essential legal qualifications and senior legal leadership experience required for a General Counsel role.</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -2204,12 +2206,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CAND-002</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+          <t>CAND-001</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Lead Designer</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lead Designer with over 20 years of multi-sector experience building brand identities and leading creative teams across financial services, technology, NGOs, and specialist sectors. Specialist in end-to-end campaign creative direction, design systems, and multi-channel delivery aligned to commercial objectives.</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>23</v>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
@@ -2221,7 +2233,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>No candidate profile, experience, or career history is provided to evaluate suitability for the General Counsel role.</t>
+          <t>The candidate's background is exclusively in creative design and brand direction, lacking the legal qualifications and governance experience required for a General Counsel role.</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -2264,25 +2276,13 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CAND-003</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Senior Designer (Brand Design &amp; UI/UX)</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Senior Brand &amp; Visual Designer with 7+ years of experience delivering brand identity, packaging, digital campaigns, and UI/UX design across consumer, B2B, and SaaS sectors. Specialist in multi-brand asset management, print production, AI workflow integration, and high-impact visual communications.</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>7</v>
-      </c>
-      <c r="I7" t="b">
-        <v>1</v>
-      </c>
+          <t>CAND-002</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
@@ -2293,7 +2293,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>The candidate's background in visual and brand design is completely unrelated to the senior legal, compliance, and governance requirements of a General Counsel role.</t>
+          <t>No profile or professional experience details are provided to evaluate the candidate's suitability for a senior legal leadership role.</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -2336,23 +2336,25 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CAND-004</t>
+          <t>CAND-003</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Work Placement Officer</t>
+          <t>Senior Designer (Brand Design &amp; UI/UX)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Education administration professional and law graduate with over a year of experience in compliance, admissions support, and stakeholder coordination. Possesses expertise in contract review, data accuracy, and business engagement with plans to pursue SQE qualifications.</t>
+          <t>Senior Brand &amp; Visual Designer with 7+ years of experience delivering brand identity, packaging, digital campaigns, and UI/UX design across consumer, B2B, and SaaS sectors. Specialist in multi-brand asset management, print production, AI workflow integration, and high-impact visual communications.</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="I8" t="b">
+        <v>1</v>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
@@ -2363,7 +2365,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>API timeout</t>
+          <t>The candidate's background is entirely in visual design and UI/UX, lacking the required legal qualifications and senior governance experience necessary for a General Counsel role.</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -2406,12 +2408,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CAND-005</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+          <t>CAND-004</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Work Placement Officer</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Education administration professional and law graduate with over a year of experience in compliance, admissions support, and stakeholder coordination. Possesses expertise in contract review, data accuracy, and business engagement with plans to pursue SQE qualifications.</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
@@ -2423,7 +2435,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>No candidate profile or experience details are provided to assess suitability for the role.</t>
+          <t>The candidate is an entry-level professional who is not yet a qualified lawyer, making them completely unsuitable for a senior executive General Counsel position.</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -2466,25 +2478,13 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CAND-006</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Lead Visual Artist</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Senior Brand and Visual Designer with over 6 years of experience leading brand creation and visual systems across physical and digital touchpoints. Specialist in translating strategic positioning into cohesive visual identities, campaign design, and design systems within the tech and wearables sector.</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>6</v>
-      </c>
-      <c r="I10" t="b">
-        <v>1</v>
-      </c>
+          <t>CAND-005</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>API timeout</t>
+          <t>There is no information provided about the candidate's background, experience, or qualifications to assess suitability for the General Counsel role.</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
@@ -2538,24 +2538,24 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CAND-007</t>
+          <t>CAND-006</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Freelance Senior Visual Designer</t>
+          <t>Lead Visual Artist</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Senior Visual Designer with over 10 years of experience delivering branding, digital campaigns, web design, and motion graphics across global agencies and brands. Specialises in creative strategy, user interface design, and digital product systems with extensive experience leading design projects across the US, LATAM, and UK.</t>
+          <t>Senior Brand and Visual Designer with over 6 years of experience leading brand creation and visual systems across physical and digital touchpoints. Specialist in translating strategic positioning into cohesive visual identities, campaign design, and design systems within the tech and wearables sector.</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>The candidate's background is entirely in visual design and creative strategy, with no qualifications or experience in legal affairs or executive governance required for a General Counsel role.</t>
+          <t>The candidate's background in visual design lacks the required legal qualifications and executive governance experience necessary for a General Counsel role.</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
@@ -2610,23 +2610,25 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CAND-008</t>
+          <t>CAND-007</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lead Digital Designer</t>
+          <t>Freelance Senior Visual Designer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lead Digital Designer with over 18 years of experience directing and executing digital design, motion creative, UI, and branding for global integrated campaigns. Demonstrates strong craft leadership and expertise in managing design teams, brand guardianship, and integrating generative AI tools into creative workflows across consumer, tech, and financial sectors.</t>
+          <t>Senior Visual Designer with over 10 years of experience delivering branding, digital campaigns, web design, and motion graphics across global agencies and brands. Specialises in creative strategy, user interface design, and digital product systems with extensive experience leading design projects across the US, LATAM, and UK.</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>18</v>
-      </c>
-      <c r="I12" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
@@ -2637,7 +2639,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>API timeout</t>
+          <t>The candidate's background is entirely in visual design, lacking the required legal qualifications, governance expertise, and senior legal leadership experience for a General Counsel role.</t>
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
@@ -2680,12 +2682,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CAND-009</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+          <t>CAND-008</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Lead Digital Designer</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lead Digital Designer with over 18 years of experience directing and executing digital design, motion creative, UI, and branding for global integrated campaigns. Demonstrates strong craft leadership and expertise in managing design teams, brand guardianship, and integrating generative AI tools into creative workflows across consumer, tech, and financial sectors.</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>18</v>
+      </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
@@ -2697,7 +2709,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>No candidate profile or career history is available to assess suitability for this senior legal role.</t>
+          <t>The candidate has a background entirely in digital design and creative leadership with no relevant experience in legal or governance functions required for a General Counsel role.</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
@@ -2740,25 +2752,13 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SYNTH-001</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Senior Creative Producer (Film &amp; Photography)</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Award-winning Senior Creative Producer with 9 years specialising in documentary film, charity campaigns, and editorial photography for international NGOs. Proven track record managing end-to-end productions from concept to broadcast, leading cross-functional creative teams and delivering compelling visual storytelling.</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>9</v>
-      </c>
-      <c r="I14" t="b">
-        <v>1</v>
-      </c>
+          <t>CAND-009</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
@@ -2769,7 +2769,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>The candidate's background in creative production lacks the required legal qualifications and senior governance experience necessary for a General Counsel role.</t>
+          <t>No profile or professional background details are provided to evaluate the candidate's suitability for the General Counsel role.</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
@@ -2812,21 +2812,21 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SYNTH-002</t>
+          <t>SYNTH-001</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Digital Delivery Manager</t>
+          <t>Senior Creative Producer (Film &amp; Photography)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Results-driven Digital Delivery Manager with 7 years delivering agile digital products and online platforms for charity and public sector organisations. Experienced in Scrum, Kanban and SAFe frameworks, managing cross-functional teams of 15+ to deliver user-centred services on time and within budget.</t>
+          <t>Award-winning Senior Creative Producer with 9 years specialising in documentary film, charity campaigns, and editorial photography for international NGOs. Proven track record managing end-to-end productions from concept to broadcast, leading cross-functional creative teams and delivering compelling visual storytelling.</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I15" t="b">
         <v>1</v>
@@ -2841,7 +2841,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>API timeout</t>
+          <t>The candidate has a background in creative media production and completely lacks the legal qualifications, legal leadership, and governance experience required for a General Counsel position.</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
@@ -2884,21 +2884,21 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>SYNTH-006</t>
+          <t>SYNTH-002</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Senior Procurement Manager</t>
+          <t>Digital Delivery Manager</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>CIPS-qualified Senior Procurement Manager with 8 years leading procurement functions in charity and public sector organisations. Expert in strategic sourcing, supplier relationship management, and contract management. Delivered £4.5m of savings over 5 years through category management and competitive tendering. Experienced in EU procurement regulations and PCR 2015.</t>
+          <t>Results-driven Digital Delivery Manager with 7 years delivering agile digital products and online platforms for charity and public sector organisations. Experienced in Scrum, Kanban and SAFe frameworks, managing cross-functional teams of 15+ to deliver user-centred services on time and within budget.</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I16" t="b">
         <v>1</v>
@@ -2913,7 +2913,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>API timeout</t>
+          <t>The candidate has a background in digital product management and lacks the required legal qualifications and senior legal leadership experience for a General Counsel role.</t>
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
@@ -3080,7 +3080,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>3.5</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3123,27 +3123,43 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>The candidate holds the exact matching job title, CIIA qualification, and direct charity sector experience required for this role.</t>
+          <t>The candidate has the exact matching job title, a CIIA qualification, and 11 years of directly transferable enterprise risk and audit experience within the charity sector.</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0/6 Anforderungen</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
+          <t>5/6 Anforderungen</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Fehlender Beleg/Nachweis bezüglich eines Criminal Records Checks (z.B. DBS Check in UK)</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[9/10] Experienced risk or audit professional with a stro: 11 Jahre Berufserfahrung; aktuell Head of Internal Audit &amp; R
+[8/10] Excellent analytical and communication skills: CV führt 'Data Analytics for Audit', 'Critical Thinking' und
+[9/10] Ability to challenge and influence senior stakehol: Nachgewiesene Berichterstattung an Audit Committees bei Macm
+[9/10] Strong understanding of risk, assurance, and gover: Umfassende Kenntnisse in ISO 31000, Control Framework Design
+[8/10] Commitment to integrity and continuous improvement: Soft Skills nennen explizit 'Integrity' sowie 'Independence </t>
+        </is>
+      </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Strong Match</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>(failed: )</t>
+          <t>**Strengths**: • CIIA-qualified with 11 years of relevant experience, currently serving as Head of Internal Audit &amp; Risk at Macmillan Cancer Support.
+• Proven track record of board-level stakeholder engagement, regularly presenting to Audit &amp; Risk Committees across the Charity, NHS, and Financial Services sectors.
+• Deep expertise in governance and risk frameworks (ISO 31000), backed by measurable delivery such as achieving a 40% reduction in critical cyber risk at Macmillan.
+**Gaps**: • Missing explicit confirmation/evidence of a successful criminal records check (DBS check).
+**Recommendation**: The candidate brings direct charity-sector head level leadership and technical excellence perfectly aligned with UNICEF UK's core requirements. I strongly recommend progressing to interview, subject to standard DBS verification.</t>
         </is>
       </c>
       <c r="S2" t="inlineStr"/>
@@ -3154,7 +3170,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.7000000000000001</v>
+        <v>1.4</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -3168,21 +3184,21 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>SYNTH-006</t>
+          <t>SYNTH-003</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Senior Procurement Manager</t>
+          <t>Head of Finance Business Partnering</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>CIPS-qualified Senior Procurement Manager with 8 years leading procurement functions in charity and public sector organisations. Expert in strategic sourcing, supplier relationship management, and contract management. Delivered £4.5m of savings over 5 years through category management and competitive tendering. Experienced in EU procurement regulations and PCR 2015.</t>
+          <t>CIMA-qualified Head of Finance Business Partnering with 12 years in charity and public sector finance. Expert in management accounting, financial planning &amp; analysis, and strategic finance partnering with senior leadership teams. Experienced in leading finance transformation projects and implementing ERP systems.</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I3" t="b">
         <v>1</v>
@@ -3193,11 +3209,11 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>The candidate's background is exclusively in procurement and contract management, lacking the required professional qualifications and direct experience in enterprise risk management and internal audit.</t>
+          <t>While the candidate has strong senior charity sector finance experience, they lack the specific track record in internal audit and enterprise risk management required for this role.</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
@@ -3226,7 +3242,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.35</v>
+        <v>1.05</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -3240,21 +3256,21 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SYNTH-002</t>
+          <t>SYNTH-005</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Digital Delivery Manager</t>
+          <t>Deputy General Counsel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Results-driven Digital Delivery Manager with 7 years delivering agile digital products and online platforms for charity and public sector organisations. Experienced in Scrum, Kanban and SAFe frameworks, managing cross-functional teams of 15+ to deliver user-centred services on time and within budget.</t>
+          <t>Qualified solicitor and Deputy General Counsel with 14 years of in-house and private practice experience in the charity, media, and technology sectors. Expert in commercial contracts, employment law, GDPR/data protection, charity governance, and IP/brand protection. Experienced advising Boards and Trustees.</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="I4" t="b">
         <v>1</v>
@@ -3265,11 +3281,11 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>The candidate's background is exclusively in Agile digital product delivery, lacking the essential expertise in enterprise risk management, governance, and internal audit required for this senior leadership position.</t>
+          <t>While the candidate has strong charity governance and Board experience, a legal background as a Deputy General Counsel lacks the dedicated internal audit and enterprise risk management expertise required for this role.</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -3298,7 +3314,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -3312,34 +3328,36 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CAND-001</t>
+          <t>SYNTH-006</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lead Designer</t>
+          <t>Senior Procurement Manager</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lead Designer with over 20 years of multi-sector experience building brand identities and leading creative teams across financial services, technology, NGOs, and specialist sectors. Specialist in end-to-end campaign creative direction, design systems, and multi-channel delivery aligned to commercial objectives.</t>
+          <t>CIPS-qualified Senior Procurement Manager with 8 years leading procurement functions in charity and public sector organisations. Expert in strategic sourcing, supplier relationship management, and contract management. Delivered £4.5m of savings over 5 years through category management and competitive tendering. Experienced in EU procurement regulations and PCR 2015.</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>23</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="I5" t="b">
+        <v>1</v>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>The candidate's background is entirely in creative design and branding, lacking any experience in risk management or internal audit required for this role.</t>
+          <t>While the candidate has relevant charity sector experience, procurement is a completely different functional domain from enterprise risk management and internal audit.</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -3368,7 +3386,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -3382,24 +3400,36 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CAND-002</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+          <t>SYNTH-002</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Digital Delivery Manager</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Results-driven Digital Delivery Manager with 7 years delivering agile digital products and online platforms for charity and public sector organisations. Experienced in Scrum, Kanban and SAFe frameworks, managing cross-functional teams of 15+ to deliver user-centred services on time and within budget.</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>7</v>
+      </c>
+      <c r="I6" t="b">
+        <v>1</v>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>API timeout</t>
+          <t>The candidate's background is entirely in digital product delivery and agile project management, lacking any specialized experience in enterprise risk management or internal audit.</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -3442,25 +3472,23 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CAND-003</t>
+          <t>CAND-001</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Senior Designer (Brand Design &amp; UI/UX)</t>
+          <t>Lead Designer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Senior Brand &amp; Visual Designer with 7+ years of experience delivering brand identity, packaging, digital campaigns, and UI/UX design across consumer, B2B, and SaaS sectors. Specialist in multi-brand asset management, print production, AI workflow integration, and high-impact visual communications.</t>
+          <t>Lead Designer with over 20 years of multi-sector experience building brand identities and leading creative teams across financial services, technology, NGOs, and specialist sectors. Specialist in end-to-end campaign creative direction, design systems, and multi-channel delivery aligned to commercial objectives.</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>7</v>
-      </c>
-      <c r="I7" t="b">
-        <v>1</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
@@ -3471,7 +3499,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>The candidate's background in graphic design and UI/UX has no relevance to enterprise risk management or internal audit.</t>
+          <t>The candidate's background is entirely in creative design and branding, with no relevant experience in enterprise risk management or internal audit.</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -3514,22 +3542,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CAND-004</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Work Placement Officer</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Education administration professional and law graduate with over a year of experience in compliance, admissions support, and stakeholder coordination. Possesses expertise in contract review, data accuracy, and business engagement with plans to pursue SQE qualifications.</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>1</v>
-      </c>
+          <t>CAND-002</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
@@ -3541,7 +3559,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>The candidate has only one year of junior entry-level experience in education administration, making them completely unqualified for a senior Head of Risk and Internal Audit role requiring extensive leadership and enterprise risk management experience.</t>
+          <t>No information regarding the candidate's professional background, experience, or qualifications is available to assess suitability for the role.</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -3584,13 +3602,25 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CAND-005</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+          <t>CAND-003</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Senior Designer (Brand Design &amp; UI/UX)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Senior Brand &amp; Visual Designer with 7+ years of experience delivering brand identity, packaging, digital campaigns, and UI/UX design across consumer, B2B, and SaaS sectors. Specialist in multi-brand asset management, print production, AI workflow integration, and high-impact visual communications.</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>7</v>
+      </c>
+      <c r="I9" t="b">
+        <v>1</v>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
@@ -3601,7 +3631,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>API timeout</t>
+          <t>The candidate's background in creative brand design and UI/UX is completely unrelated to enterprise risk management and internal audit.</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -3644,25 +3674,23 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CAND-006</t>
+          <t>CAND-004</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lead Visual Artist</t>
+          <t>Work Placement Officer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Senior Brand and Visual Designer with over 6 years of experience leading brand creation and visual systems across physical and digital touchpoints. Specialist in translating strategic positioning into cohesive visual identities, campaign design, and design systems within the tech and wearables sector.</t>
+          <t>Education administration professional and law graduate with over a year of experience in compliance, admissions support, and stakeholder coordination. Possesses expertise in contract review, data accuracy, and business engagement with plans to pursue SQE qualifications.</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>6</v>
-      </c>
-      <c r="I10" t="b">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
@@ -3673,7 +3701,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>The candidate has a background entirely focused on visual design and branding with zero experience in risk management, internal audit, or governance.</t>
+          <t>The candidate is a junior education administrator with only one year of experience, lacking the extensive senior leadership and specialised enterprise risk management background required for a Head of Department role.</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
@@ -3716,25 +3744,13 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CAND-007</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Freelance Senior Visual Designer</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Senior Visual Designer with over 10 years of experience delivering branding, digital campaigns, web design, and motion graphics across global agencies and brands. Specialises in creative strategy, user interface design, and digital product systems with extensive experience leading design projects across the US, LATAM, and UK.</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>10</v>
-      </c>
-      <c r="I11" t="b">
-        <v>0</v>
-      </c>
+          <t>CAND-005</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
@@ -3745,7 +3761,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>API timeout</t>
+          <t>The candidate profile contains no background information or relevant experience to assess suitability for this role.</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
@@ -3788,23 +3804,25 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CAND-008</t>
+          <t>CAND-006</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lead Digital Designer</t>
+          <t>Lead Visual Artist</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lead Digital Designer with over 18 years of experience directing and executing digital design, motion creative, UI, and branding for global integrated campaigns. Demonstrates strong craft leadership and expertise in managing design teams, brand guardianship, and integrating generative AI tools into creative workflows across consumer, tech, and financial sectors.</t>
+          <t>Senior Brand and Visual Designer with over 6 years of experience leading brand creation and visual systems across physical and digital touchpoints. Specialist in translating strategic positioning into cohesive visual identities, campaign design, and design systems within the tech and wearables sector.</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>18</v>
-      </c>
-      <c r="I12" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="I12" t="b">
+        <v>1</v>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
@@ -3815,7 +3833,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>API timeout</t>
+          <t>The candidate's experience is exclusively in visual design and branding, with no background or qualifications in enterprise risk management or internal audit.</t>
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
@@ -3858,13 +3876,25 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CAND-009</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
+          <t>CAND-007</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Freelance Senior Visual Designer</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Senior Visual Designer with over 10 years of experience delivering branding, digital campaigns, web design, and motion graphics across global agencies and brands. Specialises in creative strategy, user interface design, and digital product systems with extensive experience leading design projects across the US, LATAM, and UK.</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>10</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
@@ -3875,7 +3905,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>The candidate profile lacks any employment history or qualifications, making it impossible to determine suitability for a senior risk and audit role.</t>
+          <t>The candidate's background in visual design and creative direction bears no relevance to enterprise risk management or internal audit functions.</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
@@ -3918,25 +3948,23 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SYNTH-001</t>
+          <t>CAND-008</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Senior Creative Producer (Film &amp; Photography)</t>
+          <t>Lead Digital Designer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Award-winning Senior Creative Producer with 9 years specialising in documentary film, charity campaigns, and editorial photography for international NGOs. Proven track record managing end-to-end productions from concept to broadcast, leading cross-functional creative teams and delivering compelling visual storytelling.</t>
+          <t>Lead Digital Designer with over 18 years of experience directing and executing digital design, motion creative, UI, and branding for global integrated campaigns. Demonstrates strong craft leadership and expertise in managing design teams, brand guardianship, and integrating generative AI tools into creative workflows across consumer, tech, and financial sectors.</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>9</v>
-      </c>
-      <c r="I14" t="b">
-        <v>1</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
@@ -3947,7 +3975,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>The candidate's background in creative production and media lacks the specialized expertise in enterprise risk management and internal auditing required for this senior leadership role.</t>
+          <t>The candidate's background is entirely in digital design and creative direction, lacking any relevant experience in enterprise risk management or internal audit.</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
@@ -3990,25 +4018,13 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SYNTH-003</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Head of Finance Business Partnering</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>CIMA-qualified Head of Finance Business Partnering with 12 years in charity and public sector finance. Expert in management accounting, financial planning &amp; analysis, and strategic finance partnering with senior leadership teams. Experienced in leading finance transformation projects and implementing ERP systems.</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>12</v>
-      </c>
-      <c r="I15" t="b">
-        <v>1</v>
-      </c>
+          <t>CAND-009</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
@@ -4019,7 +4035,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>API timeout</t>
+          <t>The candidate profile lacks any background, experience, or job history details to evaluate suitability for the role.</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
@@ -4062,21 +4078,21 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>SYNTH-005</t>
+          <t>SYNTH-001</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Deputy General Counsel</t>
+          <t>Senior Creative Producer (Film &amp; Photography)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Qualified solicitor and Deputy General Counsel with 14 years of in-house and private practice experience in the charity, media, and technology sectors. Expert in commercial contracts, employment law, GDPR/data protection, charity governance, and IP/brand protection. Experienced advising Boards and Trustees.</t>
+          <t>Award-winning Senior Creative Producer with 9 years specialising in documentary film, charity campaigns, and editorial photography for international NGOs. Proven track record managing end-to-end productions from concept to broadcast, leading cross-functional creative teams and delivering compelling visual storytelling.</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I16" t="b">
         <v>1</v>
@@ -4091,7 +4107,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>API timeout</t>
+          <t>The candidate's experience is entirely within creative media production and lacks the necessary background in risk management, internal audit, or governance.</t>
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
@@ -4258,7 +4274,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>1.05</v>
+        <v>7.931</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4272,54 +4288,68 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>SYNTH-004</t>
+          <t>SYNTH-003</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Head of Internal Audit &amp; Risk</t>
+          <t>Head of Finance Business Partnering</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>CIIA-qualified Head of Internal Audit and Risk with 11 years in the charity and financial services sectors. Specialist in enterprise risk management (ERM), internal audit delivery, and governance frameworks. Experienced in audit committee reporting, fraud prevention, and regulatory compliance.</t>
+          <t>CIMA-qualified Head of Finance Business Partnering with 12 years in charity and public sector finance. Expert in management accounting, financial planning &amp; analysis, and strategic finance partnering with senior leadership teams. Experienced in leading finance transformation projects and implementing ERP systems.</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I2" t="b">
         <v>1</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>✗ NEIN</t>
+          <t>✓ JA</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Internal audit and risk management experience does not provide the required track record in FP&amp;A and strategic finance business partnering needed for an interim leadership role.</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>The candidate is a direct title match with 12 years of CIMA-qualified experience specifically within the charity sector.</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>7.33</v>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>None/None Anforderungen</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
+          <t>2/3 Anforderungen</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Fehlender konkreter Nachweis über Business Partnering mit einkommensgenerierenden Teams / Fundraising</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>[10/10] Experience successfully managing a similar Finance: Head of Finance Business Partnering bei British Red Cross: F
+[5/10] Track record in effective partnering with income-g: Business Partnering für 12 Direktorate (British Red Cross) s
+[7/10] Track record in building a high-performing team th: Leitung von 6 FBPs bei British Red Cross und Erzielung von 2</t>
+        </is>
+      </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>(nicht analysiert — nicht in Top 5)</t>
+          <t>Possible Match</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>(nicht analysiert)</t>
+          <t>**Strengths**: Proven track record as Head of Finance Business Partnering at British Red Cross, successfully leading a team of 6 FBPs across 12 directorates. Strong FP&amp;A credentials, delivering £2m cost savings via zero-based budgeting and cutting budget cycles by 40% using Adaptive Insights. CIMA-qualified with 12 years of dedicated UK charity and public sector experience.
+**Gaps**: Lacks explicit evidence of partnering directly with income-generating or fundraising teams, which is a key requirement for this role.
+**Recommendation**: Strong functional and sector fit with direct leadership experience in a major UK charity. Recommended for initial interview to probe experience supporting income-generation streams.</t>
         </is>
       </c>
       <c r="S2" t="inlineStr"/>
@@ -4330,7 +4360,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.35</v>
+        <v>1.05</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -4344,21 +4374,21 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>SYNTH-006</t>
+          <t>SYNTH-004</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Senior Procurement Manager</t>
+          <t>Head of Internal Audit &amp; Risk</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>CIPS-qualified Senior Procurement Manager with 8 years leading procurement functions in charity and public sector organisations. Expert in strategic sourcing, supplier relationship management, and contract management. Delivered £4.5m of savings over 5 years through category management and competitive tendering. Experienced in EU procurement regulations and PCR 2015.</t>
+          <t>CIIA-qualified Head of Internal Audit and Risk with 11 years in the charity and financial services sectors. Specialist in enterprise risk management (ERM), internal audit delivery, and governance frameworks. Experienced in audit committee reporting, fraud prevention, and regulatory compliance.</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I3" t="b">
         <v>1</v>
@@ -4369,11 +4399,11 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Although the candidate has charity sector experience, a background in procurement lacks the essential professional accounting qualifications and FP&amp;A leadership expertise required for this finance role.</t>
+          <t>While the candidate has valuable charity sector experience, an Internal Audit and Risk background lacks the commercial FP&amp;A and direct finance business partnering leadership required for this senior interim role.</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
@@ -4402,7 +4432,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -4416,34 +4446,36 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CAND-001</t>
+          <t>SYNTH-002</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lead Designer</t>
+          <t>Digital Delivery Manager</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lead Designer with over 20 years of multi-sector experience building brand identities and leading creative teams across financial services, technology, NGOs, and specialist sectors. Specialist in end-to-end campaign creative direction, design systems, and multi-channel delivery aligned to commercial objectives.</t>
+          <t>Results-driven Digital Delivery Manager with 7 years delivering agile digital products and online platforms for charity and public sector organisations. Experienced in Scrum, Kanban and SAFe frameworks, managing cross-functional teams of 15+ to deliver user-centred services on time and within budget.</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>23</v>
-      </c>
-      <c r="I4" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="I4" t="b">
+        <v>1</v>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>API timeout</t>
+          <t>The candidate's profile is entirely focused on digital product delivery and project management, lacking the essential expertise in corporate finance, FP&amp;A, and financial business partnering required for this senior leadership role.</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -4472,7 +4504,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -4486,24 +4518,36 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CAND-002</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+          <t>SYNTH-005</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Deputy General Counsel</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Qualified solicitor and Deputy General Counsel with 14 years of in-house and private practice experience in the charity, media, and technology sectors. Expert in commercial contracts, employment law, GDPR/data protection, charity governance, and IP/brand protection. Experienced advising Boards and Trustees.</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>14</v>
+      </c>
+      <c r="I5" t="b">
+        <v>1</v>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>No candidate profile or work experience information is provided to evaluate suitability for the role.</t>
+          <t>Although the candidate has charity sector experience, their background is strictly legal with no track record of managing finance, accounting, or FP&amp;A functions.</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -4532,7 +4576,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -4546,21 +4590,21 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CAND-003</t>
+          <t>SYNTH-006</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Senior Designer (Brand Design &amp; UI/UX)</t>
+          <t>Senior Procurement Manager</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Senior Brand &amp; Visual Designer with 7+ years of experience delivering brand identity, packaging, digital campaigns, and UI/UX design across consumer, B2B, and SaaS sectors. Specialist in multi-brand asset management, print production, AI workflow integration, and high-impact visual communications.</t>
+          <t>CIPS-qualified Senior Procurement Manager with 8 years leading procurement functions in charity and public sector organisations. Expert in strategic sourcing, supplier relationship management, and contract management. Delivered £4.5m of savings over 5 years through category management and competitive tendering. Experienced in EU procurement regulations and PCR 2015.</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I6" t="b">
         <v>1</v>
@@ -4571,11 +4615,11 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>API timeout</t>
+          <t>The candidate's experience is strictly within procurement and contract management, lacking the required accounting qualifications and FP&amp;A leadership background.</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -4618,21 +4662,21 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CAND-004</t>
+          <t>CAND-001</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Work Placement Officer</t>
+          <t>Lead Designer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Education administration professional and law graduate with over a year of experience in compliance, admissions support, and stakeholder coordination. Possesses expertise in contract review, data accuracy, and business engagement with plans to pursue SQE qualifications.</t>
+          <t>Lead Designer with over 20 years of multi-sector experience building brand identities and leading creative teams across financial services, technology, NGOs, and specialist sectors. Specialist in end-to-end campaign creative direction, design systems, and multi-channel delivery aligned to commercial objectives.</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
@@ -4645,7 +4689,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>The candidate lacks any finance background and possesses only one year of junior administration experience, making them completely unqualified for a senior Head of Finance role.</t>
+          <t>The candidate's background is entirely in creative design and brand strategy, lacking any required expertise in financial planning, analysis, or finance team leadership.</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -4688,7 +4732,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CAND-005</t>
+          <t>CAND-002</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -4705,7 +4749,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>The candidate profile contains no information or relevant experience, making it impossible for a recruiter to consider them for the role.</t>
+          <t>There is no candidate information provided to assess suitability for this role.</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -4748,21 +4792,21 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CAND-006</t>
+          <t>CAND-003</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lead Visual Artist</t>
+          <t>Senior Designer (Brand Design &amp; UI/UX)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Senior Brand and Visual Designer with over 6 years of experience leading brand creation and visual systems across physical and digital touchpoints. Specialist in translating strategic positioning into cohesive visual identities, campaign design, and design systems within the tech and wearables sector.</t>
+          <t>Senior Brand &amp; Visual Designer with 7+ years of experience delivering brand identity, packaging, digital campaigns, and UI/UX design across consumer, B2B, and SaaS sectors. Specialist in multi-brand asset management, print production, AI workflow integration, and high-impact visual communications.</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I9" t="b">
         <v>1</v>
@@ -4777,7 +4821,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>API timeout</t>
+          <t>The candidate's background is entirely in visual and UI/UX design, possessing no relevant experience for a senior finance leadership role.</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -4820,25 +4864,23 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CAND-007</t>
+          <t>CAND-004</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Freelance Senior Visual Designer</t>
+          <t>Work Placement Officer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Senior Visual Designer with over 10 years of experience delivering branding, digital campaigns, web design, and motion graphics across global agencies and brands. Specialises in creative strategy, user interface design, and digital product systems with extensive experience leading design projects across the US, LATAM, and UK.</t>
+          <t>Education administration professional and law graduate with over a year of experience in compliance, admissions support, and stakeholder coordination. Possesses expertise in contract review, data accuracy, and business engagement with plans to pursue SQE qualifications.</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>10</v>
-      </c>
-      <c r="I10" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
@@ -4849,7 +4891,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>API timeout</t>
+          <t>The candidate has only one year of experience in education administration and legal compliance, completely lacking the required senior finance expertise and leadership background.</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
@@ -4892,22 +4934,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CAND-008</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Lead Digital Designer</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Lead Digital Designer with over 18 years of experience directing and executing digital design, motion creative, UI, and branding for global integrated campaigns. Demonstrates strong craft leadership and expertise in managing design teams, brand guardianship, and integrating generative AI tools into creative workflows across consumer, tech, and financial sectors.</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>18</v>
-      </c>
+          <t>CAND-005</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
@@ -4919,7 +4951,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>API timeout</t>
+          <t>The candidate profile contains no information regarding job titles, experience, or relevant financial background to assess suitability.</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
@@ -4962,13 +4994,25 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CAND-009</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
+          <t>CAND-006</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Lead Visual Artist</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Senior Brand and Visual Designer with over 6 years of experience leading brand creation and visual systems across physical and digital touchpoints. Specialist in translating strategic positioning into cohesive visual identities, campaign design, and design systems within the tech and wearables sector.</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>6</v>
+      </c>
+      <c r="I12" t="b">
+        <v>1</v>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
@@ -4979,7 +5023,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>No candidate information or work history is provided to assess suitability for this senior finance position.</t>
+          <t>The candidate's background is entirely in brand and visual design, lacking any finance, FP&amp;A, or financial business partnering experience required for this senior leadership role.</t>
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
@@ -5022,24 +5066,24 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SYNTH-001</t>
+          <t>CAND-007</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Senior Creative Producer (Film &amp; Photography)</t>
+          <t>Freelance Senior Visual Designer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Award-winning Senior Creative Producer with 9 years specialising in documentary film, charity campaigns, and editorial photography for international NGOs. Proven track record managing end-to-end productions from concept to broadcast, leading cross-functional creative teams and delivering compelling visual storytelling.</t>
+          <t>Senior Visual Designer with over 10 years of experience delivering branding, digital campaigns, web design, and motion graphics across global agencies and brands. Specialises in creative strategy, user interface design, and digital product systems with extensive experience leading design projects across the US, LATAM, and UK.</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -5051,7 +5095,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>API timeout</t>
+          <t>The candidate's background in visual design and creative strategy bears no relevance to a senior finance business partnering leadership role.</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
@@ -5094,25 +5138,23 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SYNTH-002</t>
+          <t>CAND-008</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Digital Delivery Manager</t>
+          <t>Lead Digital Designer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Results-driven Digital Delivery Manager with 7 years delivering agile digital products and online platforms for charity and public sector organisations. Experienced in Scrum, Kanban and SAFe frameworks, managing cross-functional teams of 15+ to deliver user-centred services on time and within budget.</t>
+          <t>Lead Digital Designer with over 18 years of experience directing and executing digital design, motion creative, UI, and branding for global integrated campaigns. Demonstrates strong craft leadership and expertise in managing design teams, brand guardianship, and integrating generative AI tools into creative workflows across consumer, tech, and financial sectors.</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>7</v>
-      </c>
-      <c r="I14" t="b">
-        <v>1</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
@@ -5123,7 +5165,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>API timeout</t>
+          <t>The candidate's background is entirely in creative digital design with no relevant experience in finance, accounting, or FP&amp;A required for a Head of Finance role.</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
@@ -5166,25 +5208,13 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SYNTH-003</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Head of Finance Business Partnering</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>CIMA-qualified Head of Finance Business Partnering with 12 years in charity and public sector finance. Expert in management accounting, financial planning &amp; analysis, and strategic finance partnering with senior leadership teams. Experienced in leading finance transformation projects and implementing ERP systems.</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>12</v>
-      </c>
-      <c r="I15" t="b">
-        <v>1</v>
-      </c>
+          <t>CAND-009</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
@@ -5195,7 +5225,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>API timeout</t>
+          <t>The candidate profile contains no employment history or qualifications to assess suitability for the role.</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
@@ -5238,21 +5268,21 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>SYNTH-005</t>
+          <t>SYNTH-001</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Deputy General Counsel</t>
+          <t>Senior Creative Producer (Film &amp; Photography)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Qualified solicitor and Deputy General Counsel with 14 years of in-house and private practice experience in the charity, media, and technology sectors. Expert in commercial contracts, employment law, GDPR/data protection, charity governance, and IP/brand protection. Experienced advising Boards and Trustees.</t>
+          <t>Award-winning Senior Creative Producer with 9 years specialising in documentary film, charity campaigns, and editorial photography for international NGOs. Proven track record managing end-to-end productions from concept to broadcast, leading cross-functional creative teams and delivering compelling visual storytelling.</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I16" t="b">
         <v>1</v>
@@ -5267,7 +5297,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>API timeout</t>
+          <t>The candidate has a background strictly in creative media production and lacks any of the required financial management, FP&amp;A, or accounting experience necessary for a Head of Finance role.</t>
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
@@ -5434,7 +5464,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>8.35</v>
+        <v>8.515000000000001</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5477,27 +5507,27 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>The candidate is a CIPS-qualified procurement professional with 8 years of direct procurement leadership experience within the charity sector, making them an ideal match for this role.</t>
+          <t>The candidate is a CIPS-qualified Senior Procurement Manager with extensive experience in the UK charity sector, making them an outstanding fit for a Procurement Lead role at UNICEF UK.</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2/3 Anforderungen</t>
+          <t>3/3 Anforderungen</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Fehlende konkrete Belege für die Balancierung von Governance mit operativer Flexibilität (operational flexibility).</t>
+          <t>Fehlende explizite Nachweise über die direkte Einflussnahme auf C-Level / Board-Ebene (Senior Stakeholder Influence)., Keine konkreten Fallbeispiele im CV zur praktischen Ausbalancierung von Governance und operationaler Flexibilität.</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>[8/10] Shape procurement practice: Senior Procurement Manager bei Action Aid UK: 'Lead procurem
-[7/10] Influence senior stakeholders: Explizite Soft Skills: Stakeholder Management, Leadership, C
-[6/10] Ensure strong governance whilst enabling operation: Starke Governance-Belege durch PCR 2015 / OJEU-Compliance be</t>
+          <t>[8/10] Shape procurement practice: Leitung der Procurement-Funktion bei Action Aid UK inkl. Ein
+[7/10] Influence senior stakeholders: Ausgewiesene Soft Skills in 'Stakeholder Management', 'Leade
+[7/10] Ensure strong governance whilst enabling operation: Starke Governance-Belege durch PCR 2015, OJEU-Compliance, Su</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -5507,9 +5537,9 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>**Strengths**: Proven track record of shaping procurement practices within the UK charity sector, leading an £18m annual spend portfolio at ActionAid UK and establishing a category management framework that generated £1.2m in year-1 savings. Demonstrates robust governance capability through MCIPS accreditation and extensive PCR 2015/OJEU compliance experience across 12 tendering exercises. Strong leadership background, managing a team of 3 and delivering £4.5m total savings across 8 years.
-**Gaps**: Lacks explicit evidence of successfully balancing strict governance controls with operational flexibility.
-**Recommendation**: An excellent sector-aligned candidate with proven procurement leadership in a comparable charity environment. I recommend progressing to interview to explore their practical approach to enabling operational agility alongside compliance.</t>
+          <t>**Strengths**: MCIPS-qualified with 8 years of relevant charity and public sector experience, currently leading Action Aid UK's procurement function (£18m spend, team of 3) and delivering a category framework saving £1.2m in year 1. Demonstrates robust governance expertise through extensive PCR 2015 and OJEU compliant procurement exercises.
+**Gaps**: Lacks explicit CV evidence of direct C-suite or Board-level stakeholder influence, alongside a missing practical record of balancing governance with operational flexibility.
+**Recommendation**: Highly suitable candidate possessing direct charity sector leadership experience and strong domain expertise. Recommend proceeding to interview, probing specifically on C-level stakeholder engagement and operational agility.</t>
         </is>
       </c>
       <c r="S2" t="inlineStr"/>
@@ -5563,7 +5593,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>While the candidate has strong charity sector experience at a senior level, their profile is entirely focused on finance and FP&amp;A rather than procurement, sourcing, and vendor management.</t>
+          <t>While the candidate has strong charity sector experience, a career in finance business partnering lacks the specialized sourcing, contract management, and vendor negotiation skills required for a Procurement Lead role.</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
@@ -5635,7 +5665,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Although the candidate has strong legal and charity sector experience, a legal background does not align with the core supply chain and strategic sourcing responsibilities required for a Procurement Lead.</t>
+          <t>Although the candidate has valuable charity sector experience and expertise in commercial contracts, a Deputy General Counsel lacks the specific operational procurement, purchasing, and supply chain management background required for a Procurement Lead.</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -5707,7 +5737,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>While the candidate has valuable charity sector experience, a background in digital delivery management lacks the core commercial, sourcing, and contract management skills required for a Procurement Lead.</t>
+          <t>While the candidate has valuable charity sector experience, digital delivery management lacks the essential sourcing, commercial contract, and supply chain expertise required for a Procurement Lead.</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -5779,7 +5809,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Although the candidate has relevant charity sector experience, Internal Audit and Risk is a distinct function that lacks the required commercial sourcing, vendor management, and supply chain expertise needed for a Procurement Lead role.</t>
+          <t>Although the candidate has strong charity sector experience, Internal Audit and Risk is a completely different functional specialization from Procurement.</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -5822,25 +5852,23 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>SYNTH-001</t>
+          <t>CAND-004</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Senior Creative Producer (Film &amp; Photography)</t>
+          <t>Work Placement Officer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Award-winning Senior Creative Producer with 9 years specialising in documentary film, charity campaigns, and editorial photography for international NGOs. Proven track record managing end-to-end productions from concept to broadcast, leading cross-functional creative teams and delivering compelling visual storytelling.</t>
+          <t>Education administration professional and law graduate with over a year of experience in compliance, admissions support, and stakeholder coordination. Possesses expertise in contract review, data accuracy, and business engagement with plans to pursue SQE qualifications.</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>9</v>
-      </c>
-      <c r="I7" t="b">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
@@ -5851,7 +5879,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Although the candidate has relevant NGO sector experience, a background in creative production lacks the critical commercial, vendor management, and supply chain expertise required for a Procurement Lead.</t>
+          <t>The candidate has only one year of experience in education administration and lacks the necessary procurement and supply chain management background for a Lead position.</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -5880,7 +5908,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -5894,34 +5922,36 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CAND-001</t>
+          <t>SYNTH-001</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lead Designer</t>
+          <t>Senior Creative Producer (Film &amp; Photography)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lead Designer with over 20 years of multi-sector experience building brand identities and leading creative teams across financial services, technology, NGOs, and specialist sectors. Specialist in end-to-end campaign creative direction, design systems, and multi-channel delivery aligned to commercial objectives.</t>
+          <t>Award-winning Senior Creative Producer with 9 years specialising in documentary film, charity campaigns, and editorial photography for international NGOs. Proven track record managing end-to-end productions from concept to broadcast, leading cross-functional creative teams and delivering compelling visual storytelling.</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>23</v>
-      </c>
-      <c r="I8" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="I8" t="b">
+        <v>1</v>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>A Lead Designer's creative background has no functional overlap or logical career progression into a Procurement Lead role.</t>
+          <t>While the candidate has valuable NGO sector experience, a background in creative media production lacks the required expertise in strategic sourcing, negotiation, and supply chain management essential for a Procurement Lead role.</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -5964,12 +5994,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CAND-002</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+          <t>CAND-001</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Lead Designer</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lead Designer with over 20 years of multi-sector experience building brand identities and leading creative teams across financial services, technology, NGOs, and specialist sectors. Specialist in end-to-end campaign creative direction, design systems, and multi-channel delivery aligned to commercial objectives.</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>23</v>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
@@ -5981,7 +6021,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>No candidate profile or work experience is provided to evaluate suitability for the Procurement Lead role.</t>
+          <t>The candidate's background is exclusively in creative design and branding, offering no relevant experience for a Procurement Lead role.</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -6024,25 +6064,13 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CAND-003</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Senior Designer (Brand Design &amp; UI/UX)</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Senior Brand &amp; Visual Designer with 7+ years of experience delivering brand identity, packaging, digital campaigns, and UI/UX design across consumer, B2B, and SaaS sectors. Specialist in multi-brand asset management, print production, AI workflow integration, and high-impact visual communications.</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>7</v>
-      </c>
-      <c r="I10" t="b">
-        <v>1</v>
-      </c>
+          <t>CAND-002</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
@@ -6053,7 +6081,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>API timeout</t>
+          <t>The candidate profile contains no information or background to assess suitability for the Procurement Lead role.</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
@@ -6096,23 +6124,25 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CAND-004</t>
+          <t>CAND-003</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Work Placement Officer</t>
+          <t>Senior Designer (Brand Design &amp; UI/UX)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Education administration professional and law graduate with over a year of experience in compliance, admissions support, and stakeholder coordination. Possesses expertise in contract review, data accuracy, and business engagement with plans to pursue SQE qualifications.</t>
+          <t>Senior Brand &amp; Visual Designer with 7+ years of experience delivering brand identity, packaging, digital campaigns, and UI/UX design across consumer, B2B, and SaaS sectors. Specialist in multi-brand asset management, print production, AI workflow integration, and high-impact visual communications.</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="I11" t="b">
+        <v>1</v>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
@@ -6123,7 +6153,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>API timeout</t>
+          <t>The candidate's background is entirely focused on visual and UI/UX design, offering no transferrable skills or relevant experience for a Procurement Lead position.</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
@@ -6183,7 +6213,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>The candidate profile contains no information or employment history to assess suitability for the Procurement Lead role.</t>
+          <t>No candidate information is provided to assess suitability for the Procurement Lead role.</t>
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
@@ -6255,7 +6285,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>API timeout</t>
+          <t>The candidate's background in visual art and brand design is completely unrelated to a Procurement Lead role focused on purchasing and supply chain management.</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
@@ -6327,7 +6357,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>The candidate's career is strictly focused on visual design and creative strategy, with no relevant background in procurement, sourcing, or vendor management.</t>
+          <t>The candidate's background is entirely in visual design and creative strategy, which has no functional overlap with a Procurement Lead role focused on sourcing, vendor management, and supply chain.</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
@@ -6397,7 +6427,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>The candidate's background in creative digital design and branding has no alignment with a strategic procurement and vendor management role.</t>
+          <t>The candidate's background is entirely focused on digital design and creative leadership, showing no transferable experience in procurement, vendor management, or strategic purchasing.</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
@@ -6457,7 +6487,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>The candidate profile contains no information regarding background, skills, or experience to evaluate suitability for a Procurement Lead role.</t>
+          <t>No candidate profile or career history is provided to assess suitability for the Procurement Lead position.</t>
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
@@ -6624,7 +6654,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>8.57</v>
+        <v>8.994</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6667,11 +6697,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>The candidate has the exact matching job title and 9 years of directly relevant experience in film and photography production within the charity and international NGO sector.</t>
+          <t>The candidate holds the exact job title required, possesses 9 years of directly relevant experience within international NGOs, and fully aligns with the creative and production demands of the role.</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>7.8</v>
+        <v>8.17</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -6680,26 +6710,28 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Expliziter Nachweis von Kenntnissen und Haltung zu ethischer Content-Erstellung (Ethical Content Creation) und inklusivem Storytelling (Inclusive Storytelling).</t>
+          <t>Kein expliziter Beleg für Nachweise/Zertifikate oder konkrete Frameworks zu 'Ethical Content Creation' und 'Inclusive Storytelling' im Profil vorhanden.</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[10/10] Experienced creative leader with a strong track re: 9 Jahre Berufserfahrung als Senior Creative Producer u.a. be
-[9/10] Excellent creative judgement and experience leadin: Ausgewiesene Skills in 'Creative Leadership' und 'Team Direc
-[8/10] Deep understanding of visual storytelling, audienc: Fundierte technische Skills (Storyboarding, Scriptwriting, F
-[4/10] Passion for inclusive storytelling and ethical con: Kein expliziter Beleg für 'inclusive storytelling' oder 'eth
-[7/10] Ability to translate insight, strategy, and organi: Leitung aller Film- und Fotokampagnen bei Save the Children </t>
+          <t>[10/10] Experienced creative leader with a strong track re: 9 Jahre Berufserfahrung; Senior Creative Producer bei Save t
+[9/10] Excellent creative judgement and experience leadin: Soft Skills 'Creative Leadership' und 'Team Direction'; Führ
+[8/10] Deep understanding of visual storytelling, audienc: Technische Skills in Storyboarding, Scriptwriting, Film Prod
+[6/10] Passion for inclusive storytelling and ethical con: Langjährige Tätigkeit im NGO- und Charity-Sektor (Save the C
+[7/10] Ability to translate insight, strategy, and organi: Verantwortung für sämtliche Film- und Fotokampagnen bei Save</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Strong Match</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>(failed: )</t>
+          <t>**Strengths**: Proven track record in international NGO content creation with 9 years of experience, including leading film/photography campaigns at Save the Children UK and Comic Relief. Extensive experience managing complex international productions (£1.2m budget, 40+ documentary shorts in Africa/Middle East, crews across 12 countries) and a strong portfolio demonstrated by 3 Charity Film Awards.
+**Gaps**: Lacks explicit documentation or formal frameworks regarding ethical content creation and inclusive storytelling standards in their profile, despite extensive sector experience.
+**Recommendation**: The candidate brings exceptional sector-specific experience, proven international production leadership, and award-winning visual storytelling capability directly aligned with UNICEF UK's needs. Recommend proceeding to interview to explore their approach to ethical content guidelines.</t>
         </is>
       </c>
       <c r="S2" t="inlineStr"/>
@@ -6710,7 +6742,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>1.4</v>
+        <v>1.05</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -6747,11 +6779,11 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>While the candidate possesses extensive creative leadership and NGO experience, their background focuses on graphic brand design rather than specialized film and photography content production.</t>
+          <t>While the candidate brings extensive creative leadership and NGO experience, their profile focuses on visual/graphic design and brand identity rather than hands-on film and photography production.</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
@@ -6780,7 +6812,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>1.4</v>
+        <v>1.05</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -6794,34 +6826,36 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CAND-008</t>
+          <t>CAND-003</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lead Digital Designer</t>
+          <t>Senior Designer (Brand Design &amp; UI/UX)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lead Digital Designer with over 18 years of experience directing and executing digital design, motion creative, UI, and branding for global integrated campaigns. Demonstrates strong craft leadership and expertise in managing design teams, brand guardianship, and integrating generative AI tools into creative workflows across consumer, tech, and financial sectors.</t>
+          <t>Senior Brand &amp; Visual Designer with 7+ years of experience delivering brand identity, packaging, digital campaigns, and UI/UX design across consumer, B2B, and SaaS sectors. Specialist in multi-brand asset management, print production, AI workflow integration, and high-impact visual communications.</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>18</v>
-      </c>
-      <c r="I4" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="I4" t="b">
+        <v>1</v>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>While the candidate brings extensive creative leadership in digital design and branding, they lack the specific track record in film and photography production required for this role.</t>
+          <t>The candidate's background is strictly in graphic, brand, and UI/UX design, lacking the necessary specialized experience in film and photography production.</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -6893,7 +6927,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>The candidate is a brand and visual systems designer in tech/e-commerce, lacking the required specialized experience in film and photography content production.</t>
+          <t>The candidate specializes in brand identity and visual design systems rather than film and photography content production.</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -6936,25 +6970,23 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CAND-007</t>
+          <t>CAND-008</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Freelance Senior Visual Designer</t>
+          <t>Lead Digital Designer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Senior Visual Designer with over 10 years of experience delivering branding, digital campaigns, web design, and motion graphics across global agencies and brands. Specialises in creative strategy, user interface design, and digital product systems with extensive experience leading design projects across the US, LATAM, and UK.</t>
+          <t>Lead Digital Designer with over 18 years of experience directing and executing digital design, motion creative, UI, and branding for global integrated campaigns. Demonstrates strong craft leadership and expertise in managing design teams, brand guardianship, and integrating generative AI tools into creative workflows across consumer, tech, and financial sectors.</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>10</v>
-      </c>
-      <c r="I6" t="b">
-        <v>0</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
@@ -6965,7 +6997,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>While the candidate has strong visual design and motion graphics experience, they lack the specific track record in film and photography production required for this Senior Creative Producer role.</t>
+          <t>While the candidate possesses extensive creative leadership experience, their background is focused on digital UI and branding design rather than hands-on film and photography content production.</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -7008,24 +7040,24 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>SYNTH-002</t>
+          <t>CAND-007</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Digital Delivery Manager</t>
+          <t>Freelance Senior Visual Designer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Results-driven Digital Delivery Manager with 7 years delivering agile digital products and online platforms for charity and public sector organisations. Experienced in Scrum, Kanban and SAFe frameworks, managing cross-functional teams of 15+ to deliver user-centred services on time and within budget.</t>
+          <t>Senior Visual Designer with over 10 years of experience delivering branding, digital campaigns, web design, and motion graphics across global agencies and brands. Specialises in creative strategy, user interface design, and digital product systems with extensive experience leading design projects across the US, LATAM, and UK.</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -7037,7 +7069,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>While the candidate has relevant charity sector experience, a background in agile digital delivery management lacks the essential creative leadership, film, and photography production expertise required for this role.</t>
+          <t>While the candidate has strong visual design and motion graphics experience, they lack the core film and photography production expertise required for this Creative Producer role.</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -7066,7 +7098,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -7080,24 +7112,36 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CAND-002</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+          <t>SYNTH-002</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Digital Delivery Manager</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Results-driven Digital Delivery Manager with 7 years delivering agile digital products and online platforms for charity and public sector organisations. Experienced in Scrum, Kanban and SAFe frameworks, managing cross-functional teams of 15+ to deliver user-centred services on time and within budget.</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>7</v>
+      </c>
+      <c r="I8" t="b">
+        <v>1</v>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>No candidate information or work history was provided to assess suitability for the role.</t>
+          <t>While the candidate has relevant charity sector experience, a background in technical digital delivery management lacks the required film, photography, and creative production expertise.</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -7126,7 +7170,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -7140,21 +7184,21 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CAND-003</t>
+          <t>SYNTH-005</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Senior Designer (Brand Design &amp; UI/UX)</t>
+          <t>Deputy General Counsel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Senior Brand &amp; Visual Designer with 7+ years of experience delivering brand identity, packaging, digital campaigns, and UI/UX design across consumer, B2B, and SaaS sectors. Specialist in multi-brand asset management, print production, AI workflow integration, and high-impact visual communications.</t>
+          <t>Qualified solicitor and Deputy General Counsel with 14 years of in-house and private practice experience in the charity, media, and technology sectors. Expert in commercial contracts, employment law, GDPR/data protection, charity governance, and IP/brand protection. Experienced advising Boards and Trustees.</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="I9" t="b">
         <v>1</v>
@@ -7165,11 +7209,11 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>API timeout</t>
+          <t>The candidate has a background entirely focused on legal and compliance functions, lacking the essential hands-on experience in creative direction, film production, and visual storytelling required for this role.</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -7212,22 +7256,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CAND-004</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Work Placement Officer</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Education administration professional and law graduate with over a year of experience in compliance, admissions support, and stakeholder coordination. Possesses expertise in contract review, data accuracy, and business engagement with plans to pursue SQE qualifications.</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>1</v>
-      </c>
+          <t>CAND-002</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
@@ -7239,7 +7273,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>The candidate has no experience in film, photography, or creative leadership, coming from an entry-level background in legal and educational administration.</t>
+          <t>No candidate profile or work history is provided, making it impossible for a recruiter to consider this application.</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
@@ -7282,12 +7316,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CAND-005</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+          <t>CAND-004</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Work Placement Officer</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Education administration professional and law graduate with over a year of experience in compliance, admissions support, and stakeholder coordination. Possesses expertise in contract review, data accuracy, and business engagement with plans to pursue SQE qualifications.</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
@@ -7299,7 +7343,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>The candidate profile contains no information or career history to demonstrate the required film and photography production experience.</t>
+          <t>The candidate's background in education administration and law completely lacks the creative leadership and film/photography production experience required for this senior role.</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
@@ -7342,7 +7386,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CAND-009</t>
+          <t>CAND-005</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -7359,7 +7403,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>No candidate information or work history is provided, making it impossible for a recruiter to consider them for this role.</t>
+          <t>No professional details, job title, or experience are provided to evaluate suitability for the role.</t>
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
@@ -7402,25 +7446,13 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SYNTH-003</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Head of Finance Business Partnering</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>CIMA-qualified Head of Finance Business Partnering with 12 years in charity and public sector finance. Expert in management accounting, financial planning &amp; analysis, and strategic finance partnering with senior leadership teams. Experienced in leading finance transformation projects and implementing ERP systems.</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>12</v>
-      </c>
-      <c r="I13" t="b">
-        <v>1</v>
-      </c>
+          <t>CAND-009</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
@@ -7431,7 +7463,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>API timeout</t>
+          <t>No profile, work history, or experience details are provided to evaluate the candidate's suitability for the role.</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
@@ -7474,21 +7506,21 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SYNTH-004</t>
+          <t>SYNTH-003</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Head of Internal Audit &amp; Risk</t>
+          <t>Head of Finance Business Partnering</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>CIIA-qualified Head of Internal Audit and Risk with 11 years in the charity and financial services sectors. Specialist in enterprise risk management (ERM), internal audit delivery, and governance frameworks. Experienced in audit committee reporting, fraud prevention, and regulatory compliance.</t>
+          <t>CIMA-qualified Head of Finance Business Partnering with 12 years in charity and public sector finance. Expert in management accounting, financial planning &amp; analysis, and strategic finance partnering with senior leadership teams. Experienced in leading finance transformation projects and implementing ERP systems.</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I14" t="b">
         <v>1</v>
@@ -7503,7 +7535,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>The candidate's background is entirely in internal audit, risk management, and compliance, offering no transferable experience for a senior creative media production role.</t>
+          <t>The candidate has an entirely finance-focused background with zero experience in visual storytelling, creative leadership, or film and photography production.</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
@@ -7546,21 +7578,21 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SYNTH-005</t>
+          <t>SYNTH-004</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Deputy General Counsel</t>
+          <t>Head of Internal Audit &amp; Risk</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Qualified solicitor and Deputy General Counsel with 14 years of in-house and private practice experience in the charity, media, and technology sectors. Expert in commercial contracts, employment law, GDPR/data protection, charity governance, and IP/brand protection. Experienced advising Boards and Trustees.</t>
+          <t>CIIA-qualified Head of Internal Audit and Risk with 11 years in the charity and financial services sectors. Specialist in enterprise risk management (ERM), internal audit delivery, and governance frameworks. Experienced in audit committee reporting, fraud prevention, and regulatory compliance.</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I15" t="b">
         <v>1</v>
@@ -7575,7 +7607,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Despite extensive legal experience in the charity sector, the candidate completely lacks the required background in film and photography production, visual storytelling, and creative leadership.</t>
+          <t>The candidate's background in internal audit and risk management is completely unrelated to creative leadership, film, and photography production.</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
@@ -7647,7 +7679,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>The candidate's background in procurement and contract management is entirely unrelated to visual storytelling, film, and photography production.</t>
+          <t>The candidate's experience is exclusively in procurement and contract management, lacking any background in creative leadership, film, or visual content production.</t>
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
@@ -7814,7 +7846,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>8.19</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7853,15 +7885,15 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>The candidate has a highly relevant public sector finance background and CIMA qualification, making them a very strong candidate despite potentially being overqualified for a Senior Officer role.</t>
+          <t>The candidate is CIMA-qualified with extensive UK public sector finance experience, making them a highly plausible and strong candidate for a Senior Finance Officer role.</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -7871,11 +7903,11 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>[8/10] Building and managing relationships: developing ra: Führung eines Teams von 6 Finance Business Partnern zur Unte
-[8/10] Communicating, engaging and influencing: presentin: Soft Skills 'Communication' und 'Stakeholder Influence'; erf
-[8/10] Planning and organising: thinking ahead, managing : Verwaltung eines 85 Mio. £ Budgets, Verantwortung für Month-
-[7/10] Research and analysis: gathering intelligence from: Erfahrung mit Variance Analysis, FP&amp;A und Cash Flow Forecast
-[8/10] Problem solving: analysing and interpreting situat: Expliziter Soft Skill 'Problem Solving'; Lösungskompetenz de</t>
+          <t>[8/10] Building and managing relationships: developing ra: Led a team of 6 finance business partners supporting 12 dire
+[8/10] Communicating, engaging and influencing: presentin: Engaged and influenced stakeholders across 12 directorates t
+[8/10] Planning and organising: thinking ahead, managing : Managed an £85m combined budget, oversaw month-end close and
+[7/10] Research and analysis: gathering intelligence from: Demonstrated through Variance Analysis, FP&amp;A skills, and zer
+[7/10] Problem solving: analysing and interpreting situat: Explicitly listed Problem Solving and Strategic Thinking ski</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -7885,9 +7917,9 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>**Strengths**: CIMA-qualified with 12 years of public and charity sector experience, including relevant local government exposure at London Borough of Southwark. Proficient in SAP and month-end close processes with strong stakeholder engagement skills.
-**Gaps**: Candidate is overqualified, currently operating as Head of Finance Business Partnering. Lacks explicit details on day-to-day Asset and Estate Management (AEM) tenant operations.
-**Recommendation**: The candidate easily exceeds technical requirements and brings valuable public sector expertise. Recommend probing motivation and career expectations to manage potential overqualification risks.</t>
+          <t>**Strengths**: 1. Strong public sector and housing domain experience from London Borough of Southwark (£85m budget management). 2. CIMA-qualified with direct SAP proficiency and hands-on month-end close and reporting expertise. 3. Proven stakeholder engagement skills, having led teams and influenced senior leadership across 12 directorates.
+**Gaps**: 1. Risk of overqualification, moving from a Head of Finance position to an operational Senior Finance Officer role. 2. Lacks explicit experience in Asset &amp; Estate Management (AEM) portfolio oversight and tenant-related cash transfer notes.
+**Recommendation**: The candidate's public sector background, CIMA qualification, and SAP skills make them technically ideal for OPDC. Recommend interviewing to assess motivation for stepping into a more hands-on operational role.</t>
         </is>
       </c>
       <c r="S2" t="inlineStr"/>
@@ -7898,7 +7930,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>7.07</v>
+        <v>2.4</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -7941,41 +7973,29 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>The candidate has a strong background in financial governance, risk, and audit within public-adjacent sectors, making them functionally relevant despite being potentially overqualified.</t>
+          <t>The candidate's extensive background in internal audit, governance, and financial risk within adjacent sectors makes them a highly relevant applicant for a Senior Finance Officer role.</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>5/5 Anforderungen</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>Fokus liegt stark auf Audit, Risiko und Governance; direkte Nachweise für operative Buchhaltung, Budgetierung und Finanzberichterstattung (Management Accounting) fehlen im Detail.</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>[8/10] Building and managing relationships: developing ra: Nachgewiesene Erfahrung in der Führung von Audit-Teams (4-6 
-[8/10] Communicating, engaging and influencing: presentin: 'Board Communication', 'Audit Committee Reporting' bei Macmi
-[8/10] Planning and organising: thinking ahead, managing : Verantwortlich für das gesamte Internal Audit Programm und E
-[8/10] Research and analysis: gathering intelligence from: Durchführung komplexer Finanz- und Betriebs-Audits bei Lloyd
-[7/10] Problem solving: analysing and interpreting situat: 'Critical Thinking', Analyse komplexer operativer/finanziell</t>
-        </is>
-      </c>
+          <t>0/5 Anforderungen</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Possible Match</t>
+          <t>Weak Match</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>**Strengths**: CIIA-qualified with a BA in Accounting &amp; Finance and 11 years of governance experience across public/charity sectors (NHS, Macmillan). Demonstrates strong stakeholder communication skills, reporting directly to CFOs and Board Committees. Proven analytical expertise in financial control, having identified £3.2m in control weaknesses at Lloyds Banking Group.
-**Gaps**: Lacks explicit evidence of hands-on operational accounting routines, such as posting SAP journals, raising sales invoices, and cash allocations. No documented experience managing Asset &amp; Estate Management (AEM) portfolios.
-**Recommendation**: The candidate possesses strong transferable analytical skills and relevant sector background, but is currently focused on high-level risk and audit. Interviewing should probe their willingness and technical capability to perform day-to-day transactional finance duties.</t>
+          <t>**Strengths**: Holds a BA in Accounting &amp; Finance and a CIIA qualification, providing a solid technical foundation. Demonstrates strong experience in stakeholder engagement, risk analysis, and reporting to CFOs and senior committees within public and third-sector organisations (NHS England, Macmillan).
+**Gaps**: Lacks direct hands-on operational accounting experience, specifically posting SAP journals, period/quarter-end close processes, raising sales invoices, and Asset &amp; Estate Management (AEM) portfolio oversight. The profile is heavily aligned with audit and risk governance rather than routine financial operations.
+**Recommendation**: While highly qualified in internal audit and risk management, the candidate's background does not align with the day-to-day operational and transactional accounting tasks required for this role.</t>
         </is>
       </c>
       <c r="S3" t="inlineStr"/>
@@ -8029,7 +8049,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Although the candidate has strong public sector experience, procurement is a distinct discipline from finance and lacks the required accounting qualifications and financial management background for a Senior Finance Officer role.</t>
+          <t>While the candidate has strong public sector procurement experience, they lack the specific accounting qualifications and core financial management expertise required for a Senior Finance Officer role.</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -8058,7 +8078,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.35</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -8072,34 +8092,36 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CAND-004</t>
+          <t>SYNTH-002</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Work Placement Officer</t>
+          <t>Digital Delivery Manager</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Education administration professional and law graduate with over a year of experience in compliance, admissions support, and stakeholder coordination. Possesses expertise in contract review, data accuracy, and business engagement with plans to pursue SQE qualifications.</t>
+          <t>Results-driven Digital Delivery Manager with 7 years delivering agile digital products and online platforms for charity and public sector organisations. Experienced in Scrum, Kanban and SAFe frameworks, managing cross-functional teams of 15+ to deliver user-centred services on time and within budget.</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="I5" t="b">
+        <v>1</v>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>The candidate lacks a background in finance and senior-level experience, coming from a junior education administration and legal profile.</t>
+          <t>The candidate's background in digital product delivery lacks the essential accounting qualifications and financial management expertise required for a Senior Finance Officer role.</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -8142,25 +8164,23 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SYNTH-002</t>
+          <t>CAND-004</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Digital Delivery Manager</t>
+          <t>Work Placement Officer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Results-driven Digital Delivery Manager with 7 years delivering agile digital products and online platforms for charity and public sector organisations. Experienced in Scrum, Kanban and SAFe frameworks, managing cross-functional teams of 15+ to deliver user-centred services on time and within budget.</t>
+          <t>Education administration professional and law graduate with over a year of experience in compliance, admissions support, and stakeholder coordination. Possesses expertise in contract review, data accuracy, and business engagement with plans to pursue SQE qualifications.</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>7</v>
-      </c>
-      <c r="I6" t="b">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
@@ -8171,7 +8191,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>The candidate's background is in digital product delivery and agile project management, lacking the required financial qualifications and core accounting experience for a Senior Finance Officer role.</t>
+          <t>The candidate has only one year of experience in education administration and legal compliance, completely lacking the finance background required for a senior finance role.</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -8214,21 +8234,21 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>SYNTH-005</t>
+          <t>SYNTH-001</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Deputy General Counsel</t>
+          <t>Senior Creative Producer (Film &amp; Photography)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Qualified solicitor and Deputy General Counsel with 14 years of in-house and private practice experience in the charity, media, and technology sectors. Expert in commercial contracts, employment law, GDPR/data protection, charity governance, and IP/brand protection. Experienced advising Boards and Trustees.</t>
+          <t>Award-winning Senior Creative Producer with 9 years specialising in documentary film, charity campaigns, and editorial photography for international NGOs. Proven track record managing end-to-end productions from concept to broadcast, leading cross-functional creative teams and delivering compelling visual storytelling.</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I7" t="b">
         <v>1</v>
@@ -8243,7 +8263,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>The candidate is a senior legal professional with no background or qualifications in finance and accounting required for a Senior Finance Officer role.</t>
+          <t>The candidate's background is entirely in creative media production and lacks the necessary financial qualifications and core accounting experience required for a Senior Finance Officer role.</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -8272,7 +8292,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -8286,34 +8306,36 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CAND-001</t>
+          <t>SYNTH-005</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lead Designer</t>
+          <t>Deputy General Counsel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lead Designer with over 20 years of multi-sector experience building brand identities and leading creative teams across financial services, technology, NGOs, and specialist sectors. Specialist in end-to-end campaign creative direction, design systems, and multi-channel delivery aligned to commercial objectives.</t>
+          <t>Qualified solicitor and Deputy General Counsel with 14 years of in-house and private practice experience in the charity, media, and technology sectors. Expert in commercial contracts, employment law, GDPR/data protection, charity governance, and IP/brand protection. Experienced advising Boards and Trustees.</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>23</v>
-      </c>
-      <c r="I8" t="inlineStr"/>
+        <v>14</v>
+      </c>
+      <c r="I8" t="b">
+        <v>1</v>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>The candidate has a purely creative background in design and brand management, completely lacking the required financial management and accounting background for a Senior Finance Officer role.</t>
+          <t>The candidate is a qualified legal professional (Deputy General Counsel) with no background or credentials in accounting and financial management required for a Senior Finance Officer role.</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -8356,12 +8378,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CAND-002</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+          <t>CAND-001</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Lead Designer</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lead Designer with over 20 years of multi-sector experience building brand identities and leading creative teams across financial services, technology, NGOs, and specialist sectors. Specialist in end-to-end campaign creative direction, design systems, and multi-channel delivery aligned to commercial objectives.</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>23</v>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
@@ -8373,7 +8405,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>No career history, job title, or profile details are provided to demonstrate any suitability for a Senior Finance Officer role.</t>
+          <t>The candidate has a career exclusively in creative direction and design, making them unqualified for a Senior Finance Officer role.</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -8416,25 +8448,13 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CAND-003</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Senior Designer (Brand Design &amp; UI/UX)</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Senior Brand &amp; Visual Designer with 7+ years of experience delivering brand identity, packaging, digital campaigns, and UI/UX design across consumer, B2B, and SaaS sectors. Specialist in multi-brand asset management, print production, AI workflow integration, and high-impact visual communications.</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>7</v>
-      </c>
-      <c r="I10" t="b">
-        <v>1</v>
-      </c>
+          <t>CAND-002</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
@@ -8445,7 +8465,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>The candidate's background in brand design and UI/UX has no professional alignment or transferable domain expertise for a Senior Finance Officer position.</t>
+          <t>No candidate profile or experience data is provided to evaluate suitability for a Senior Finance Officer position.</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
@@ -8488,13 +8508,25 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CAND-005</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
+          <t>CAND-003</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Senior Designer (Brand Design &amp; UI/UX)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Senior Brand &amp; Visual Designer with 7+ years of experience delivering brand identity, packaging, digital campaigns, and UI/UX design across consumer, B2B, and SaaS sectors. Specialist in multi-brand asset management, print production, AI workflow integration, and high-impact visual communications.</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>7</v>
+      </c>
+      <c r="I11" t="b">
+        <v>1</v>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
@@ -8505,7 +8537,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>The candidate's profile contains no details regarding their background, experience, or current role to assess suitability for the Senior Finance Officer position.</t>
+          <t>The candidate's background is entirely in brand and UI/UX design with no relevant finance, accounting, or public sector experience required for a Senior Finance Officer role.</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
@@ -8548,25 +8580,13 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CAND-006</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Lead Visual Artist</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Senior Brand and Visual Designer with over 6 years of experience leading brand creation and visual systems across physical and digital touchpoints. Specialist in translating strategic positioning into cohesive visual identities, campaign design, and design systems within the tech and wearables sector.</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>6</v>
-      </c>
-      <c r="I12" t="b">
-        <v>1</v>
-      </c>
+          <t>CAND-005</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
@@ -8577,7 +8597,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>The candidate's background as a Lead Visual Artist in brand design has no relevant experience or technical skills applicable to a Senior Finance Officer role.</t>
+          <t>No information about the candidate's career history or qualifications is available to assess suitability for the role.</t>
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
@@ -8620,24 +8640,24 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CAND-007</t>
+          <t>CAND-006</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Freelance Senior Visual Designer</t>
+          <t>Lead Visual Artist</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Senior Visual Designer with over 10 years of experience delivering branding, digital campaigns, web design, and motion graphics across global agencies and brands. Specialises in creative strategy, user interface design, and digital product systems with extensive experience leading design projects across the US, LATAM, and UK.</t>
+          <t>Senior Brand and Visual Designer with over 6 years of experience leading brand creation and visual systems across physical and digital touchpoints. Specialist in translating strategic positioning into cohesive visual identities, campaign design, and design systems within the tech and wearables sector.</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -8649,7 +8669,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>The candidate's background is entirely in visual design and branding, lacking any relevant finance, accounting, or public sector financial management experience required for a Senior Finance Officer role.</t>
+          <t>The candidate's experience is entirely in visual design and branding, lacking the essential finance background and qualifications required for a Senior Finance Officer role.</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
@@ -8692,23 +8712,25 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CAND-008</t>
+          <t>CAND-007</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lead Digital Designer</t>
+          <t>Freelance Senior Visual Designer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lead Digital Designer with over 18 years of experience directing and executing digital design, motion creative, UI, and branding for global integrated campaigns. Demonstrates strong craft leadership and expertise in managing design teams, brand guardianship, and integrating generative AI tools into creative workflows across consumer, tech, and financial sectors.</t>
+          <t>Senior Visual Designer with over 10 years of experience delivering branding, digital campaigns, web design, and motion graphics across global agencies and brands. Specialises in creative strategy, user interface design, and digital product systems with extensive experience leading design projects across the US, LATAM, and UK.</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>18</v>
-      </c>
-      <c r="I14" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
@@ -8719,7 +8741,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>The candidate's extensive background in digital design and creative direction has no relevance or technical alignment with a Senior Finance Officer role.</t>
+          <t>The candidate's background is entirely in visual design and creative strategy, with no relevant experience or qualifications in finance or accounting.</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
@@ -8762,12 +8784,22 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CAND-009</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
+          <t>CAND-008</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Lead Digital Designer</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lead Digital Designer with over 18 years of experience directing and executing digital design, motion creative, UI, and branding for global integrated campaigns. Demonstrates strong craft leadership and expertise in managing design teams, brand guardianship, and integrating generative AI tools into creative workflows across consumer, tech, and financial sectors.</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>18</v>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
@@ -8779,7 +8811,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>The profile contains no information regarding work history, skills, or financial experience, making it impossible to consider the candidate for a Senior Finance Officer role.</t>
+          <t>The candidate's 18-year background in digital design and creative direction is completely unrelated to a Senior Finance Officer role in the public sector.</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
@@ -8822,25 +8854,13 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>SYNTH-001</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Senior Creative Producer (Film &amp; Photography)</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Award-winning Senior Creative Producer with 9 years specialising in documentary film, charity campaigns, and editorial photography for international NGOs. Proven track record managing end-to-end productions from concept to broadcast, leading cross-functional creative teams and delivering compelling visual storytelling.</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>9</v>
-      </c>
-      <c r="I16" t="b">
-        <v>1</v>
-      </c>
+          <t>CAND-009</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
@@ -8851,7 +8871,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>The candidate's background is exclusively in creative media production and lacks any relevant financial management or accounting experience required for a Senior Finance Officer role.</t>
+          <t>No work history or candidate details are provided, making it impossible for a recruiter to consider this profile for a Senior Finance Officer position.</t>
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
@@ -9032,21 +9052,21 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>SYNTH-001</t>
+          <t>SYNTH-003</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Senior Creative Producer (Film &amp; Photography)</t>
+          <t>Head of Finance Business Partnering</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Award-winning Senior Creative Producer with 9 years specialising in documentary film, charity campaigns, and editorial photography for international NGOs. Proven track record managing end-to-end productions from concept to broadcast, leading cross-functional creative teams and delivering compelling visual storytelling.</t>
+          <t>CIMA-qualified Head of Finance Business Partnering with 12 years in charity and public sector finance. Expert in management accounting, financial planning &amp; analysis, and strategic finance partnering with senior leadership teams. Experienced in leading finance transformation projects and implementing ERP systems.</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I2" t="b">
         <v>1</v>
@@ -9061,7 +9081,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>The candidate's background in creative media production completely lacks the required clinical expertise, health professional training experience, and knowledge of Baby Friendly Initiative standards.</t>
+          <t>The candidate is a senior finance executive lacking the required clinical or health practitioner background in infant feeding and Baby Friendly standards.</t>
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
@@ -9090,7 +9110,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -9104,34 +9124,36 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CAND-001</t>
+          <t>SYNTH-004</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lead Designer</t>
+          <t>Head of Internal Audit &amp; Risk</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lead Designer with over 20 years of multi-sector experience building brand identities and leading creative teams across financial services, technology, NGOs, and specialist sectors. Specialist in end-to-end campaign creative direction, design systems, and multi-channel delivery aligned to commercial objectives.</t>
+          <t>CIIA-qualified Head of Internal Audit and Risk with 11 years in the charity and financial services sectors. Specialist in enterprise risk management (ERM), internal audit delivery, and governance frameworks. Experienced in audit committee reporting, fraud prevention, and regulatory compliance.</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>23</v>
-      </c>
-      <c r="I3" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="I3" t="b">
+        <v>1</v>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>The candidate has a creative design background with no experience in UK public healthcare, infant feeding standards, or delivering health professional training.</t>
+          <t>The candidate's background is strictly in internal audit and risk management, completely lacking the required clinical and practical expertise in infant feeding standards and healthcare training.</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
@@ -9160,7 +9182,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -9174,24 +9196,36 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CAND-002</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+          <t>SYNTH-005</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Deputy General Counsel</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Qualified solicitor and Deputy General Counsel with 14 years of in-house and private practice experience in the charity, media, and technology sectors. Expert in commercial contracts, employment law, GDPR/data protection, charity governance, and IP/brand protection. Experienced advising Boards and Trustees.</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>14</v>
+      </c>
+      <c r="I4" t="b">
+        <v>1</v>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>API timeout</t>
+          <t>The candidate is a senior legal professional without the required clinical background or experience in delivering infant feeding training to health professionals.</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -9234,25 +9268,23 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CAND-003</t>
+          <t>CAND-001</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Senior Designer (Brand Design &amp; UI/UX)</t>
+          <t>Lead Designer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Senior Brand &amp; Visual Designer with 7+ years of experience delivering brand identity, packaging, digital campaigns, and UI/UX design across consumer, B2B, and SaaS sectors. Specialist in multi-brand asset management, print production, AI workflow integration, and high-impact visual communications.</t>
+          <t>Lead Designer with over 20 years of multi-sector experience building brand identities and leading creative teams across financial services, technology, NGOs, and specialist sectors. Specialist in end-to-end campaign creative direction, design systems, and multi-channel delivery aligned to commercial objectives.</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>7</v>
-      </c>
-      <c r="I5" t="b">
-        <v>1</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
@@ -9263,7 +9295,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>API timeout</t>
+          <t>The candidate's background in creative design and brand direction is entirely unrelated to the required clinical and public health expertise in infant feeding standards.</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -9306,22 +9338,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CAND-004</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Work Placement Officer</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Education administration professional and law graduate with over a year of experience in compliance, admissions support, and stakeholder coordination. Possesses expertise in contract review, data accuracy, and business engagement with plans to pursue SQE qualifications.</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>1</v>
-      </c>
+          <t>CAND-002</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
@@ -9333,7 +9355,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>API timeout</t>
+          <t>The candidate profile is completely empty, offering no evidence of the required infant feeding expertise or public service background.</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -9376,13 +9398,25 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CAND-005</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
+          <t>CAND-003</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Senior Designer (Brand Design &amp; UI/UX)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Senior Brand &amp; Visual Designer with 7+ years of experience delivering brand identity, packaging, digital campaigns, and UI/UX design across consumer, B2B, and SaaS sectors. Specialist in multi-brand asset management, print production, AI workflow integration, and high-impact visual communications.</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>7</v>
+      </c>
+      <c r="I7" t="b">
+        <v>1</v>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
@@ -9393,7 +9427,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>API timeout</t>
+          <t>The candidate's background in brand and UI/UX design is completely unrelated to the required expertise in public health, infant feeding training, and Baby Friendly Initiative standards.</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -9436,25 +9470,23 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CAND-006</t>
+          <t>CAND-004</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lead Visual Artist</t>
+          <t>Work Placement Officer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Senior Brand and Visual Designer with over 6 years of experience leading brand creation and visual systems across physical and digital touchpoints. Specialist in translating strategic positioning into cohesive visual identities, campaign design, and design systems within the tech and wearables sector.</t>
+          <t>Education administration professional and law graduate with over a year of experience in compliance, admissions support, and stakeholder coordination. Possesses expertise in contract review, data accuracy, and business engagement with plans to pursue SQE qualifications.</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>6</v>
-      </c>
-      <c r="I8" t="b">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
@@ -9465,7 +9497,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>The candidate's background is entirely in visual design and technology, lacking any relevant UK public health, healthcare training, or Baby Friendly Initiative experience.</t>
+          <t>The candidate lacks the required healthcare practitioner background, infant feeding training experience, and expertise in Baby Friendly Initiative standards.</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -9508,25 +9540,13 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CAND-007</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Freelance Senior Visual Designer</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Senior Visual Designer with over 10 years of experience delivering branding, digital campaigns, web design, and motion graphics across global agencies and brands. Specialises in creative strategy, user interface design, and digital product systems with extensive experience leading design projects across the US, LATAM, and UK.</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>10</v>
-      </c>
-      <c r="I9" t="b">
-        <v>0</v>
-      </c>
+          <t>CAND-005</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
@@ -9537,7 +9557,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>The candidate's background in visual design and branding is completely unrelated to the required public health expertise in infant feeding standards.</t>
+          <t>No candidate background or professional profile is provided to evaluate suitability for this specialised role.</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -9580,23 +9600,25 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CAND-008</t>
+          <t>CAND-006</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lead Digital Designer</t>
+          <t>Lead Visual Artist</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lead Digital Designer with over 18 years of experience directing and executing digital design, motion creative, UI, and branding for global integrated campaigns. Demonstrates strong craft leadership and expertise in managing design teams, brand guardianship, and integrating generative AI tools into creative workflows across consumer, tech, and financial sectors.</t>
+          <t>Senior Brand and Visual Designer with over 6 years of experience leading brand creation and visual systems across physical and digital touchpoints. Specialist in translating strategic positioning into cohesive visual identities, campaign design, and design systems within the tech and wearables sector.</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>18</v>
-      </c>
-      <c r="I10" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="I10" t="b">
+        <v>1</v>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
@@ -9607,7 +9629,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>API timeout</t>
+          <t>The candidate's background in visual design and branding lacks the required healthcare qualifications, infant feeding expertise, and public service experience essential for this role.</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
@@ -9650,13 +9672,25 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CAND-009</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
+          <t>CAND-007</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Freelance Senior Visual Designer</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Senior Visual Designer with over 10 years of experience delivering branding, digital campaigns, web design, and motion graphics across global agencies and brands. Specialises in creative strategy, user interface design, and digital product systems with extensive experience leading design projects across the US, LATAM, and UK.</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>10</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
@@ -9667,7 +9701,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>No candidate profile or work experience details are provided to evaluate suitability for the position.</t>
+          <t>The candidate's background in visual design and creative media bears no relevance to the specialized public health, infant feeding training, and clinical assessment qualifications required for this role.</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
@@ -9710,25 +9744,23 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>SYNTH-002</t>
+          <t>CAND-008</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Digital Delivery Manager</t>
+          <t>Lead Digital Designer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Results-driven Digital Delivery Manager with 7 years delivering agile digital products and online platforms for charity and public sector organisations. Experienced in Scrum, Kanban and SAFe frameworks, managing cross-functional teams of 15+ to deliver user-centred services on time and within budget.</t>
+          <t>Lead Digital Designer with over 18 years of experience directing and executing digital design, motion creative, UI, and branding for global integrated campaigns. Demonstrates strong craft leadership and expertise in managing design teams, brand guardianship, and integrating generative AI tools into creative workflows across consumer, tech, and financial sectors.</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>7</v>
-      </c>
-      <c r="I12" t="b">
-        <v>1</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
@@ -9739,7 +9771,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>The candidate's background in digital delivery and IT management completely lacks the required clinical practitioner experience and expertise in infant feeding standards.</t>
+          <t>The candidate's background in digital design completely lacks the required UK public health experience and infant feeding expertise essential for this role.</t>
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
@@ -9782,25 +9814,13 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SYNTH-003</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Head of Finance Business Partnering</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>CIMA-qualified Head of Finance Business Partnering with 12 years in charity and public sector finance. Expert in management accounting, financial planning &amp; analysis, and strategic finance partnering with senior leadership teams. Experienced in leading finance transformation projects and implementing ERP systems.</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>12</v>
-      </c>
-      <c r="I13" t="b">
-        <v>1</v>
-      </c>
+          <t>CAND-009</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
@@ -9811,7 +9831,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>The candidate's background is entirely in strategic finance and accounting, lacking the required clinical experience and expertise in infant feeding training.</t>
+          <t>No profile or background information is provided to assess the candidate's suitability for this specialized role.</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
@@ -9854,21 +9874,21 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SYNTH-004</t>
+          <t>SYNTH-001</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Head of Internal Audit &amp; Risk</t>
+          <t>Senior Creative Producer (Film &amp; Photography)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>CIIA-qualified Head of Internal Audit and Risk with 11 years in the charity and financial services sectors. Specialist in enterprise risk management (ERM), internal audit delivery, and governance frameworks. Experienced in audit committee reporting, fraud prevention, and regulatory compliance.</t>
+          <t>Award-winning Senior Creative Producer with 9 years specialising in documentary film, charity campaigns, and editorial photography for international NGOs. Proven track record managing end-to-end productions from concept to broadcast, leading cross-functional creative teams and delivering compelling visual storytelling.</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I14" t="b">
         <v>1</v>
@@ -9883,7 +9903,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>The candidate has a background strictly in internal audit and risk management, lacking the required clinical practitioner experience and specialized expertise in infant feeding standards.</t>
+          <t>The candidate's background in creative media production completely lacks the essential healthcare practitioner experience and specialized infant feeding training expertise required for this role.</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
@@ -9926,21 +9946,21 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SYNTH-005</t>
+          <t>SYNTH-002</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Deputy General Counsel</t>
+          <t>Digital Delivery Manager</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Qualified solicitor and Deputy General Counsel with 14 years of in-house and private practice experience in the charity, media, and technology sectors. Expert in commercial contracts, employment law, GDPR/data protection, charity governance, and IP/brand protection. Experienced advising Boards and Trustees.</t>
+          <t>Results-driven Digital Delivery Manager with 7 years delivering agile digital products and online platforms for charity and public sector organisations. Experienced in Scrum, Kanban and SAFe frameworks, managing cross-functional teams of 15+ to deliver user-centred services on time and within budget.</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="I15" t="b">
         <v>1</v>
@@ -9955,7 +9975,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>API timeout</t>
+          <t>The candidate's background in digital delivery management lacks the essential clinical expertise in infant feeding and practical experience implementing Baby Friendly Initiative standards in a healthcare setting.</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
@@ -10027,7 +10047,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>The candidate has a background strictly in procurement and entirely lacks the required clinical practitioner experience and expertise in infant feeding training.</t>
+          <t>The candidate's background in procurement and commercial contract management is completely unrelated to clinical infant feeding standards and health professional training.</t>
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
@@ -10172,7 +10192,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>9.67</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10215,11 +10235,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>The candidate brings 7 years of direct experience as a Digital Delivery Manager within the charity sector, perfectly matching the required skillset and domain background.</t>
+          <t>The candidate has 7 years of direct experience as a Digital Delivery Manager in the charity sector, making them an ideal match for the role.</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -10229,11 +10249,11 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>[10/10] Significant experience delivering complex projects: 7 Jahre Berufserfahrung als Digital Delivery Manager / Produ
-[9/10] Experience working closely with Product Managers a: Führte 4 agile Squads (18 Personen) bei UNICEF UK, coachter 
-[9/10] Strong stakeholder management, planning, and organ: Explizite Skills in Stakeholder Management, Product Roadmapp
-[9/10] Ability to manage competing priorities, build coll: Erfahrung in der Steuerung von 3 konkurrierenden Workstreams
-[10/10] Experience with agile delivery methodologies, cont: Ausgewiesener Experte mit CSM, SAFe 5 Agilist, Agile Deliver</t>
+          <t>[10/10] Significant experience delivering complex projects: 7 Jahre Berufserfahrung als Digital Delivery Manager/Product
+[10/10] Experience working closely with Product Managers a: Führung von 4 multidisziplinären agilen Squads (18 Personen)
+[10/10] Strong stakeholder management, planning, and organ: Nachgewiesene Skills in Stakeholder Management, Risk Managem
+[9/10] Ability to manage competing priorities, build coll: Steuerung von 3 zeitgleichen Product Workstreams bei NSPCC; 
+[10/10] Experience with agile delivery methodologies, cont: Zertifiziert als CSM und SAFe 5 Agilist; fundierte Erfahrung</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -10243,9 +10263,9 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>**Strengths**: Proven track record directly at UNICEF UK leading the digital fundraising platform overhaul (increasing donations by 34%) and managing 4 agile squads (18 people). Brings 7 years of digital delivery experience across charity and public sectors (NSPCC, Cabinet Office) with strong expertise in Scrum, Kanban, and handling competing workstreams.
-**Gaps**: The profile lacks explicit mention of managing User Acceptance Testing (UAT) sign-off processes and specific coordination with external agency partners.
-**Recommendation**: The candidate fully satisfies all essential requirements and brings direct domain experience within UNICEF UK. Highly recommended for an immediate interview.</t>
+          <t>**Strengths**: Directly relevant experience currently leading UNICEF UK's digital fundraising platform overhaul across 4 agile squads (18 people), driving a 34% increase in donations. Possesses 7 years of charity and public sector expertise (NSPCC, GDS), demonstrating strong mastery of Scrum, Kanban, and cross-functional delivery.
+**Gaps**: CV lacks explicit details on coordinating formal UAT readiness/sign-off processes. Motivation for transitioning between internal roles at UNICEF UK should be explored during interview.
+**Recommendation**: An outstanding candidate who fully satisfies all essential requirements with existing UNICEF UK domain knowledge and a proven track record. Highly recommended for immediate interview.</t>
         </is>
       </c>
       <c r="S2" t="inlineStr"/>
@@ -10256,7 +10276,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.7000000000000001</v>
+        <v>1.05</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -10270,24 +10290,24 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CAND-007</t>
+          <t>SYNTH-001</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Freelance Senior Visual Designer</t>
+          <t>Senior Creative Producer (Film &amp; Photography)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Senior Visual Designer with over 10 years of experience delivering branding, digital campaigns, web design, and motion graphics across global agencies and brands. Specialises in creative strategy, user interface design, and digital product systems with extensive experience leading design projects across the US, LATAM, and UK.</t>
+          <t>Award-winning Senior Creative Producer with 9 years specialising in documentary film, charity campaigns, and editorial photography for international NGOs. Proven track record managing end-to-end productions from concept to broadcast, leading cross-functional creative teams and delivering compelling visual storytelling.</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -10295,11 +10315,11 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>The candidate's experience is focused on hands-on visual design and creative execution rather than digital project delivery management and Agile team leadership.</t>
+          <t>While the candidate has relevant charity sector experience, film and creative production management lacks the required background in digital software and tech product delivery.</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
@@ -10342,25 +10362,23 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SYNTH-001</t>
+          <t>CAND-001</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Senior Creative Producer (Film &amp; Photography)</t>
+          <t>Lead Designer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Award-winning Senior Creative Producer with 9 years specialising in documentary film, charity campaigns, and editorial photography for international NGOs. Proven track record managing end-to-end productions from concept to broadcast, leading cross-functional creative teams and delivering compelling visual storytelling.</t>
+          <t>Lead Designer with over 20 years of multi-sector experience building brand identities and leading creative teams across financial services, technology, NGOs, and specialist sectors. Specialist in end-to-end campaign creative direction, design systems, and multi-channel delivery aligned to commercial objectives.</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9</v>
-      </c>
-      <c r="I4" t="b">
-        <v>1</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
@@ -10371,7 +10389,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>While the candidate has valuable charity sector experience, film and photography production lacks the required background in digital technology, software products, and agile delivery methodologies.</t>
+          <t>While the candidate has extensive experience leading creative teams and NGO exposure, a design background lacks the specific agile product delivery and technical project management required for a Delivery Manager role.</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -10414,21 +10432,21 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>SYNTH-003</t>
+          <t>CAND-003</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Head of Finance Business Partnering</t>
+          <t>Senior Designer (Brand Design &amp; UI/UX)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>CIMA-qualified Head of Finance Business Partnering with 12 years in charity and public sector finance. Expert in management accounting, financial planning &amp; analysis, and strategic finance partnering with senior leadership teams. Experienced in leading finance transformation projects and implementing ERP systems.</t>
+          <t>Senior Brand &amp; Visual Designer with 7+ years of experience delivering brand identity, packaging, digital campaigns, and UI/UX design across consumer, B2B, and SaaS sectors. Specialist in multi-brand asset management, print production, AI workflow integration, and high-impact visual communications.</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I5" t="b">
         <v>1</v>
@@ -10443,7 +10461,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>The candidate has a background strictly in finance and accounting, lacking the required experience in digital, technology, or online product delivery.</t>
+          <t>The candidate has a purely creative visual and UI/UX design background without the required hands-on experience in digital delivery management, agile project governance, or operational team leadership.</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -10486,24 +10504,24 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SYNTH-005</t>
+          <t>CAND-007</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Deputy General Counsel</t>
+          <t>Freelance Senior Visual Designer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Qualified solicitor and Deputy General Counsel with 14 years of in-house and private practice experience in the charity, media, and technology sectors. Expert in commercial contracts, employment law, GDPR/data protection, charity governance, and IP/brand protection. Experienced advising Boards and Trustees.</t>
+          <t>Senior Visual Designer with over 10 years of experience delivering branding, digital campaigns, web design, and motion graphics across global agencies and brands. Specialises in creative strategy, user interface design, and digital product systems with extensive experience leading design projects across the US, LATAM, and UK.</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -10515,7 +10533,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Although the candidate has relevant sector experience in charity and technology, their background is strictly legal and governance-focused, lacking the hands-on digital product delivery and Agile project management experience required for this role.</t>
+          <t>While the candidate has strong digital design experience, they lack the hands-on agile project delivery, governance, and delivery management expertise required for this role.</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -10544,7 +10562,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.35</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -10558,21 +10576,21 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CAND-004</t>
+          <t>CAND-008</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Work Placement Officer</t>
+          <t>Lead Digital Designer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Education administration professional and law graduate with over a year of experience in compliance, admissions support, and stakeholder coordination. Possesses expertise in contract review, data accuracy, and business engagement with plans to pursue SQE qualifications.</t>
+          <t>Lead Digital Designer with over 18 years of experience directing and executing digital design, motion creative, UI, and branding for global integrated campaigns. Demonstrates strong craft leadership and expertise in managing design teams, brand guardianship, and integrating generative AI tools into creative workflows across consumer, tech, and financial sectors.</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
@@ -10581,11 +10599,11 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>The candidate lacks the required significant experience in digital product delivery, holding only one year of junior background in education administration and legal compliance.</t>
+          <t>The candidate's background is strictly focused on creative design and brand leadership rather than digital product delivery management and project execution.</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -10614,7 +10632,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.35</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -10628,21 +10646,21 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CAND-006</t>
+          <t>SYNTH-003</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lead Visual Artist</t>
+          <t>Head of Finance Business Partnering</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Senior Brand and Visual Designer with over 6 years of experience leading brand creation and visual systems across physical and digital touchpoints. Specialist in translating strategic positioning into cohesive visual identities, campaign design, and design systems within the tech and wearables sector.</t>
+          <t>CIMA-qualified Head of Finance Business Partnering with 12 years in charity and public sector finance. Expert in management accounting, financial planning &amp; analysis, and strategic finance partnering with senior leadership teams. Experienced in leading finance transformation projects and implementing ERP systems.</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I8" t="b">
         <v>1</v>
@@ -10653,11 +10671,11 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>The candidate's experience is strictly focused on visual design and branding, lacking the necessary digital project management and team delivery capabilities required for this role.</t>
+          <t>The candidate's background is exclusively in strategic finance and FP&amp;A, lacking the essential experience required in digital product delivery and leading multidisciplinary tech teams.</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -10686,7 +10704,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.35</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -10700,21 +10718,21 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>SYNTH-004</t>
+          <t>SYNTH-005</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Head of Internal Audit &amp; Risk</t>
+          <t>Deputy General Counsel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>CIIA-qualified Head of Internal Audit and Risk with 11 years in the charity and financial services sectors. Specialist in enterprise risk management (ERM), internal audit delivery, and governance frameworks. Experienced in audit committee reporting, fraud prevention, and regulatory compliance.</t>
+          <t>Qualified solicitor and Deputy General Counsel with 14 years of in-house and private practice experience in the charity, media, and technology sectors. Expert in commercial contracts, employment law, GDPR/data protection, charity governance, and IP/brand protection. Experienced advising Boards and Trustees.</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I9" t="b">
         <v>1</v>
@@ -10725,11 +10743,11 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>The candidate's background is strictly focused on internal audit, risk, and compliance, lacking any required experience in digital product delivery, technology environments, or agile methodologies.</t>
+          <t>While the candidate possesses relevant sector experience in charity and tech, their background is strictly legal and lacks required hands-on experience in digital project delivery and agile product management.</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -10758,7 +10776,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -10772,34 +10790,36 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CAND-001</t>
+          <t>SYNTH-006</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lead Designer</t>
+          <t>Senior Procurement Manager</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lead Designer with over 20 years of multi-sector experience building brand identities and leading creative teams across financial services, technology, NGOs, and specialist sectors. Specialist in end-to-end campaign creative direction, design systems, and multi-channel delivery aligned to commercial objectives.</t>
+          <t>CIPS-qualified Senior Procurement Manager with 8 years leading procurement functions in charity and public sector organisations. Expert in strategic sourcing, supplier relationship management, and contract management. Delivered £4.5m of savings over 5 years through category management and competitive tendering. Experienced in EU procurement regulations and PCR 2015.</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>23</v>
-      </c>
-      <c r="I10" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="I10" t="b">
+        <v>1</v>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>API timeout</t>
+          <t>The candidate's experience is strictly focused on procurement and contract management, lacking the required digital product delivery and agile environment experience.</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
@@ -10828,7 +10848,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -10842,24 +10862,36 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CAND-002</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
+          <t>CAND-006</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Lead Visual Artist</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Senior Brand and Visual Designer with over 6 years of experience leading brand creation and visual systems across physical and digital touchpoints. Specialist in translating strategic positioning into cohesive visual identities, campaign design, and design systems within the tech and wearables sector.</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>6</v>
+      </c>
+      <c r="I11" t="b">
+        <v>1</v>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>No candidate profile or work experience details are provided to assess suitability for the role.</t>
+          <t>The candidate's profile is strictly focused on creative visual design and brand systems, lacking the necessary digital project management and agile delivery experience required for a Delivery Manager role.</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
@@ -10888,7 +10920,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -10902,21 +10934,21 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CAND-003</t>
+          <t>SYNTH-004</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Senior Designer (Brand Design &amp; UI/UX)</t>
+          <t>Head of Internal Audit &amp; Risk</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Senior Brand &amp; Visual Designer with 7+ years of experience delivering brand identity, packaging, digital campaigns, and UI/UX design across consumer, B2B, and SaaS sectors. Specialist in multi-brand asset management, print production, AI workflow integration, and high-impact visual communications.</t>
+          <t>CIIA-qualified Head of Internal Audit and Risk with 11 years in the charity and financial services sectors. Specialist in enterprise risk management (ERM), internal audit delivery, and governance frameworks. Experienced in audit committee reporting, fraud prevention, and regulatory compliance.</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I12" t="b">
         <v>1</v>
@@ -10927,11 +10959,11 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>API timeout</t>
+          <t>The candidate's profile is strictly focused on internal audit, governance, and risk compliance, lacking any demonstrated experience in digital product delivery or working with tech product teams.</t>
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
@@ -10974,7 +11006,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CAND-005</t>
+          <t>CAND-002</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -10991,7 +11023,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>API timeout</t>
+          <t>No profile or work history is provided to assess suitability for the role.</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
@@ -11034,21 +11066,21 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CAND-008</t>
+          <t>CAND-004</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lead Digital Designer</t>
+          <t>Work Placement Officer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lead Digital Designer with over 18 years of experience directing and executing digital design, motion creative, UI, and branding for global integrated campaigns. Demonstrates strong craft leadership and expertise in managing design teams, brand guardianship, and integrating generative AI tools into creative workflows across consumer, tech, and financial sectors.</t>
+          <t>Education administration professional and law graduate with over a year of experience in compliance, admissions support, and stakeholder coordination. Possesses expertise in contract review, data accuracy, and business engagement with plans to pursue SQE qualifications.</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
@@ -11061,7 +11093,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>API timeout</t>
+          <t>The candidate lacks the required digital and product delivery experience, holding only one year of junior administrative background in the education and legal sectors.</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
@@ -11104,7 +11136,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CAND-009</t>
+          <t>CAND-005</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
@@ -11121,7 +11153,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>No candidate details or work experience were provided to assess suitability for the Delivery Manager role.</t>
+          <t>The candidate profile contains no information or career history to evaluate their suitability for the Delivery Manager role.</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
@@ -11164,25 +11196,13 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>SYNTH-006</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Senior Procurement Manager</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>CIPS-qualified Senior Procurement Manager with 8 years leading procurement functions in charity and public sector organisations. Expert in strategic sourcing, supplier relationship management, and contract management. Delivered £4.5m of savings over 5 years through category management and competitive tendering. Experienced in EU procurement regulations and PCR 2015.</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>8</v>
-      </c>
-      <c r="I16" t="b">
-        <v>1</v>
-      </c>
+          <t>CAND-009</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
@@ -11193,7 +11213,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>API timeout</t>
+          <t>There is no profile or experience information provided to evaluate the candidate's suitability for the Delivery Manager role.</t>
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
@@ -11222,7 +11242,7 @@
         <v>1</v>
       </c>
       <c r="B17" t="n">
-        <v>7.681</v>
+        <v>7.94</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -11265,11 +11285,11 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>With 14 years of legal experience, direct charity governance background, and current Deputy General Counsel standing, this candidate represents a highly logical and strong progression into the General Counsel role.</t>
+          <t>The candidate has 14 years of legal experience, currently serves as Deputy General Counsel, and possesses direct expertise in charity governance and board advisory, making this an ideal step-up for the General Counsel role at UNICEF UK.</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>6.33</v>
+        <v>6.8</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -11278,16 +11298,16 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Kein Nachweis über einen durchgeführten oder erfolgreichen Criminal Records Check (DBS Check) im Profil., Fehlende finale Gesamtverantwortung als General Counsel (bisher 'Second-in-command' als Deputy General Counsel).</t>
+          <t>Kein Nachweis über eine erfolgte Überprüfung des Strafregisters (Criminal Records Check / DBS Check) im Profil vorhanden., Bisher noch keine Erstverantwortung als Gesamtleiter / General Counsel (bislang Deputy General Counsel).</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>[7/10] Significant senior-level experience leading legal : 14 Jahre Berufserfahrung, aktuell Deputy General Counsel bei
-[8/10] Track record of supporting executive and board-lev: Skills in Board Secretariat und Board-Level Communication so
-[9/10] Strong commercial acumen combined with sound judge: Erfahrung bei Clifford Chance (M&amp;A/JVs für FTSE 100), Verhan
-[7/10] Ability to balance legal risk with organisational : Nachgewiesene Skills in Strategic Legal Advice, Risk Managem
-[7/10] Influential and collaborative leadership skills, a: Leitung eines Teams aus 4 Anwälten und 2 Paralegals bei WWF-</t>
+          <t xml:space="preserve">[8/10] Significant senior-level experience leading legal : 14 Berufsjahre; aktuell Deputy General Counsel bei WWF-UK (S
+[8/10] Track record of supporting executive and board-lev: Nachgewiesene Skills in 'Board-Level Communication', 'Strate
+[9/10] Strong commercial acumen combined with sound judge: Umfangreiche kommerzielle Erfahrung: Verhandlung von £50m+ V
+[8/10] Ability to balance legal risk with organisational : Fähigkeiten in 'Strategic Legal Advice' und 'Risk Management
+[8/10] Influential and collaborative leadership skills, a: Führungserfahrung als Deputy General Counsel bei WWF-UK mit </t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -11297,9 +11317,9 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>**Strengths**: Directly relevant charity governance and team leadership experience as Deputy General Counsel at WWF-UK (managing 6 staff and advising the Board), backed by top-tier commercial expertise from Clifford Chance and Channel 4 (£50m+ negotiations).
-**Gaps**: Represents a step-up from 'second-in-command' to ultimate General Counsel accountability; no explicit record of a criminal records check (DBS) provided in the profile.
-**Recommendation**: An outstanding candidate combining elite commercial training with directly transferable charity leadership. Recommend interviewing to assess readiness for top-level GC ownership and verifying DBS status.</t>
+          <t>**Strengths**: 14 years' legal experience, including direct sector leadership as Deputy General Counsel at WWF-UK managing a 6-person team and advising Trustees. Exceptional commercial acumen backed by Magic Circle training (Clifford Chance) and managing £50m+ contracts at Channel 4.
+**Gaps**: Seeking a step-up to full General Counsel level (currently second-in-command). No current evidence of a completed criminal records check in profile.
+**Recommendation**: Highly qualified candidate offering an ideal blend of top-tier commercial rigor and proven charity governance experience. Highly recommended for interview, subject to verifying criminal records check status.</t>
         </is>
       </c>
       <c r="S17" t="inlineStr"/>
@@ -11353,7 +11373,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>While the candidate has relevant charity sector and governance experience, they lack the required professional legal qualifications and practicing background essential for a General Counsel role.</t>
+          <t>While the candidate has relevant charity sector and governance experience, they lack the legal qualifications and formal legal practice background required for a General Counsel position.</t>
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
@@ -11425,7 +11445,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>The candidate has a finance background (CIMA), whereas a General Counsel position strictly requires a qualified legal professional with extensive legal and governance experience.</t>
+          <t>The candidate has a background in finance and accounting rather than the required legal qualifications and legal leadership experience needed for a General Counsel role.</t>
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
@@ -11454,7 +11474,7 @@
         <v>4</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -11468,34 +11488,36 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CAND-001</t>
+          <t>SYNTH-006</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lead Designer</t>
+          <t>Senior Procurement Manager</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lead Designer with over 20 years of multi-sector experience building brand identities and leading creative teams across financial services, technology, NGOs, and specialist sectors. Specialist in end-to-end campaign creative direction, design systems, and multi-channel delivery aligned to commercial objectives.</t>
+          <t>CIPS-qualified Senior Procurement Manager with 8 years leading procurement functions in charity and public sector organisations. Expert in strategic sourcing, supplier relationship management, and contract management. Delivered £4.5m of savings over 5 years through category management and competitive tendering. Experienced in EU procurement regulations and PCR 2015.</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>23</v>
-      </c>
-      <c r="I20" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="I20" t="b">
+        <v>1</v>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>The candidate has a creative background in design and brand identity, completely lacking the requisite legal qualifications and governance leadership experience required for a General Counsel position.</t>
+          <t>The candidate is a procurement specialist and lacks the essential legal qualifications and senior legal leadership experience required for a General Counsel role.</t>
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
@@ -11538,12 +11560,22 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CAND-002</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+          <t>CAND-001</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Lead Designer</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lead Designer with over 20 years of multi-sector experience building brand identities and leading creative teams across financial services, technology, NGOs, and specialist sectors. Specialist in end-to-end campaign creative direction, design systems, and multi-channel delivery aligned to commercial objectives.</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>23</v>
+      </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
@@ -11555,7 +11587,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>No candidate profile, experience, or career history is provided to evaluate suitability for the General Counsel role.</t>
+          <t>The candidate's background is exclusively in creative design and brand direction, lacking the legal qualifications and governance experience required for a General Counsel role.</t>
         </is>
       </c>
       <c r="M21" t="inlineStr"/>
@@ -11598,25 +11630,13 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>CAND-003</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Senior Designer (Brand Design &amp; UI/UX)</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Senior Brand &amp; Visual Designer with 7+ years of experience delivering brand identity, packaging, digital campaigns, and UI/UX design across consumer, B2B, and SaaS sectors. Specialist in multi-brand asset management, print production, AI workflow integration, and high-impact visual communications.</t>
-        </is>
-      </c>
-      <c r="H22" t="n">
-        <v>7</v>
-      </c>
-      <c r="I22" t="b">
-        <v>1</v>
-      </c>
+          <t>CAND-002</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
@@ -11627,7 +11647,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>The candidate's background in visual and brand design is completely unrelated to the senior legal, compliance, and governance requirements of a General Counsel role.</t>
+          <t>No profile or professional experience details are provided to evaluate the candidate's suitability for a senior legal leadership role.</t>
         </is>
       </c>
       <c r="M22" t="inlineStr"/>
@@ -11670,23 +11690,25 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>CAND-004</t>
+          <t>CAND-003</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Work Placement Officer</t>
+          <t>Senior Designer (Brand Design &amp; UI/UX)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Education administration professional and law graduate with over a year of experience in compliance, admissions support, and stakeholder coordination. Possesses expertise in contract review, data accuracy, and business engagement with plans to pursue SQE qualifications.</t>
+          <t>Senior Brand &amp; Visual Designer with 7+ years of experience delivering brand identity, packaging, digital campaigns, and UI/UX design across consumer, B2B, and SaaS sectors. Specialist in multi-brand asset management, print production, AI workflow integration, and high-impact visual communications.</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
-      </c>
-      <c r="I23" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="I23" t="b">
+        <v>1</v>
+      </c>
       <c r="J23" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
@@ -11697,7 +11719,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>API timeout</t>
+          <t>The candidate's background is entirely in visual design and UI/UX, lacking the required legal qualifications and senior governance experience necessary for a General Counsel role.</t>
         </is>
       </c>
       <c r="M23" t="inlineStr"/>
@@ -11740,12 +11762,22 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CAND-005</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
+          <t>CAND-004</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Work Placement Officer</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Education administration professional and law graduate with over a year of experience in compliance, admissions support, and stakeholder coordination. Possesses expertise in contract review, data accuracy, and business engagement with plans to pursue SQE qualifications.</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
@@ -11757,7 +11789,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>No candidate profile or experience details are provided to assess suitability for the role.</t>
+          <t>The candidate is an entry-level professional who is not yet a qualified lawyer, making them completely unsuitable for a senior executive General Counsel position.</t>
         </is>
       </c>
       <c r="M24" t="inlineStr"/>
@@ -11800,25 +11832,13 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>CAND-006</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Lead Visual Artist</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Senior Brand and Visual Designer with over 6 years of experience leading brand creation and visual systems across physical and digital touchpoints. Specialist in translating strategic positioning into cohesive visual identities, campaign design, and design systems within the tech and wearables sector.</t>
-        </is>
-      </c>
-      <c r="H25" t="n">
-        <v>6</v>
-      </c>
-      <c r="I25" t="b">
-        <v>1</v>
-      </c>
+          <t>CAND-005</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
@@ -11829,7 +11849,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>API timeout</t>
+          <t>There is no information provided about the candidate's background, experience, or qualifications to assess suitability for the General Counsel role.</t>
         </is>
       </c>
       <c r="M25" t="inlineStr"/>
@@ -11872,24 +11892,24 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CAND-007</t>
+          <t>CAND-006</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Freelance Senior Visual Designer</t>
+          <t>Lead Visual Artist</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Senior Visual Designer with over 10 years of experience delivering branding, digital campaigns, web design, and motion graphics across global agencies and brands. Specialises in creative strategy, user interface design, and digital product systems with extensive experience leading design projects across the US, LATAM, and UK.</t>
+          <t>Senior Brand and Visual Designer with over 6 years of experience leading brand creation and visual systems across physical and digital touchpoints. Specialist in translating strategic positioning into cohesive visual identities, campaign design, and design systems within the tech and wearables sector.</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -11901,7 +11921,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>The candidate's background is entirely in visual design and creative strategy, with no qualifications or experience in legal affairs or executive governance required for a General Counsel role.</t>
+          <t>The candidate's background in visual design lacks the required legal qualifications and executive governance experience necessary for a General Counsel role.</t>
         </is>
       </c>
       <c r="M26" t="inlineStr"/>
@@ -11944,23 +11964,25 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CAND-008</t>
+          <t>CAND-007</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lead Digital Designer</t>
+          <t>Freelance Senior Visual Designer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lead Digital Designer with over 18 years of experience directing and executing digital design, motion creative, UI, and branding for global integrated campaigns. Demonstrates strong craft leadership and expertise in managing design teams, brand guardianship, and integrating generative AI tools into creative workflows across consumer, tech, and financial sectors.</t>
+          <t>Senior Visual Designer with over 10 years of experience delivering branding, digital campaigns, web design, and motion graphics across global agencies and brands. Specialises in creative strategy, user interface design, and digital product systems with extensive experience leading design projects across the US, LATAM, and UK.</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>18</v>
-      </c>
-      <c r="I27" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="I27" t="b">
+        <v>0</v>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
@@ -11971,7 +11993,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>API timeout</t>
+          <t>The candidate's background is entirely in visual design, lacking the required legal qualifications, governance expertise, and senior legal leadership experience for a General Counsel role.</t>
         </is>
       </c>
       <c r="M27" t="inlineStr"/>
@@ -12014,12 +12036,22 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>CAND-009</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+          <t>CAND-008</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Lead Digital Designer</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Lead Digital Designer with over 18 years of experience directing and executing digital design, motion creative, UI, and branding for global integrated campaigns. Demonstrates strong craft leadership and expertise in managing design teams, brand guardianship, and integrating generative AI tools into creative workflows across consumer, tech, and financial sectors.</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>18</v>
+      </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
@@ -12031,7 +12063,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>No candidate profile or career history is available to assess suitability for this senior legal role.</t>
+          <t>The candidate has a background entirely in digital design and creative leadership with no relevant experience in legal or governance functions required for a General Counsel role.</t>
         </is>
       </c>
       <c r="M28" t="inlineStr"/>
@@ -12074,25 +12106,13 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>SYNTH-001</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Senior Creative Producer (Film &amp; Photography)</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Award-winning Senior Creative Producer with 9 years specialising in documentary film, charity campaigns, and editorial photography for international NGOs. Proven track record managing end-to-end productions from concept to broadcast, leading cross-functional creative teams and delivering compelling visual storytelling.</t>
-        </is>
-      </c>
-      <c r="H29" t="n">
-        <v>9</v>
-      </c>
-      <c r="I29" t="b">
-        <v>1</v>
-      </c>
+          <t>CAND-009</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
@@ -12103,7 +12123,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>The candidate's background in creative production lacks the required legal qualifications and senior governance experience necessary for a General Counsel role.</t>
+          <t>No profile or professional background details are provided to evaluate the candidate's suitability for the General Counsel role.</t>
         </is>
       </c>
       <c r="M29" t="inlineStr"/>
@@ -12146,21 +12166,21 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>SYNTH-002</t>
+          <t>SYNTH-001</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Digital Delivery Manager</t>
+          <t>Senior Creative Producer (Film &amp; Photography)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Results-driven Digital Delivery Manager with 7 years delivering agile digital products and online platforms for charity and public sector organisations. Experienced in Scrum, Kanban and SAFe frameworks, managing cross-functional teams of 15+ to deliver user-centred services on time and within budget.</t>
+          <t>Award-winning Senior Creative Producer with 9 years specialising in documentary film, charity campaigns, and editorial photography for international NGOs. Proven track record managing end-to-end productions from concept to broadcast, leading cross-functional creative teams and delivering compelling visual storytelling.</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I30" t="b">
         <v>1</v>
@@ -12175,7 +12195,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>API timeout</t>
+          <t>The candidate has a background in creative media production and completely lacks the legal qualifications, legal leadership, and governance experience required for a General Counsel position.</t>
         </is>
       </c>
       <c r="M30" t="inlineStr"/>
@@ -12218,21 +12238,21 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>SYNTH-006</t>
+          <t>SYNTH-002</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Senior Procurement Manager</t>
+          <t>Digital Delivery Manager</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>CIPS-qualified Senior Procurement Manager with 8 years leading procurement functions in charity and public sector organisations. Expert in strategic sourcing, supplier relationship management, and contract management. Delivered £4.5m of savings over 5 years through category management and competitive tendering. Experienced in EU procurement regulations and PCR 2015.</t>
+          <t>Results-driven Digital Delivery Manager with 7 years delivering agile digital products and online platforms for charity and public sector organisations. Experienced in Scrum, Kanban and SAFe frameworks, managing cross-functional teams of 15+ to deliver user-centred services on time and within budget.</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I31" t="b">
         <v>1</v>
@@ -12247,7 +12267,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>API timeout</t>
+          <t>The candidate has a background in digital product management and lacks the required legal qualifications and senior legal leadership experience for a General Counsel role.</t>
         </is>
       </c>
       <c r="M31" t="inlineStr"/>
@@ -12276,7 +12296,7 @@
         <v>1</v>
       </c>
       <c r="B32" t="n">
-        <v>3.5</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -12319,27 +12339,43 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>The candidate holds the exact matching job title, CIIA qualification, and direct charity sector experience required for this role.</t>
+          <t>The candidate has the exact matching job title, a CIIA qualification, and 11 years of directly transferable enterprise risk and audit experience within the charity sector.</t>
         </is>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0/6 Anforderungen</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
+          <t>5/6 Anforderungen</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Fehlender Beleg/Nachweis bezüglich eines Criminal Records Checks (z.B. DBS Check in UK)</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[9/10] Experienced risk or audit professional with a stro: 11 Jahre Berufserfahrung; aktuell Head of Internal Audit &amp; R
+[8/10] Excellent analytical and communication skills: CV führt 'Data Analytics for Audit', 'Critical Thinking' und
+[9/10] Ability to challenge and influence senior stakehol: Nachgewiesene Berichterstattung an Audit Committees bei Macm
+[9/10] Strong understanding of risk, assurance, and gover: Umfassende Kenntnisse in ISO 31000, Control Framework Design
+[8/10] Commitment to integrity and continuous improvement: Soft Skills nennen explizit 'Integrity' sowie 'Independence </t>
+        </is>
+      </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Strong Match</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>(failed: )</t>
+          <t>**Strengths**: • CIIA-qualified with 11 years of relevant experience, currently serving as Head of Internal Audit &amp; Risk at Macmillan Cancer Support.
+• Proven track record of board-level stakeholder engagement, regularly presenting to Audit &amp; Risk Committees across the Charity, NHS, and Financial Services sectors.
+• Deep expertise in governance and risk frameworks (ISO 31000), backed by measurable delivery such as achieving a 40% reduction in critical cyber risk at Macmillan.
+**Gaps**: • Missing explicit confirmation/evidence of a successful criminal records check (DBS check).
+**Recommendation**: The candidate brings direct charity-sector head level leadership and technical excellence perfectly aligned with UNICEF UK's core requirements. I strongly recommend progressing to interview, subject to standard DBS verification.</t>
         </is>
       </c>
       <c r="S32" t="inlineStr"/>
@@ -12350,7 +12386,7 @@
         <v>2</v>
       </c>
       <c r="B33" t="n">
-        <v>0.7000000000000001</v>
+        <v>1.4</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -12364,21 +12400,21 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>SYNTH-006</t>
+          <t>SYNTH-003</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Senior Procurement Manager</t>
+          <t>Head of Finance Business Partnering</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>CIPS-qualified Senior Procurement Manager with 8 years leading procurement functions in charity and public sector organisations. Expert in strategic sourcing, supplier relationship management, and contract management. Delivered £4.5m of savings over 5 years through category management and competitive tendering. Experienced in EU procurement regulations and PCR 2015.</t>
+          <t>CIMA-qualified Head of Finance Business Partnering with 12 years in charity and public sector finance. Expert in management accounting, financial planning &amp; analysis, and strategic finance partnering with senior leadership teams. Experienced in leading finance transformation projects and implementing ERP systems.</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I33" t="b">
         <v>1</v>
@@ -12389,11 +12425,11 @@
         </is>
       </c>
       <c r="K33" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>The candidate's background is exclusively in procurement and contract management, lacking the required professional qualifications and direct experience in enterprise risk management and internal audit.</t>
+          <t>While the candidate has strong senior charity sector finance experience, they lack the specific track record in internal audit and enterprise risk management required for this role.</t>
         </is>
       </c>
       <c r="M33" t="inlineStr"/>
@@ -12422,7 +12458,7 @@
         <v>3</v>
       </c>
       <c r="B34" t="n">
-        <v>0.35</v>
+        <v>1.05</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -12436,21 +12472,21 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>SYNTH-002</t>
+          <t>SYNTH-005</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Digital Delivery Manager</t>
+          <t>Deputy General Counsel</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Results-driven Digital Delivery Manager with 7 years delivering agile digital products and online platforms for charity and public sector organisations. Experienced in Scrum, Kanban and SAFe frameworks, managing cross-functional teams of 15+ to deliver user-centred services on time and within budget.</t>
+          <t>Qualified solicitor and Deputy General Counsel with 14 years of in-house and private practice experience in the charity, media, and technology sectors. Expert in commercial contracts, employment law, GDPR/data protection, charity governance, and IP/brand protection. Experienced advising Boards and Trustees.</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="I34" t="b">
         <v>1</v>
@@ -12461,11 +12497,11 @@
         </is>
       </c>
       <c r="K34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>The candidate's background is exclusively in Agile digital product delivery, lacking the essential expertise in enterprise risk management, governance, and internal audit required for this senior leadership position.</t>
+          <t>While the candidate has strong charity governance and Board experience, a legal background as a Deputy General Counsel lacks the dedicated internal audit and enterprise risk management expertise required for this role.</t>
         </is>
       </c>
       <c r="M34" t="inlineStr"/>
@@ -12494,7 +12530,7 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>0</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -12508,34 +12544,36 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>CAND-001</t>
+          <t>SYNTH-006</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lead Designer</t>
+          <t>Senior Procurement Manager</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lead Designer with over 20 years of multi-sector experience building brand identities and leading creative teams across financial services, technology, NGOs, and specialist sectors. Specialist in end-to-end campaign creative direction, design systems, and multi-channel delivery aligned to commercial objectives.</t>
+          <t>CIPS-qualified Senior Procurement Manager with 8 years leading procurement functions in charity and public sector organisations. Expert in strategic sourcing, supplier relationship management, and contract management. Delivered £4.5m of savings over 5 years through category management and competitive tendering. Experienced in EU procurement regulations and PCR 2015.</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>23</v>
-      </c>
-      <c r="I35" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="I35" t="b">
+        <v>1</v>
+      </c>
       <c r="J35" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>The candidate's background is entirely in creative design and branding, lacking any experience in risk management or internal audit required for this role.</t>
+          <t>While the candidate has relevant charity sector experience, procurement is a completely different functional domain from enterprise risk management and internal audit.</t>
         </is>
       </c>
       <c r="M35" t="inlineStr"/>
@@ -12564,7 +12602,7 @@
         <v>5</v>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -12578,24 +12616,36 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>CAND-002</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
+          <t>SYNTH-002</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Digital Delivery Manager</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Results-driven Digital Delivery Manager with 7 years delivering agile digital products and online platforms for charity and public sector organisations. Experienced in Scrum, Kanban and SAFe frameworks, managing cross-functional teams of 15+ to deliver user-centred services on time and within budget.</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>7</v>
+      </c>
+      <c r="I36" t="b">
+        <v>1</v>
+      </c>
       <c r="J36" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>API timeout</t>
+          <t>The candidate's background is entirely in digital product delivery and agile project management, lacking any specialized experience in enterprise risk management or internal audit.</t>
         </is>
       </c>
       <c r="M36" t="inlineStr"/>
@@ -12638,25 +12688,23 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>CAND-003</t>
+          <t>CAND-001</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Senior Designer (Brand Design &amp; UI/UX)</t>
+          <t>Lead Designer</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Senior Brand &amp; Visual Designer with 7+ years of experience delivering brand identity, packaging, digital campaigns, and UI/UX design across consumer, B2B, and SaaS sectors. Specialist in multi-brand asset management, print production, AI workflow integration, and high-impact visual communications.</t>
+          <t>Lead Designer with over 20 years of multi-sector experience building brand identities and leading creative teams across financial services, technology, NGOs, and specialist sectors. Specialist in end-to-end campaign creative direction, design systems, and multi-channel delivery aligned to commercial objectives.</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>7</v>
-      </c>
-      <c r="I37" t="b">
-        <v>1</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
@@ -12667,7 +12715,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>The candidate's background in graphic design and UI/UX has no relevance to enterprise risk management or internal audit.</t>
+          <t>The candidate's background is entirely in creative design and branding, with no relevant experience in enterprise risk management or internal audit.</t>
         </is>
       </c>
       <c r="M37" t="inlineStr"/>
@@ -12710,22 +12758,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>CAND-004</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Work Placement Officer</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Education administration professional and law graduate with over a year of experience in compliance, admissions support, and stakeholder coordination. Possesses expertise in contract review, data accuracy, and business engagement with plans to pursue SQE qualifications.</t>
-        </is>
-      </c>
-      <c r="H38" t="n">
-        <v>1</v>
-      </c>
+          <t>CAND-002</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
@@ -12737,7 +12775,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>The candidate has only one year of junior entry-level experience in education administration, making them completely unqualified for a senior Head of Risk and Internal Audit role requiring extensive leadership and enterprise risk management experience.</t>
+          <t>No information regarding the candidate's professional background, experience, or qualifications is available to assess suitability for the role.</t>
         </is>
       </c>
       <c r="M38" t="inlineStr"/>
@@ -12780,13 +12818,25 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>CAND-005</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
+          <t>CAND-003</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Senior Designer (Brand Design &amp; UI/UX)</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Senior Brand &amp; Visual Designer with 7+ years of experience delivering brand identity, packaging, digital campaigns, and UI/UX design across consumer, B2B, and SaaS sectors. Specialist in multi-brand asset management, print production, AI workflow integration, and high-impact visual communications.</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>7</v>
+      </c>
+      <c r="I39" t="b">
+        <v>1</v>
+      </c>
       <c r="J39" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
@@ -12797,7 +12847,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>API timeout</t>
+          <t>The candidate's background in creative brand design and UI/UX is completely unrelated to enterprise risk management and internal audit.</t>
         </is>
       </c>
       <c r="M39" t="inlineStr"/>
@@ -12840,25 +12890,23 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>CAND-006</t>
+          <t>CAND-004</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lead Visual Artist</t>
+          <t>Work Placement Officer</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Senior Brand and Visual Designer with over 6 years of experience leading brand creation and visual systems across physical and digital touchpoints. Specialist in translating strategic positioning into cohesive visual identities, campaign design, and design systems within the tech and wearables sector.</t>
+          <t>Education administration professional and law graduate with over a year of experience in compliance, admissions support, and stakeholder coordination. Possesses expertise in contract review, data accuracy, and business engagement with plans to pursue SQE qualifications.</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>6</v>
-      </c>
-      <c r="I40" t="b">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
@@ -12869,7 +12917,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>The candidate has a background entirely focused on visual design and branding with zero experience in risk management, internal audit, or governance.</t>
+          <t>The candidate is a junior education administrator with only one year of experience, lacking the extensive senior leadership and specialised enterprise risk management background required for a Head of Department role.</t>
         </is>
       </c>
       <c r="M40" t="inlineStr"/>
@@ -12912,25 +12960,13 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>CAND-007</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Freelance Senior Visual Designer</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Senior Visual Designer with over 10 years of experience delivering branding, digital campaigns, web design, and motion graphics across global agencies and brands. Specialises in creative strategy, user interface design, and digital product systems with extensive experience leading design projects across the US, LATAM, and UK.</t>
-        </is>
-      </c>
-      <c r="H41" t="n">
-        <v>10</v>
-      </c>
-      <c r="I41" t="b">
-        <v>0</v>
-      </c>
+          <t>CAND-005</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
@@ -12941,7 +12977,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>API timeout</t>
+          <t>The candidate profile contains no background information or relevant experience to assess suitability for this role.</t>
         </is>
       </c>
       <c r="M41" t="inlineStr"/>
@@ -12984,23 +13020,25 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>CAND-008</t>
+          <t>CAND-006</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lead Digital Designer</t>
+          <t>Lead Visual Artist</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lead Digital Designer with over 18 years of experience directing and executing digital design, motion creative, UI, and branding for global integrated campaigns. Demonstrates strong craft leadership and expertise in managing design teams, brand guardianship, and integrating generative AI tools into creative workflows across consumer, tech, and financial sectors.</t>
+          <t>Senior Brand and Visual Designer with over 6 years of experience leading brand creation and visual systems across physical and digital touchpoints. Specialist in translating strategic positioning into cohesive visual identities, campaign design, and design systems within the tech and wearables sector.</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>18</v>
-      </c>
-      <c r="I42" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="I42" t="b">
+        <v>1</v>
+      </c>
       <c r="J42" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
@@ -13011,7 +13049,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>API timeout</t>
+          <t>The candidate's experience is exclusively in visual design and branding, with no background or qualifications in enterprise risk management or internal audit.</t>
         </is>
       </c>
       <c r="M42" t="inlineStr"/>
@@ -13054,13 +13092,25 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>CAND-009</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
+          <t>CAND-007</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Freelance Senior Visual Designer</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Senior Visual Designer with over 10 years of experience delivering branding, digital campaigns, web design, and motion graphics across global agencies and brands. Specialises in creative strategy, user interface design, and digital product systems with extensive experience leading design projects across the US, LATAM, and UK.</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>10</v>
+      </c>
+      <c r="I43" t="b">
+        <v>0</v>
+      </c>
       <c r="J43" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
@@ -13071,7 +13121,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>The candidate profile lacks any employment history or qualifications, making it impossible to determine suitability for a senior risk and audit role.</t>
+          <t>The candidate's background in visual design and creative direction bears no relevance to enterprise risk management or internal audit functions.</t>
         </is>
       </c>
       <c r="M43" t="inlineStr"/>
@@ -13114,25 +13164,23 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>SYNTH-001</t>
+          <t>CAND-008</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Senior Creative Producer (Film &amp; Photography)</t>
+          <t>Lead Digital Designer</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Award-winning Senior Creative Producer with 9 years specialising in documentary film, charity campaigns, and editorial photography for international NGOs. Proven track record managing end-to-end productions from concept to broadcast, leading cross-functional creative teams and delivering compelling visual storytelling.</t>
+          <t>Lead Digital Designer with over 18 years of experience directing and executing digital design, motion creative, UI, and branding for global integrated campaigns. Demonstrates strong craft leadership and expertise in managing design teams, brand guardianship, and integrating generative AI tools into creative workflows across consumer, tech, and financial sectors.</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>9</v>
-      </c>
-      <c r="I44" t="b">
-        <v>1</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
@@ -13143,7 +13191,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>The candidate's background in creative production and media lacks the specialized expertise in enterprise risk management and internal auditing required for this senior leadership role.</t>
+          <t>The candidate's background is entirely in digital design and creative direction, lacking any relevant experience in enterprise risk management or internal audit.</t>
         </is>
       </c>
       <c r="M44" t="inlineStr"/>
@@ -13186,25 +13234,13 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>SYNTH-003</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Head of Finance Business Partnering</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>CIMA-qualified Head of Finance Business Partnering with 12 years in charity and public sector finance. Expert in management accounting, financial planning &amp; analysis, and strategic finance partnering with senior leadership teams. Experienced in leading finance transformation projects and implementing ERP systems.</t>
-        </is>
-      </c>
-      <c r="H45" t="n">
-        <v>12</v>
-      </c>
-      <c r="I45" t="b">
-        <v>1</v>
-      </c>
+          <t>CAND-009</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
@@ -13215,7 +13251,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>API timeout</t>
+          <t>The candidate profile lacks any background, experience, or job history details to evaluate suitability for the role.</t>
         </is>
       </c>
       <c r="M45" t="inlineStr"/>
@@ -13258,21 +13294,21 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>SYNTH-005</t>
+          <t>SYNTH-001</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Deputy General Counsel</t>
+          <t>Senior Creative Producer (Film &amp; Photography)</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Qualified solicitor and Deputy General Counsel with 14 years of in-house and private practice experience in the charity, media, and technology sectors. Expert in commercial contracts, employment law, GDPR/data protection, charity governance, and IP/brand protection. Experienced advising Boards and Trustees.</t>
+          <t>Award-winning Senior Creative Producer with 9 years specialising in documentary film, charity campaigns, and editorial photography for international NGOs. Proven track record managing end-to-end productions from concept to broadcast, leading cross-functional creative teams and delivering compelling visual storytelling.</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I46" t="b">
         <v>1</v>
@@ -13287,7 +13323,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>API timeout</t>
+          <t>The candidate's experience is entirely within creative media production and lacks the necessary background in risk management, internal audit, or governance.</t>
         </is>
       </c>
       <c r="M46" t="inlineStr"/>
@@ -13316,7 +13352,7 @@
         <v>1</v>
       </c>
       <c r="B47" t="n">
-        <v>1.05</v>
+        <v>7.931</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -13330,54 +13366,68 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>SYNTH-004</t>
+          <t>SYNTH-003</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Head of Internal Audit &amp; Risk</t>
+          <t>Head of Finance Business Partnering</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>CIIA-qualified Head of Internal Audit and Risk with 11 years in the charity and financial services sectors. Specialist in enterprise risk management (ERM), internal audit delivery, and governance frameworks. Experienced in audit committee reporting, fraud prevention, and regulatory compliance.</t>
+          <t>CIMA-qualified Head of Finance Business Partnering with 12 years in charity and public sector finance. Expert in management accounting, financial planning &amp; analysis, and strategic finance partnering with senior leadership teams. Experienced in leading finance transformation projects and implementing ERP systems.</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I47" t="b">
         <v>1</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>✗ NEIN</t>
+          <t>✓ JA</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Internal audit and risk management experience does not provide the required track record in FP&amp;A and strategic finance business partnering needed for an interim leadership role.</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr"/>
+          <t>The candidate is a direct title match with 12 years of CIMA-qualified experience specifically within the charity sector.</t>
+        </is>
+      </c>
+      <c r="M47" t="n">
+        <v>7.33</v>
+      </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>None/None Anforderungen</t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
+          <t>2/3 Anforderungen</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Fehlender konkreter Nachweis über Business Partnering mit einkommensgenerierenden Teams / Fundraising</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>[10/10] Experience successfully managing a similar Finance: Head of Finance Business Partnering bei British Red Cross: F
+[5/10] Track record in effective partnering with income-g: Business Partnering für 12 Direktorate (British Red Cross) s
+[7/10] Track record in building a high-performing team th: Leitung von 6 FBPs bei British Red Cross und Erzielung von 2</t>
+        </is>
+      </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>(nicht analysiert — nicht in Top 5)</t>
+          <t>Possible Match</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>(nicht analysiert)</t>
+          <t>**Strengths**: Proven track record as Head of Finance Business Partnering at British Red Cross, successfully leading a team of 6 FBPs across 12 directorates. Strong FP&amp;A credentials, delivering £2m cost savings via zero-based budgeting and cutting budget cycles by 40% using Adaptive Insights. CIMA-qualified with 12 years of dedicated UK charity and public sector experience.
+**Gaps**: Lacks explicit evidence of partnering directly with income-generating or fundraising teams, which is a key requirement for this role.
+**Recommendation**: Strong functional and sector fit with direct leadership experience in a major UK charity. Recommended for initial interview to probe experience supporting income-generation streams.</t>
         </is>
       </c>
       <c r="S47" t="inlineStr"/>
@@ -13388,7 +13438,7 @@
         <v>2</v>
       </c>
       <c r="B48" t="n">
-        <v>0.35</v>
+        <v>1.05</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -13402,21 +13452,21 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>SYNTH-006</t>
+          <t>SYNTH-004</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Senior Procurement Manager</t>
+          <t>Head of Internal Audit &amp; Risk</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>CIPS-qualified Senior Procurement Manager with 8 years leading procurement functions in charity and public sector organisations. Expert in strategic sourcing, supplier relationship management, and contract management. Delivered £4.5m of savings over 5 years through category management and competitive tendering. Experienced in EU procurement regulations and PCR 2015.</t>
+          <t>CIIA-qualified Head of Internal Audit and Risk with 11 years in the charity and financial services sectors. Specialist in enterprise risk management (ERM), internal audit delivery, and governance frameworks. Experienced in audit committee reporting, fraud prevention, and regulatory compliance.</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I48" t="b">
         <v>1</v>
@@ -13427,11 +13477,11 @@
         </is>
       </c>
       <c r="K48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Although the candidate has charity sector experience, a background in procurement lacks the essential professional accounting qualifications and FP&amp;A leadership expertise required for this finance role.</t>
+          <t>While the candidate has valuable charity sector experience, an Internal Audit and Risk background lacks the commercial FP&amp;A and direct finance business partnering leadership required for this senior interim role.</t>
         </is>
       </c>
       <c r="M48" t="inlineStr"/>
@@ -13460,7 +13510,7 @@
         <v>3</v>
       </c>
       <c r="B49" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -13474,34 +13524,36 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>CAND-001</t>
+          <t>SYNTH-002</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lead Designer</t>
+          <t>Digital Delivery Manager</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lead Designer with over 20 years of multi-sector experience building brand identities and leading creative teams across financial services, technology, NGOs, and specialist sectors. Specialist in end-to-end campaign creative direction, design systems, and multi-channel delivery aligned to commercial objectives.</t>
+          <t>Results-driven Digital Delivery Manager with 7 years delivering agile digital products and online platforms for charity and public sector organisations. Experienced in Scrum, Kanban and SAFe frameworks, managing cross-functional teams of 15+ to deliver user-centred services on time and within budget.</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>23</v>
-      </c>
-      <c r="I49" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="I49" t="b">
+        <v>1</v>
+      </c>
       <c r="J49" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
         </is>
       </c>
       <c r="K49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>API timeout</t>
+          <t>The candidate's profile is entirely focused on digital product delivery and project management, lacking the essential expertise in corporate finance, FP&amp;A, and financial business partnering required for this senior leadership role.</t>
         </is>
       </c>
       <c r="M49" t="inlineStr"/>
@@ -13530,7 +13582,7 @@
         <v>4</v>
       </c>
       <c r="B50" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -13544,24 +13596,36 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>CAND-002</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
+          <t>SYNTH-005</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Deputy General Counsel</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Qualified solicitor and Deputy General Counsel with 14 years of in-house and private practice experience in the charity, media, and technology sectors. Expert in commercial contracts, employment law, GDPR/data protection, charity governance, and IP/brand protection. Experienced advising Boards and Trustees.</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>14</v>
+      </c>
+      <c r="I50" t="b">
+        <v>1</v>
+      </c>
       <c r="J50" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
         </is>
       </c>
       <c r="K50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>No candidate profile or work experience information is provided to evaluate suitability for the role.</t>
+          <t>Although the candidate has charity sector experience, their background is strictly legal with no track record of managing finance, accounting, or FP&amp;A functions.</t>
         </is>
       </c>
       <c r="M50" t="inlineStr"/>
@@ -13590,7 +13654,7 @@
         <v>5</v>
       </c>
       <c r="B51" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -13604,21 +13668,21 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>CAND-003</t>
+          <t>SYNTH-006</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Senior Designer (Brand Design &amp; UI/UX)</t>
+          <t>Senior Procurement Manager</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Senior Brand &amp; Visual Designer with 7+ years of experience delivering brand identity, packaging, digital campaigns, and UI/UX design across consumer, B2B, and SaaS sectors. Specialist in multi-brand asset management, print production, AI workflow integration, and high-impact visual communications.</t>
+          <t>CIPS-qualified Senior Procurement Manager with 8 years leading procurement functions in charity and public sector organisations. Expert in strategic sourcing, supplier relationship management, and contract management. Delivered £4.5m of savings over 5 years through category management and competitive tendering. Experienced in EU procurement regulations and PCR 2015.</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I51" t="b">
         <v>1</v>
@@ -13629,11 +13693,11 @@
         </is>
       </c>
       <c r="K51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>API timeout</t>
+          <t>The candidate's experience is strictly within procurement and contract management, lacking the required accounting qualifications and FP&amp;A leadership background.</t>
         </is>
       </c>
       <c r="M51" t="inlineStr"/>
@@ -13676,21 +13740,21 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>CAND-004</t>
+          <t>CAND-001</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Work Placement Officer</t>
+          <t>Lead Designer</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Education administration professional and law graduate with over a year of experience in compliance, admissions support, and stakeholder coordination. Possesses expertise in contract review, data accuracy, and business engagement with plans to pursue SQE qualifications.</t>
+          <t>Lead Designer with over 20 years of multi-sector experience building brand identities and leading creative teams across financial services, technology, NGOs, and specialist sectors. Specialist in end-to-end campaign creative direction, design systems, and multi-channel delivery aligned to commercial objectives.</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
@@ -13703,7 +13767,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>The candidate lacks any finance background and possesses only one year of junior administration experience, making them completely unqualified for a senior Head of Finance role.</t>
+          <t>The candidate's background is entirely in creative design and brand strategy, lacking any required expertise in financial planning, analysis, or finance team leadership.</t>
         </is>
       </c>
       <c r="M52" t="inlineStr"/>
@@ -13746,7 +13810,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>CAND-005</t>
+          <t>CAND-002</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
@@ -13763,7 +13827,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>The candidate profile contains no information or relevant experience, making it impossible for a recruiter to consider them for the role.</t>
+          <t>There is no candidate information provided to assess suitability for this role.</t>
         </is>
       </c>
       <c r="M53" t="inlineStr"/>
@@ -13806,21 +13870,21 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>CAND-006</t>
+          <t>CAND-003</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lead Visual Artist</t>
+          <t>Senior Designer (Brand Design &amp; UI/UX)</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Senior Brand and Visual Designer with over 6 years of experience leading brand creation and visual systems across physical and digital touchpoints. Specialist in translating strategic positioning into cohesive visual identities, campaign design, and design systems within the tech and wearables sector.</t>
+          <t>Senior Brand &amp; Visual Designer with 7+ years of experience delivering brand identity, packaging, digital campaigns, and UI/UX design across consumer, B2B, and SaaS sectors. Specialist in multi-brand asset management, print production, AI workflow integration, and high-impact visual communications.</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I54" t="b">
         <v>1</v>
@@ -13835,7 +13899,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>API timeout</t>
+          <t>The candidate's background is entirely in visual and UI/UX design, possessing no relevant experience for a senior finance leadership role.</t>
         </is>
       </c>
       <c r="M54" t="inlineStr"/>
@@ -13878,25 +13942,23 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>CAND-007</t>
+          <t>CAND-004</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Freelance Senior Visual Designer</t>
+          <t>Work Placement Officer</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Senior Visual Designer with over 10 years of experience delivering branding, digital campaigns, web design, and motion graphics across global agencies and brands. Specialises in creative strategy, user interface design, and digital product systems with extensive experience leading design projects across the US, LATAM, and UK.</t>
+          <t>Education administration professional and law graduate with over a year of experience in compliance, admissions support, and stakeholder coordination. Possesses expertise in contract review, data accuracy, and business engagement with plans to pursue SQE qualifications.</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>10</v>
-      </c>
-      <c r="I55" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
@@ -13907,7 +13969,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>API timeout</t>
+          <t>The candidate has only one year of experience in education administration and legal compliance, completely lacking the required senior finance expertise and leadership background.</t>
         </is>
       </c>
       <c r="M55" t="inlineStr"/>
@@ -13950,22 +14012,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>CAND-008</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Lead Digital Designer</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Lead Digital Designer with over 18 years of experience directing and executing digital design, motion creative, UI, and branding for global integrated campaigns. Demonstrates strong craft leadership and expertise in managing design teams, brand guardianship, and integrating generative AI tools into creative workflows across consumer, tech, and financial sectors.</t>
-        </is>
-      </c>
-      <c r="H56" t="n">
-        <v>18</v>
-      </c>
+          <t>CAND-005</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
@@ -13977,7 +14029,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>API timeout</t>
+          <t>The candidate profile contains no information regarding job titles, experience, or relevant financial background to assess suitability.</t>
         </is>
       </c>
       <c r="M56" t="inlineStr"/>
@@ -14020,13 +14072,25 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>CAND-009</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
+          <t>CAND-006</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Lead Visual Artist</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Senior Brand and Visual Designer with over 6 years of experience leading brand creation and visual systems across physical and digital touchpoints. Specialist in translating strategic positioning into cohesive visual identities, campaign design, and design systems within the tech and wearables sector.</t>
+        </is>
+      </c>
+      <c r="H57" t="n">
+        <v>6</v>
+      </c>
+      <c r="I57" t="b">
+        <v>1</v>
+      </c>
       <c r="J57" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
@@ -14037,7 +14101,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>No candidate information or work history is provided to assess suitability for this senior finance position.</t>
+          <t>The candidate's background is entirely in brand and visual design, lacking any finance, FP&amp;A, or financial business partnering experience required for this senior leadership role.</t>
         </is>
       </c>
       <c r="M57" t="inlineStr"/>
@@ -14080,24 +14144,24 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>SYNTH-001</t>
+          <t>CAND-007</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Senior Creative Producer (Film &amp; Photography)</t>
+          <t>Freelance Senior Visual Designer</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Award-winning Senior Creative Producer with 9 years specialising in documentary film, charity campaigns, and editorial photography for international NGOs. Proven track record managing end-to-end productions from concept to broadcast, leading cross-functional creative teams and delivering compelling visual storytelling.</t>
+          <t>Senior Visual Designer with over 10 years of experience delivering branding, digital campaigns, web design, and motion graphics across global agencies and brands. Specialises in creative strategy, user interface design, and digital product systems with extensive experience leading design projects across the US, LATAM, and UK.</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -14109,7 +14173,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>API timeout</t>
+          <t>The candidate's background in visual design and creative strategy bears no relevance to a senior finance business partnering leadership role.</t>
         </is>
       </c>
       <c r="M58" t="inlineStr"/>
@@ -14152,25 +14216,23 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>SYNTH-002</t>
+          <t>CAND-008</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Digital Delivery Manager</t>
+          <t>Lead Digital Designer</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Results-driven Digital Delivery Manager with 7 years delivering agile digital products and online platforms for charity and public sector organisations. Experienced in Scrum, Kanban and SAFe frameworks, managing cross-functional teams of 15+ to deliver user-centred services on time and within budget.</t>
+          <t>Lead Digital Designer with over 18 years of experience directing and executing digital design, motion creative, UI, and branding for global integrated campaigns. Demonstrates strong craft leadership and expertise in managing design teams, brand guardianship, and integrating generative AI tools into creative workflows across consumer, tech, and financial sectors.</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>7</v>
-      </c>
-      <c r="I59" t="b">
-        <v>1</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
@@ -14181,7 +14243,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>API timeout</t>
+          <t>The candidate's background is entirely in creative digital design with no relevant experience in finance, accounting, or FP&amp;A required for a Head of Finance role.</t>
         </is>
       </c>
       <c r="M59" t="inlineStr"/>
@@ -14224,25 +14286,13 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>SYNTH-003</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Head of Finance Business Partnering</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>CIMA-qualified Head of Finance Business Partnering with 12 years in charity and public sector finance. Expert in management accounting, financial planning &amp; analysis, and strategic finance partnering with senior leadership teams. Experienced in leading finance transformation projects and implementing ERP systems.</t>
-        </is>
-      </c>
-      <c r="H60" t="n">
-        <v>12</v>
-      </c>
-      <c r="I60" t="b">
-        <v>1</v>
-      </c>
+          <t>CAND-009</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
@@ -14253,7 +14303,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>API timeout</t>
+          <t>The candidate profile contains no employment history or qualifications to assess suitability for the role.</t>
         </is>
       </c>
       <c r="M60" t="inlineStr"/>
@@ -14296,21 +14346,21 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>SYNTH-005</t>
+          <t>SYNTH-001</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Deputy General Counsel</t>
+          <t>Senior Creative Producer (Film &amp; Photography)</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Qualified solicitor and Deputy General Counsel with 14 years of in-house and private practice experience in the charity, media, and technology sectors. Expert in commercial contracts, employment law, GDPR/data protection, charity governance, and IP/brand protection. Experienced advising Boards and Trustees.</t>
+          <t>Award-winning Senior Creative Producer with 9 years specialising in documentary film, charity campaigns, and editorial photography for international NGOs. Proven track record managing end-to-end productions from concept to broadcast, leading cross-functional creative teams and delivering compelling visual storytelling.</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I61" t="b">
         <v>1</v>
@@ -14325,7 +14375,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>API timeout</t>
+          <t>The candidate has a background strictly in creative media production and lacks any of the required financial management, FP&amp;A, or accounting experience necessary for a Head of Finance role.</t>
         </is>
       </c>
       <c r="M61" t="inlineStr"/>
@@ -14354,7 +14404,7 @@
         <v>1</v>
       </c>
       <c r="B62" t="n">
-        <v>8.35</v>
+        <v>8.515000000000001</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -14397,27 +14447,27 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>The candidate is a CIPS-qualified procurement professional with 8 years of direct procurement leadership experience within the charity sector, making them an ideal match for this role.</t>
+          <t>The candidate is a CIPS-qualified Senior Procurement Manager with extensive experience in the UK charity sector, making them an outstanding fit for a Procurement Lead role at UNICEF UK.</t>
         </is>
       </c>
       <c r="M62" t="n">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>2/3 Anforderungen</t>
+          <t>3/3 Anforderungen</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Fehlende konkrete Belege für die Balancierung von Governance mit operativer Flexibilität (operational flexibility).</t>
+          <t>Fehlende explizite Nachweise über die direkte Einflussnahme auf C-Level / Board-Ebene (Senior Stakeholder Influence)., Keine konkreten Fallbeispiele im CV zur praktischen Ausbalancierung von Governance und operationaler Flexibilität.</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>[8/10] Shape procurement practice: Senior Procurement Manager bei Action Aid UK: 'Lead procurem
-[7/10] Influence senior stakeholders: Explizite Soft Skills: Stakeholder Management, Leadership, C
-[6/10] Ensure strong governance whilst enabling operation: Starke Governance-Belege durch PCR 2015 / OJEU-Compliance be</t>
+          <t>[8/10] Shape procurement practice: Leitung der Procurement-Funktion bei Action Aid UK inkl. Ein
+[7/10] Influence senior stakeholders: Ausgewiesene Soft Skills in 'Stakeholder Management', 'Leade
+[7/10] Ensure strong governance whilst enabling operation: Starke Governance-Belege durch PCR 2015, OJEU-Compliance, Su</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
@@ -14427,9 +14477,9 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>**Strengths**: Proven track record of shaping procurement practices within the UK charity sector, leading an £18m annual spend portfolio at ActionAid UK and establishing a category management framework that generated £1.2m in year-1 savings. Demonstrates robust governance capability through MCIPS accreditation and extensive PCR 2015/OJEU compliance experience across 12 tendering exercises. Strong leadership background, managing a team of 3 and delivering £4.5m total savings across 8 years.
-**Gaps**: Lacks explicit evidence of successfully balancing strict governance controls with operational flexibility.
-**Recommendation**: An excellent sector-aligned candidate with proven procurement leadership in a comparable charity environment. I recommend progressing to interview to explore their practical approach to enabling operational agility alongside compliance.</t>
+          <t>**Strengths**: MCIPS-qualified with 8 years of relevant charity and public sector experience, currently leading Action Aid UK's procurement function (£18m spend, team of 3) and delivering a category framework saving £1.2m in year 1. Demonstrates robust governance expertise through extensive PCR 2015 and OJEU compliant procurement exercises.
+**Gaps**: Lacks explicit CV evidence of direct C-suite or Board-level stakeholder influence, alongside a missing practical record of balancing governance with operational flexibility.
+**Recommendation**: Highly suitable candidate possessing direct charity sector leadership experience and strong domain expertise. Recommend proceeding to interview, probing specifically on C-level stakeholder engagement and operational agility.</t>
         </is>
       </c>
       <c r="S62" t="inlineStr"/>
@@ -14483,7 +14533,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>While the candidate has strong charity sector experience at a senior level, their profile is entirely focused on finance and FP&amp;A rather than procurement, sourcing, and vendor management.</t>
+          <t>While the candidate has strong charity sector experience, a career in finance business partnering lacks the specialized sourcing, contract management, and vendor negotiation skills required for a Procurement Lead role.</t>
         </is>
       </c>
       <c r="M63" t="inlineStr"/>
@@ -14555,7 +14605,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>Although the candidate has strong legal and charity sector experience, a legal background does not align with the core supply chain and strategic sourcing responsibilities required for a Procurement Lead.</t>
+          <t>Although the candidate has valuable charity sector experience and expertise in commercial contracts, a Deputy General Counsel lacks the specific operational procurement, purchasing, and supply chain management background required for a Procurement Lead.</t>
         </is>
       </c>
       <c r="M64" t="inlineStr"/>
@@ -14627,7 +14677,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>While the candidate has valuable charity sector experience, a background in digital delivery management lacks the core commercial, sourcing, and contract management skills required for a Procurement Lead.</t>
+          <t>While the candidate has valuable charity sector experience, digital delivery management lacks the essential sourcing, commercial contract, and supply chain expertise required for a Procurement Lead.</t>
         </is>
       </c>
       <c r="M65" t="inlineStr"/>
@@ -14699,7 +14749,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>Although the candidate has relevant charity sector experience, Internal Audit and Risk is a distinct function that lacks the required commercial sourcing, vendor management, and supply chain expertise needed for a Procurement Lead role.</t>
+          <t>Although the candidate has strong charity sector experience, Internal Audit and Risk is a completely different functional specialization from Procurement.</t>
         </is>
       </c>
       <c r="M66" t="inlineStr"/>
@@ -14742,25 +14792,23 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>SYNTH-001</t>
+          <t>CAND-004</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Senior Creative Producer (Film &amp; Photography)</t>
+          <t>Work Placement Officer</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Award-winning Senior Creative Producer with 9 years specialising in documentary film, charity campaigns, and editorial photography for international NGOs. Proven track record managing end-to-end productions from concept to broadcast, leading cross-functional creative teams and delivering compelling visual storytelling.</t>
+          <t>Education administration professional and law graduate with over a year of experience in compliance, admissions support, and stakeholder coordination. Possesses expertise in contract review, data accuracy, and business engagement with plans to pursue SQE qualifications.</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>9</v>
-      </c>
-      <c r="I67" t="b">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
@@ -14771,7 +14819,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>Although the candidate has relevant NGO sector experience, a background in creative production lacks the critical commercial, vendor management, and supply chain expertise required for a Procurement Lead.</t>
+          <t>The candidate has only one year of experience in education administration and lacks the necessary procurement and supply chain management background for a Lead position.</t>
         </is>
       </c>
       <c r="M67" t="inlineStr"/>
@@ -14800,7 +14848,7 @@
         <v>7</v>
       </c>
       <c r="B68" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -14814,34 +14862,36 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>CAND-001</t>
+          <t>SYNTH-001</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lead Designer</t>
+          <t>Senior Creative Producer (Film &amp; Photography)</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lead Designer with over 20 years of multi-sector experience building brand identities and leading creative teams across financial services, technology, NGOs, and specialist sectors. Specialist in end-to-end campaign creative direction, design systems, and multi-channel delivery aligned to commercial objectives.</t>
+          <t>Award-winning Senior Creative Producer with 9 years specialising in documentary film, charity campaigns, and editorial photography for international NGOs. Proven track record managing end-to-end productions from concept to broadcast, leading cross-functional creative teams and delivering compelling visual storytelling.</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>23</v>
-      </c>
-      <c r="I68" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="I68" t="b">
+        <v>1</v>
+      </c>
       <c r="J68" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
         </is>
       </c>
       <c r="K68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>A Lead Designer's creative background has no functional overlap or logical career progression into a Procurement Lead role.</t>
+          <t>While the candidate has valuable NGO sector experience, a background in creative media production lacks the required expertise in strategic sourcing, negotiation, and supply chain management essential for a Procurement Lead role.</t>
         </is>
       </c>
       <c r="M68" t="inlineStr"/>
@@ -14884,12 +14934,22 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>CAND-002</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
+          <t>CAND-001</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Lead Designer</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Lead Designer with over 20 years of multi-sector experience building brand identities and leading creative teams across financial services, technology, NGOs, and specialist sectors. Specialist in end-to-end campaign creative direction, design systems, and multi-channel delivery aligned to commercial objectives.</t>
+        </is>
+      </c>
+      <c r="H69" t="n">
+        <v>23</v>
+      </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
@@ -14901,7 +14961,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>No candidate profile or work experience is provided to evaluate suitability for the Procurement Lead role.</t>
+          <t>The candidate's background is exclusively in creative design and branding, offering no relevant experience for a Procurement Lead role.</t>
         </is>
       </c>
       <c r="M69" t="inlineStr"/>
@@ -14944,25 +15004,13 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>CAND-003</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Senior Designer (Brand Design &amp; UI/UX)</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Senior Brand &amp; Visual Designer with 7+ years of experience delivering brand identity, packaging, digital campaigns, and UI/UX design across consumer, B2B, and SaaS sectors. Specialist in multi-brand asset management, print production, AI workflow integration, and high-impact visual communications.</t>
-        </is>
-      </c>
-      <c r="H70" t="n">
-        <v>7</v>
-      </c>
-      <c r="I70" t="b">
-        <v>1</v>
-      </c>
+          <t>CAND-002</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
@@ -14973,7 +15021,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>API timeout</t>
+          <t>The candidate profile contains no information or background to assess suitability for the Procurement Lead role.</t>
         </is>
       </c>
       <c r="M70" t="inlineStr"/>
@@ -15016,23 +15064,25 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>CAND-004</t>
+          <t>CAND-003</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Work Placement Officer</t>
+          <t>Senior Designer (Brand Design &amp; UI/UX)</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Education administration professional and law graduate with over a year of experience in compliance, admissions support, and stakeholder coordination. Possesses expertise in contract review, data accuracy, and business engagement with plans to pursue SQE qualifications.</t>
+          <t>Senior Brand &amp; Visual Designer with 7+ years of experience delivering brand identity, packaging, digital campaigns, and UI/UX design across consumer, B2B, and SaaS sectors. Specialist in multi-brand asset management, print production, AI workflow integration, and high-impact visual communications.</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>1</v>
-      </c>
-      <c r="I71" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="I71" t="b">
+        <v>1</v>
+      </c>
       <c r="J71" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
@@ -15043,7 +15093,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>API timeout</t>
+          <t>The candidate's background is entirely focused on visual and UI/UX design, offering no transferrable skills or relevant experience for a Procurement Lead position.</t>
         </is>
       </c>
       <c r="M71" t="inlineStr"/>
@@ -15103,7 +15153,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>The candidate profile contains no information or employment history to assess suitability for the Procurement Lead role.</t>
+          <t>No candidate information is provided to assess suitability for the Procurement Lead role.</t>
         </is>
       </c>
       <c r="M72" t="inlineStr"/>
@@ -15175,7 +15225,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>API timeout</t>
+          <t>The candidate's background in visual art and brand design is completely unrelated to a Procurement Lead role focused on purchasing and supply chain management.</t>
         </is>
       </c>
       <c r="M73" t="inlineStr"/>
@@ -15247,7 +15297,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>The candidate's career is strictly focused on visual design and creative strategy, with no relevant background in procurement, sourcing, or vendor management.</t>
+          <t>The candidate's background is entirely in visual design and creative strategy, which has no functional overlap with a Procurement Lead role focused on sourcing, vendor management, and supply chain.</t>
         </is>
       </c>
       <c r="M74" t="inlineStr"/>
@@ -15317,7 +15367,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>The candidate's background in creative digital design and branding has no alignment with a strategic procurement and vendor management role.</t>
+          <t>The candidate's background is entirely focused on digital design and creative leadership, showing no transferable experience in procurement, vendor management, or strategic purchasing.</t>
         </is>
       </c>
       <c r="M75" t="inlineStr"/>
@@ -15377,7 +15427,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>The candidate profile contains no information regarding background, skills, or experience to evaluate suitability for a Procurement Lead role.</t>
+          <t>No candidate profile or career history is provided to assess suitability for the Procurement Lead position.</t>
         </is>
       </c>
       <c r="M76" t="inlineStr"/>
@@ -15406,7 +15456,7 @@
         <v>1</v>
       </c>
       <c r="B77" t="n">
-        <v>8.57</v>
+        <v>8.994</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -15449,11 +15499,11 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>The candidate has the exact matching job title and 9 years of directly relevant experience in film and photography production within the charity and international NGO sector.</t>
+          <t>The candidate holds the exact job title required, possesses 9 years of directly relevant experience within international NGOs, and fully aligns with the creative and production demands of the role.</t>
         </is>
       </c>
       <c r="M77" t="n">
-        <v>7.8</v>
+        <v>8.17</v>
       </c>
       <c r="N77" t="inlineStr">
         <is>
@@ -15462,26 +15512,28 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>Expliziter Nachweis von Kenntnissen und Haltung zu ethischer Content-Erstellung (Ethical Content Creation) und inklusivem Storytelling (Inclusive Storytelling).</t>
+          <t>Kein expliziter Beleg für Nachweise/Zertifikate oder konkrete Frameworks zu 'Ethical Content Creation' und 'Inclusive Storytelling' im Profil vorhanden.</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t xml:space="preserve">[10/10] Experienced creative leader with a strong track re: 9 Jahre Berufserfahrung als Senior Creative Producer u.a. be
-[9/10] Excellent creative judgement and experience leadin: Ausgewiesene Skills in 'Creative Leadership' und 'Team Direc
-[8/10] Deep understanding of visual storytelling, audienc: Fundierte technische Skills (Storyboarding, Scriptwriting, F
-[4/10] Passion for inclusive storytelling and ethical con: Kein expliziter Beleg für 'inclusive storytelling' oder 'eth
-[7/10] Ability to translate insight, strategy, and organi: Leitung aller Film- und Fotokampagnen bei Save the Children </t>
+          <t>[10/10] Experienced creative leader with a strong track re: 9 Jahre Berufserfahrung; Senior Creative Producer bei Save t
+[9/10] Excellent creative judgement and experience leadin: Soft Skills 'Creative Leadership' und 'Team Direction'; Führ
+[8/10] Deep understanding of visual storytelling, audienc: Technische Skills in Storyboarding, Scriptwriting, Film Prod
+[6/10] Passion for inclusive storytelling and ethical con: Langjährige Tätigkeit im NGO- und Charity-Sektor (Save the C
+[7/10] Ability to translate insight, strategy, and organi: Verantwortung für sämtliche Film- und Fotokampagnen bei Save</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Strong Match</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>(failed: )</t>
+          <t>**Strengths**: Proven track record in international NGO content creation with 9 years of experience, including leading film/photography campaigns at Save the Children UK and Comic Relief. Extensive experience managing complex international productions (£1.2m budget, 40+ documentary shorts in Africa/Middle East, crews across 12 countries) and a strong portfolio demonstrated by 3 Charity Film Awards.
+**Gaps**: Lacks explicit documentation or formal frameworks regarding ethical content creation and inclusive storytelling standards in their profile, despite extensive sector experience.
+**Recommendation**: The candidate brings exceptional sector-specific experience, proven international production leadership, and award-winning visual storytelling capability directly aligned with UNICEF UK's needs. Recommend proceeding to interview to explore their approach to ethical content guidelines.</t>
         </is>
       </c>
       <c r="S77" t="inlineStr"/>
@@ -15492,7 +15544,7 @@
         <v>2</v>
       </c>
       <c r="B78" t="n">
-        <v>1.4</v>
+        <v>1.05</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -15529,11 +15581,11 @@
         </is>
       </c>
       <c r="K78" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>While the candidate possesses extensive creative leadership and NGO experience, their background focuses on graphic brand design rather than specialized film and photography content production.</t>
+          <t>While the candidate brings extensive creative leadership and NGO experience, their profile focuses on visual/graphic design and brand identity rather than hands-on film and photography production.</t>
         </is>
       </c>
       <c r="M78" t="inlineStr"/>
@@ -15562,7 +15614,7 @@
         <v>3</v>
       </c>
       <c r="B79" t="n">
-        <v>1.4</v>
+        <v>1.05</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -15576,34 +15628,36 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>CAND-008</t>
+          <t>CAND-003</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lead Digital Designer</t>
+          <t>Senior Designer (Brand Design &amp; UI/UX)</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lead Digital Designer with over 18 years of experience directing and executing digital design, motion creative, UI, and branding for global integrated campaigns. Demonstrates strong craft leadership and expertise in managing design teams, brand guardianship, and integrating generative AI tools into creative workflows across consumer, tech, and financial sectors.</t>
+          <t>Senior Brand &amp; Visual Designer with 7+ years of experience delivering brand identity, packaging, digital campaigns, and UI/UX design across consumer, B2B, and SaaS sectors. Specialist in multi-brand asset management, print production, AI workflow integration, and high-impact visual communications.</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>18</v>
-      </c>
-      <c r="I79" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="I79" t="b">
+        <v>1</v>
+      </c>
       <c r="J79" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
         </is>
       </c>
       <c r="K79" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>While the candidate brings extensive creative leadership in digital design and branding, they lack the specific track record in film and photography production required for this role.</t>
+          <t>The candidate's background is strictly in graphic, brand, and UI/UX design, lacking the necessary specialized experience in film and photography production.</t>
         </is>
       </c>
       <c r="M79" t="inlineStr"/>
@@ -15675,7 +15729,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>The candidate is a brand and visual systems designer in tech/e-commerce, lacking the required specialized experience in film and photography content production.</t>
+          <t>The candidate specializes in brand identity and visual design systems rather than film and photography content production.</t>
         </is>
       </c>
       <c r="M80" t="inlineStr"/>
@@ -15718,25 +15772,23 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>CAND-007</t>
+          <t>CAND-008</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Freelance Senior Visual Designer</t>
+          <t>Lead Digital Designer</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Senior Visual Designer with over 10 years of experience delivering branding, digital campaigns, web design, and motion graphics across global agencies and brands. Specialises in creative strategy, user interface design, and digital product systems with extensive experience leading design projects across the US, LATAM, and UK.</t>
+          <t>Lead Digital Designer with over 18 years of experience directing and executing digital design, motion creative, UI, and branding for global integrated campaigns. Demonstrates strong craft leadership and expertise in managing design teams, brand guardianship, and integrating generative AI tools into creative workflows across consumer, tech, and financial sectors.</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>10</v>
-      </c>
-      <c r="I81" t="b">
-        <v>0</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
@@ -15747,7 +15799,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>While the candidate has strong visual design and motion graphics experience, they lack the specific track record in film and photography production required for this Senior Creative Producer role.</t>
+          <t>While the candidate possesses extensive creative leadership experience, their background is focused on digital UI and branding design rather than hands-on film and photography content production.</t>
         </is>
       </c>
       <c r="M81" t="inlineStr"/>
@@ -15790,24 +15842,24 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>SYNTH-002</t>
+          <t>CAND-007</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Digital Delivery Manager</t>
+          <t>Freelance Senior Visual Designer</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Results-driven Digital Delivery Manager with 7 years delivering agile digital products and online platforms for charity and public sector organisations. Experienced in Scrum, Kanban and SAFe frameworks, managing cross-functional teams of 15+ to deliver user-centred services on time and within budget.</t>
+          <t>Senior Visual Designer with over 10 years of experience delivering branding, digital campaigns, web design, and motion graphics across global agencies and brands. Specialises in creative strategy, user interface design, and digital product systems with extensive experience leading design projects across the US, LATAM, and UK.</t>
         </is>
       </c>
       <c r="H82" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I82" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
@@ -15819,7 +15871,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>While the candidate has relevant charity sector experience, a background in agile digital delivery management lacks the essential creative leadership, film, and photography production expertise required for this role.</t>
+          <t>While the candidate has strong visual design and motion graphics experience, they lack the core film and photography production expertise required for this Creative Producer role.</t>
         </is>
       </c>
       <c r="M82" t="inlineStr"/>
@@ -15848,7 +15900,7 @@
         <v>7</v>
       </c>
       <c r="B83" t="n">
-        <v>0</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -15862,24 +15914,36 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>CAND-002</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
-      <c r="I83" t="inlineStr"/>
+          <t>SYNTH-002</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Digital Delivery Manager</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Results-driven Digital Delivery Manager with 7 years delivering agile digital products and online platforms for charity and public sector organisations. Experienced in Scrum, Kanban and SAFe frameworks, managing cross-functional teams of 15+ to deliver user-centred services on time and within budget.</t>
+        </is>
+      </c>
+      <c r="H83" t="n">
+        <v>7</v>
+      </c>
+      <c r="I83" t="b">
+        <v>1</v>
+      </c>
       <c r="J83" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
         </is>
       </c>
       <c r="K83" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>No candidate information or work history was provided to assess suitability for the role.</t>
+          <t>While the candidate has relevant charity sector experience, a background in technical digital delivery management lacks the required film, photography, and creative production expertise.</t>
         </is>
       </c>
       <c r="M83" t="inlineStr"/>
@@ -15908,7 +15972,7 @@
         <v>8</v>
       </c>
       <c r="B84" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -15922,21 +15986,21 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>CAND-003</t>
+          <t>SYNTH-005</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Senior Designer (Brand Design &amp; UI/UX)</t>
+          <t>Deputy General Counsel</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Senior Brand &amp; Visual Designer with 7+ years of experience delivering brand identity, packaging, digital campaigns, and UI/UX design across consumer, B2B, and SaaS sectors. Specialist in multi-brand asset management, print production, AI workflow integration, and high-impact visual communications.</t>
+          <t>Qualified solicitor and Deputy General Counsel with 14 years of in-house and private practice experience in the charity, media, and technology sectors. Expert in commercial contracts, employment law, GDPR/data protection, charity governance, and IP/brand protection. Experienced advising Boards and Trustees.</t>
         </is>
       </c>
       <c r="H84" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="I84" t="b">
         <v>1</v>
@@ -15947,11 +16011,11 @@
         </is>
       </c>
       <c r="K84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>API timeout</t>
+          <t>The candidate has a background entirely focused on legal and compliance functions, lacking the essential hands-on experience in creative direction, film production, and visual storytelling required for this role.</t>
         </is>
       </c>
       <c r="M84" t="inlineStr"/>
@@ -15994,22 +16058,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>CAND-004</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>Work Placement Officer</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>Education administration professional and law graduate with over a year of experience in compliance, admissions support, and stakeholder coordination. Possesses expertise in contract review, data accuracy, and business engagement with plans to pursue SQE qualifications.</t>
-        </is>
-      </c>
-      <c r="H85" t="n">
-        <v>1</v>
-      </c>
+          <t>CAND-002</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
@@ -16021,7 +16075,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>The candidate has no experience in film, photography, or creative leadership, coming from an entry-level background in legal and educational administration.</t>
+          <t>No candidate profile or work history is provided, making it impossible for a recruiter to consider this application.</t>
         </is>
       </c>
       <c r="M85" t="inlineStr"/>
@@ -16064,12 +16118,22 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>CAND-005</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
+          <t>CAND-004</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Work Placement Officer</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Education administration professional and law graduate with over a year of experience in compliance, admissions support, and stakeholder coordination. Possesses expertise in contract review, data accuracy, and business engagement with plans to pursue SQE qualifications.</t>
+        </is>
+      </c>
+      <c r="H86" t="n">
+        <v>1</v>
+      </c>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr">
         <is>
@@ -16081,7 +16145,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>The candidate profile contains no information or career history to demonstrate the required film and photography production experience.</t>
+          <t>The candidate's background in education administration and law completely lacks the creative leadership and film/photography production experience required for this senior role.</t>
         </is>
       </c>
       <c r="M86" t="inlineStr"/>
@@ -16124,7 +16188,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>CAND-009</t>
+          <t>CAND-005</t>
         </is>
       </c>
       <c r="F87" t="inlineStr"/>
@@ -16141,7 +16205,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>No candidate information or work history is provided, making it impossible for a recruiter to consider them for this role.</t>
+          <t>No professional details, job title, or experience are provided to evaluate suitability for the role.</t>
         </is>
       </c>
       <c r="M87" t="inlineStr"/>
@@ -16184,25 +16248,13 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>SYNTH-003</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>Head of Finance Business Partnering</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>CIMA-qualified Head of Finance Business Partnering with 12 years in charity and public sector finance. Expert in management accounting, financial planning &amp; analysis, and strategic finance partnering with senior leadership teams. Experienced in leading finance transformation projects and implementing ERP systems.</t>
-        </is>
-      </c>
-      <c r="H88" t="n">
-        <v>12</v>
-      </c>
-      <c r="I88" t="b">
-        <v>1</v>
-      </c>
+          <t>CAND-009</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
@@ -16213,7 +16265,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>API timeout</t>
+          <t>No profile, work history, or experience details are provided to evaluate the candidate's suitability for the role.</t>
         </is>
       </c>
       <c r="M88" t="inlineStr"/>
@@ -16256,21 +16308,21 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>SYNTH-004</t>
+          <t>SYNTH-003</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Head of Internal Audit &amp; Risk</t>
+          <t>Head of Finance Business Partnering</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>CIIA-qualified Head of Internal Audit and Risk with 11 years in the charity and financial services sectors. Specialist in enterprise risk management (ERM), internal audit delivery, and governance frameworks. Experienced in audit committee reporting, fraud prevention, and regulatory compliance.</t>
+          <t>CIMA-qualified Head of Finance Business Partnering with 12 years in charity and public sector finance. Expert in management accounting, financial planning &amp; analysis, and strategic finance partnering with senior leadership teams. Experienced in leading finance transformation projects and implementing ERP systems.</t>
         </is>
       </c>
       <c r="H89" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I89" t="b">
         <v>1</v>
@@ -16285,7 +16337,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>The candidate's background is entirely in internal audit, risk management, and compliance, offering no transferable experience for a senior creative media production role.</t>
+          <t>The candidate has an entirely finance-focused background with zero experience in visual storytelling, creative leadership, or film and photography production.</t>
         </is>
       </c>
       <c r="M89" t="inlineStr"/>
@@ -16328,21 +16380,21 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>SYNTH-005</t>
+          <t>SYNTH-004</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Deputy General Counsel</t>
+          <t>Head of Internal Audit &amp; Risk</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Qualified solicitor and Deputy General Counsel with 14 years of in-house and private practice experience in the charity, media, and technology sectors. Expert in commercial contracts, employment law, GDPR/data protection, charity governance, and IP/brand protection. Experienced advising Boards and Trustees.</t>
+          <t>CIIA-qualified Head of Internal Audit and Risk with 11 years in the charity and financial services sectors. Specialist in enterprise risk management (ERM), internal audit delivery, and governance frameworks. Experienced in audit committee reporting, fraud prevention, and regulatory compliance.</t>
         </is>
       </c>
       <c r="H90" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I90" t="b">
         <v>1</v>
@@ -16357,7 +16409,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>Despite extensive legal experience in the charity sector, the candidate completely lacks the required background in film and photography production, visual storytelling, and creative leadership.</t>
+          <t>The candidate's background in internal audit and risk management is completely unrelated to creative leadership, film, and photography production.</t>
         </is>
       </c>
       <c r="M90" t="inlineStr"/>
@@ -16429,7 +16481,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>The candidate's background in procurement and contract management is entirely unrelated to visual storytelling, film, and photography production.</t>
+          <t>The candidate's experience is exclusively in procurement and contract management, lacking any background in creative leadership, film, or visual content production.</t>
         </is>
       </c>
       <c r="M91" t="inlineStr"/>
@@ -16458,7 +16510,7 @@
         <v>1</v>
       </c>
       <c r="B92" t="n">
-        <v>8.19</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -16497,15 +16549,15 @@
         </is>
       </c>
       <c r="K92" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>The candidate has a highly relevant public sector finance background and CIMA qualification, making them a very strong candidate despite potentially being overqualified for a Senior Officer role.</t>
+          <t>The candidate is CIMA-qualified with extensive UK public sector finance experience, making them a highly plausible and strong candidate for a Senior Finance Officer role.</t>
         </is>
       </c>
       <c r="M92" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="N92" t="inlineStr">
         <is>
@@ -16515,11 +16567,11 @@
       <c r="O92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>[8/10] Building and managing relationships: developing ra: Führung eines Teams von 6 Finance Business Partnern zur Unte
-[8/10] Communicating, engaging and influencing: presentin: Soft Skills 'Communication' und 'Stakeholder Influence'; erf
-[8/10] Planning and organising: thinking ahead, managing : Verwaltung eines 85 Mio. £ Budgets, Verantwortung für Month-
-[7/10] Research and analysis: gathering intelligence from: Erfahrung mit Variance Analysis, FP&amp;A und Cash Flow Forecast
-[8/10] Problem solving: analysing and interpreting situat: Expliziter Soft Skill 'Problem Solving'; Lösungskompetenz de</t>
+          <t>[8/10] Building and managing relationships: developing ra: Led a team of 6 finance business partners supporting 12 dire
+[8/10] Communicating, engaging and influencing: presentin: Engaged and influenced stakeholders across 12 directorates t
+[8/10] Planning and organising: thinking ahead, managing : Managed an £85m combined budget, oversaw month-end close and
+[7/10] Research and analysis: gathering intelligence from: Demonstrated through Variance Analysis, FP&amp;A skills, and zer
+[7/10] Problem solving: analysing and interpreting situat: Explicitly listed Problem Solving and Strategic Thinking ski</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
@@ -16529,9 +16581,9 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>**Strengths**: CIMA-qualified with 12 years of public and charity sector experience, including relevant local government exposure at London Borough of Southwark. Proficient in SAP and month-end close processes with strong stakeholder engagement skills.
-**Gaps**: Candidate is overqualified, currently operating as Head of Finance Business Partnering. Lacks explicit details on day-to-day Asset and Estate Management (AEM) tenant operations.
-**Recommendation**: The candidate easily exceeds technical requirements and brings valuable public sector expertise. Recommend probing motivation and career expectations to manage potential overqualification risks.</t>
+          <t>**Strengths**: 1. Strong public sector and housing domain experience from London Borough of Southwark (£85m budget management). 2. CIMA-qualified with direct SAP proficiency and hands-on month-end close and reporting expertise. 3. Proven stakeholder engagement skills, having led teams and influenced senior leadership across 12 directorates.
+**Gaps**: 1. Risk of overqualification, moving from a Head of Finance position to an operational Senior Finance Officer role. 2. Lacks explicit experience in Asset &amp; Estate Management (AEM) portfolio oversight and tenant-related cash transfer notes.
+**Recommendation**: The candidate's public sector background, CIMA qualification, and SAP skills make them technically ideal for OPDC. Recommend interviewing to assess motivation for stepping into a more hands-on operational role.</t>
         </is>
       </c>
       <c r="S92" t="inlineStr"/>
@@ -16542,7 +16594,7 @@
         <v>2</v>
       </c>
       <c r="B93" t="n">
-        <v>7.07</v>
+        <v>2.4</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -16585,41 +16637,29 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>The candidate has a strong background in financial governance, risk, and audit within public-adjacent sectors, making them functionally relevant despite being potentially overqualified.</t>
+          <t>The candidate's extensive background in internal audit, governance, and financial risk within adjacent sectors makes them a highly relevant applicant for a Senior Finance Officer role.</t>
         </is>
       </c>
       <c r="M93" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>5/5 Anforderungen</t>
-        </is>
-      </c>
-      <c r="O93" t="inlineStr">
-        <is>
-          <t>Fokus liegt stark auf Audit, Risiko und Governance; direkte Nachweise für operative Buchhaltung, Budgetierung und Finanzberichterstattung (Management Accounting) fehlen im Detail.</t>
-        </is>
-      </c>
-      <c r="P93" t="inlineStr">
-        <is>
-          <t>[8/10] Building and managing relationships: developing ra: Nachgewiesene Erfahrung in der Führung von Audit-Teams (4-6 
-[8/10] Communicating, engaging and influencing: presentin: 'Board Communication', 'Audit Committee Reporting' bei Macmi
-[8/10] Planning and organising: thinking ahead, managing : Verantwortlich für das gesamte Internal Audit Programm und E
-[8/10] Research and analysis: gathering intelligence from: Durchführung komplexer Finanz- und Betriebs-Audits bei Lloyd
-[7/10] Problem solving: analysing and interpreting situat: 'Critical Thinking', Analyse komplexer operativer/finanziell</t>
-        </is>
-      </c>
+          <t>0/5 Anforderungen</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr"/>
+      <c r="P93" t="inlineStr"/>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>Possible Match</t>
+          <t>Weak Match</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>**Strengths**: CIIA-qualified with a BA in Accounting &amp; Finance and 11 years of governance experience across public/charity sectors (NHS, Macmillan). Demonstrates strong stakeholder communication skills, reporting directly to CFOs and Board Committees. Proven analytical expertise in financial control, having identified £3.2m in control weaknesses at Lloyds Banking Group.
-**Gaps**: Lacks explicit evidence of hands-on operational accounting routines, such as posting SAP journals, raising sales invoices, and cash allocations. No documented experience managing Asset &amp; Estate Management (AEM) portfolios.
-**Recommendation**: The candidate possesses strong transferable analytical skills and relevant sector background, but is currently focused on high-level risk and audit. Interviewing should probe their willingness and technical capability to perform day-to-day transactional finance duties.</t>
+          <t>**Strengths**: Holds a BA in Accounting &amp; Finance and a CIIA qualification, providing a solid technical foundation. Demonstrates strong experience in stakeholder engagement, risk analysis, and reporting to CFOs and senior committees within public and third-sector organisations (NHS England, Macmillan).
+**Gaps**: Lacks direct hands-on operational accounting experience, specifically posting SAP journals, period/quarter-end close processes, raising sales invoices, and Asset &amp; Estate Management (AEM) portfolio oversight. The profile is heavily aligned with audit and risk governance rather than routine financial operations.
+**Recommendation**: While highly qualified in internal audit and risk management, the candidate's background does not align with the day-to-day operational and transactional accounting tasks required for this role.</t>
         </is>
       </c>
       <c r="S93" t="inlineStr"/>
@@ -16673,7 +16713,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>Although the candidate has strong public sector experience, procurement is a distinct discipline from finance and lacks the required accounting qualifications and financial management background for a Senior Finance Officer role.</t>
+          <t>While the candidate has strong public sector procurement experience, they lack the specific accounting qualifications and core financial management expertise required for a Senior Finance Officer role.</t>
         </is>
       </c>
       <c r="M94" t="inlineStr"/>
@@ -16702,7 +16742,7 @@
         <v>4</v>
       </c>
       <c r="B95" t="n">
-        <v>0.35</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -16716,34 +16756,36 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>CAND-004</t>
+          <t>SYNTH-002</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Work Placement Officer</t>
+          <t>Digital Delivery Manager</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Education administration professional and law graduate with over a year of experience in compliance, admissions support, and stakeholder coordination. Possesses expertise in contract review, data accuracy, and business engagement with plans to pursue SQE qualifications.</t>
+          <t>Results-driven Digital Delivery Manager with 7 years delivering agile digital products and online platforms for charity and public sector organisations. Experienced in Scrum, Kanban and SAFe frameworks, managing cross-functional teams of 15+ to deliver user-centred services on time and within budget.</t>
         </is>
       </c>
       <c r="H95" t="n">
-        <v>1</v>
-      </c>
-      <c r="I95" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="I95" t="b">
+        <v>1</v>
+      </c>
       <c r="J95" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
         </is>
       </c>
       <c r="K95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>The candidate lacks a background in finance and senior-level experience, coming from a junior education administration and legal profile.</t>
+          <t>The candidate's background in digital product delivery lacks the essential accounting qualifications and financial management expertise required for a Senior Finance Officer role.</t>
         </is>
       </c>
       <c r="M95" t="inlineStr"/>
@@ -16786,25 +16828,23 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>SYNTH-002</t>
+          <t>CAND-004</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Digital Delivery Manager</t>
+          <t>Work Placement Officer</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Results-driven Digital Delivery Manager with 7 years delivering agile digital products and online platforms for charity and public sector organisations. Experienced in Scrum, Kanban and SAFe frameworks, managing cross-functional teams of 15+ to deliver user-centred services on time and within budget.</t>
+          <t>Education administration professional and law graduate with over a year of experience in compliance, admissions support, and stakeholder coordination. Possesses expertise in contract review, data accuracy, and business engagement with plans to pursue SQE qualifications.</t>
         </is>
       </c>
       <c r="H96" t="n">
-        <v>7</v>
-      </c>
-      <c r="I96" t="b">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
@@ -16815,7 +16855,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>The candidate's background is in digital product delivery and agile project management, lacking the required financial qualifications and core accounting experience for a Senior Finance Officer role.</t>
+          <t>The candidate has only one year of experience in education administration and legal compliance, completely lacking the finance background required for a senior finance role.</t>
         </is>
       </c>
       <c r="M96" t="inlineStr"/>
@@ -16858,21 +16898,21 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>SYNTH-005</t>
+          <t>SYNTH-001</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Deputy General Counsel</t>
+          <t>Senior Creative Producer (Film &amp; Photography)</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Qualified solicitor and Deputy General Counsel with 14 years of in-house and private practice experience in the charity, media, and technology sectors. Expert in commercial contracts, employment law, GDPR/data protection, charity governance, and IP/brand protection. Experienced advising Boards and Trustees.</t>
+          <t>Award-winning Senior Creative Producer with 9 years specialising in documentary film, charity campaigns, and editorial photography for international NGOs. Proven track record managing end-to-end productions from concept to broadcast, leading cross-functional creative teams and delivering compelling visual storytelling.</t>
         </is>
       </c>
       <c r="H97" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I97" t="b">
         <v>1</v>
@@ -16887,7 +16927,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>The candidate is a senior legal professional with no background or qualifications in finance and accounting required for a Senior Finance Officer role.</t>
+          <t>The candidate's background is entirely in creative media production and lacks the necessary financial qualifications and core accounting experience required for a Senior Finance Officer role.</t>
         </is>
       </c>
       <c r="M97" t="inlineStr"/>
@@ -16916,7 +16956,7 @@
         <v>7</v>
       </c>
       <c r="B98" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -16930,34 +16970,36 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>CAND-001</t>
+          <t>SYNTH-005</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Lead Designer</t>
+          <t>Deputy General Counsel</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Lead Designer with over 20 years of multi-sector experience building brand identities and leading creative teams across financial services, technology, NGOs, and specialist sectors. Specialist in end-to-end campaign creative direction, design systems, and multi-channel delivery aligned to commercial objectives.</t>
+          <t>Qualified solicitor and Deputy General Counsel with 14 years of in-house and private practice experience in the charity, media, and technology sectors. Expert in commercial contracts, employment law, GDPR/data protection, charity governance, and IP/brand protection. Experienced advising Boards and Trustees.</t>
         </is>
       </c>
       <c r="H98" t="n">
-        <v>23</v>
-      </c>
-      <c r="I98" t="inlineStr"/>
+        <v>14</v>
+      </c>
+      <c r="I98" t="b">
+        <v>1</v>
+      </c>
       <c r="J98" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
         </is>
       </c>
       <c r="K98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>The candidate has a purely creative background in design and brand management, completely lacking the required financial management and accounting background for a Senior Finance Officer role.</t>
+          <t>The candidate is a qualified legal professional (Deputy General Counsel) with no background or credentials in accounting and financial management required for a Senior Finance Officer role.</t>
         </is>
       </c>
       <c r="M98" t="inlineStr"/>
@@ -17000,12 +17042,22 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>CAND-002</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
+          <t>CAND-001</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Lead Designer</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Lead Designer with over 20 years of multi-sector experience building brand identities and leading creative teams across financial services, technology, NGOs, and specialist sectors. Specialist in end-to-end campaign creative direction, design systems, and multi-channel delivery aligned to commercial objectives.</t>
+        </is>
+      </c>
+      <c r="H99" t="n">
+        <v>23</v>
+      </c>
       <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr">
         <is>
@@ -17017,7 +17069,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>No career history, job title, or profile details are provided to demonstrate any suitability for a Senior Finance Officer role.</t>
+          <t>The candidate has a career exclusively in creative direction and design, making them unqualified for a Senior Finance Officer role.</t>
         </is>
       </c>
       <c r="M99" t="inlineStr"/>
@@ -17060,25 +17112,13 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>CAND-003</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>Senior Designer (Brand Design &amp; UI/UX)</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>Senior Brand &amp; Visual Designer with 7+ years of experience delivering brand identity, packaging, digital campaigns, and UI/UX design across consumer, B2B, and SaaS sectors. Specialist in multi-brand asset management, print production, AI workflow integration, and high-impact visual communications.</t>
-        </is>
-      </c>
-      <c r="H100" t="n">
-        <v>7</v>
-      </c>
-      <c r="I100" t="b">
-        <v>1</v>
-      </c>
+          <t>CAND-002</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
@@ -17089,7 +17129,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>The candidate's background in brand design and UI/UX has no professional alignment or transferable domain expertise for a Senior Finance Officer position.</t>
+          <t>No candidate profile or experience data is provided to evaluate suitability for a Senior Finance Officer position.</t>
         </is>
       </c>
       <c r="M100" t="inlineStr"/>
@@ -17132,13 +17172,25 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>CAND-005</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
-      <c r="I101" t="inlineStr"/>
+          <t>CAND-003</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Senior Designer (Brand Design &amp; UI/UX)</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Senior Brand &amp; Visual Designer with 7+ years of experience delivering brand identity, packaging, digital campaigns, and UI/UX design across consumer, B2B, and SaaS sectors. Specialist in multi-brand asset management, print production, AI workflow integration, and high-impact visual communications.</t>
+        </is>
+      </c>
+      <c r="H101" t="n">
+        <v>7</v>
+      </c>
+      <c r="I101" t="b">
+        <v>1</v>
+      </c>
       <c r="J101" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
@@ -17149,7 +17201,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>The candidate's profile contains no details regarding their background, experience, or current role to assess suitability for the Senior Finance Officer position.</t>
+          <t>The candidate's background is entirely in brand and UI/UX design with no relevant finance, accounting, or public sector experience required for a Senior Finance Officer role.</t>
         </is>
       </c>
       <c r="M101" t="inlineStr"/>
@@ -17192,25 +17244,13 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>CAND-006</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>Lead Visual Artist</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>Senior Brand and Visual Designer with over 6 years of experience leading brand creation and visual systems across physical and digital touchpoints. Specialist in translating strategic positioning into cohesive visual identities, campaign design, and design systems within the tech and wearables sector.</t>
-        </is>
-      </c>
-      <c r="H102" t="n">
-        <v>6</v>
-      </c>
-      <c r="I102" t="b">
-        <v>1</v>
-      </c>
+          <t>CAND-005</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
@@ -17221,7 +17261,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>The candidate's background as a Lead Visual Artist in brand design has no relevant experience or technical skills applicable to a Senior Finance Officer role.</t>
+          <t>No information about the candidate's career history or qualifications is available to assess suitability for the role.</t>
         </is>
       </c>
       <c r="M102" t="inlineStr"/>
@@ -17264,24 +17304,24 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>CAND-007</t>
+          <t>CAND-006</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Freelance Senior Visual Designer</t>
+          <t>Lead Visual Artist</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Senior Visual Designer with over 10 years of experience delivering branding, digital campaigns, web design, and motion graphics across global agencies and brands. Specialises in creative strategy, user interface design, and digital product systems with extensive experience leading design projects across the US, LATAM, and UK.</t>
+          <t>Senior Brand and Visual Designer with over 6 years of experience leading brand creation and visual systems across physical and digital touchpoints. Specialist in translating strategic positioning into cohesive visual identities, campaign design, and design systems within the tech and wearables sector.</t>
         </is>
       </c>
       <c r="H103" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I103" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
@@ -17293,7 +17333,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>The candidate's background is entirely in visual design and branding, lacking any relevant finance, accounting, or public sector financial management experience required for a Senior Finance Officer role.</t>
+          <t>The candidate's experience is entirely in visual design and branding, lacking the essential finance background and qualifications required for a Senior Finance Officer role.</t>
         </is>
       </c>
       <c r="M103" t="inlineStr"/>
@@ -17336,23 +17376,25 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>CAND-008</t>
+          <t>CAND-007</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lead Digital Designer</t>
+          <t>Freelance Senior Visual Designer</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lead Digital Designer with over 18 years of experience directing and executing digital design, motion creative, UI, and branding for global integrated campaigns. Demonstrates strong craft leadership and expertise in managing design teams, brand guardianship, and integrating generative AI tools into creative workflows across consumer, tech, and financial sectors.</t>
+          <t>Senior Visual Designer with over 10 years of experience delivering branding, digital campaigns, web design, and motion graphics across global agencies and brands. Specialises in creative strategy, user interface design, and digital product systems with extensive experience leading design projects across the US, LATAM, and UK.</t>
         </is>
       </c>
       <c r="H104" t="n">
-        <v>18</v>
-      </c>
-      <c r="I104" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="I104" t="b">
+        <v>0</v>
+      </c>
       <c r="J104" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
@@ -17363,7 +17405,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>The candidate's extensive background in digital design and creative direction has no relevance or technical alignment with a Senior Finance Officer role.</t>
+          <t>The candidate's background is entirely in visual design and creative strategy, with no relevant experience or qualifications in finance or accounting.</t>
         </is>
       </c>
       <c r="M104" t="inlineStr"/>
@@ -17406,12 +17448,22 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>CAND-009</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr"/>
-      <c r="H105" t="inlineStr"/>
+          <t>CAND-008</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Lead Digital Designer</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Lead Digital Designer with over 18 years of experience directing and executing digital design, motion creative, UI, and branding for global integrated campaigns. Demonstrates strong craft leadership and expertise in managing design teams, brand guardianship, and integrating generative AI tools into creative workflows across consumer, tech, and financial sectors.</t>
+        </is>
+      </c>
+      <c r="H105" t="n">
+        <v>18</v>
+      </c>
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr">
         <is>
@@ -17423,7 +17475,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>The profile contains no information regarding work history, skills, or financial experience, making it impossible to consider the candidate for a Senior Finance Officer role.</t>
+          <t>The candidate's 18-year background in digital design and creative direction is completely unrelated to a Senior Finance Officer role in the public sector.</t>
         </is>
       </c>
       <c r="M105" t="inlineStr"/>
@@ -17466,25 +17518,13 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>SYNTH-001</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>Senior Creative Producer (Film &amp; Photography)</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>Award-winning Senior Creative Producer with 9 years specialising in documentary film, charity campaigns, and editorial photography for international NGOs. Proven track record managing end-to-end productions from concept to broadcast, leading cross-functional creative teams and delivering compelling visual storytelling.</t>
-        </is>
-      </c>
-      <c r="H106" t="n">
-        <v>9</v>
-      </c>
-      <c r="I106" t="b">
-        <v>1</v>
-      </c>
+          <t>CAND-009</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
@@ -17495,7 +17535,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>The candidate's background is exclusively in creative media production and lacks any relevant financial management or accounting experience required for a Senior Finance Officer role.</t>
+          <t>No work history or candidate details are provided, making it impossible for a recruiter to consider this profile for a Senior Finance Officer position.</t>
         </is>
       </c>
       <c r="M106" t="inlineStr"/>
@@ -17538,21 +17578,21 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>SYNTH-001</t>
+          <t>SYNTH-003</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Senior Creative Producer (Film &amp; Photography)</t>
+          <t>Head of Finance Business Partnering</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Award-winning Senior Creative Producer with 9 years specialising in documentary film, charity campaigns, and editorial photography for international NGOs. Proven track record managing end-to-end productions from concept to broadcast, leading cross-functional creative teams and delivering compelling visual storytelling.</t>
+          <t>CIMA-qualified Head of Finance Business Partnering with 12 years in charity and public sector finance. Expert in management accounting, financial planning &amp; analysis, and strategic finance partnering with senior leadership teams. Experienced in leading finance transformation projects and implementing ERP systems.</t>
         </is>
       </c>
       <c r="H107" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I107" t="b">
         <v>1</v>
@@ -17567,7 +17607,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>The candidate's background in creative media production completely lacks the required clinical expertise, health professional training experience, and knowledge of Baby Friendly Initiative standards.</t>
+          <t>The candidate is a senior finance executive lacking the required clinical or health practitioner background in infant feeding and Baby Friendly standards.</t>
         </is>
       </c>
       <c r="M107" t="inlineStr"/>
@@ -17596,7 +17636,7 @@
         <v>2</v>
       </c>
       <c r="B108" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -17610,34 +17650,36 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>CAND-001</t>
+          <t>SYNTH-004</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Lead Designer</t>
+          <t>Head of Internal Audit &amp; Risk</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lead Designer with over 20 years of multi-sector experience building brand identities and leading creative teams across financial services, technology, NGOs, and specialist sectors. Specialist in end-to-end campaign creative direction, design systems, and multi-channel delivery aligned to commercial objectives.</t>
+          <t>CIIA-qualified Head of Internal Audit and Risk with 11 years in the charity and financial services sectors. Specialist in enterprise risk management (ERM), internal audit delivery, and governance frameworks. Experienced in audit committee reporting, fraud prevention, and regulatory compliance.</t>
         </is>
       </c>
       <c r="H108" t="n">
-        <v>23</v>
-      </c>
-      <c r="I108" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="I108" t="b">
+        <v>1</v>
+      </c>
       <c r="J108" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
         </is>
       </c>
       <c r="K108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>The candidate has a creative design background with no experience in UK public healthcare, infant feeding standards, or delivering health professional training.</t>
+          <t>The candidate's background is strictly in internal audit and risk management, completely lacking the required clinical and practical expertise in infant feeding standards and healthcare training.</t>
         </is>
       </c>
       <c r="M108" t="inlineStr"/>
@@ -17666,7 +17708,7 @@
         <v>3</v>
       </c>
       <c r="B109" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -17680,24 +17722,36 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>CAND-002</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr"/>
-      <c r="H109" t="inlineStr"/>
-      <c r="I109" t="inlineStr"/>
+          <t>SYNTH-005</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Deputy General Counsel</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Qualified solicitor and Deputy General Counsel with 14 years of in-house and private practice experience in the charity, media, and technology sectors. Expert in commercial contracts, employment law, GDPR/data protection, charity governance, and IP/brand protection. Experienced advising Boards and Trustees.</t>
+        </is>
+      </c>
+      <c r="H109" t="n">
+        <v>14</v>
+      </c>
+      <c r="I109" t="b">
+        <v>1</v>
+      </c>
       <c r="J109" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
         </is>
       </c>
       <c r="K109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>API timeout</t>
+          <t>The candidate is a senior legal professional without the required clinical background or experience in delivering infant feeding training to health professionals.</t>
         </is>
       </c>
       <c r="M109" t="inlineStr"/>
@@ -17740,25 +17794,23 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>CAND-003</t>
+          <t>CAND-001</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Senior Designer (Brand Design &amp; UI/UX)</t>
+          <t>Lead Designer</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Senior Brand &amp; Visual Designer with 7+ years of experience delivering brand identity, packaging, digital campaigns, and UI/UX design across consumer, B2B, and SaaS sectors. Specialist in multi-brand asset management, print production, AI workflow integration, and high-impact visual communications.</t>
+          <t>Lead Designer with over 20 years of multi-sector experience building brand identities and leading creative teams across financial services, technology, NGOs, and specialist sectors. Specialist in end-to-end campaign creative direction, design systems, and multi-channel delivery aligned to commercial objectives.</t>
         </is>
       </c>
       <c r="H110" t="n">
-        <v>7</v>
-      </c>
-      <c r="I110" t="b">
-        <v>1</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
@@ -17769,7 +17821,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>API timeout</t>
+          <t>The candidate's background in creative design and brand direction is entirely unrelated to the required clinical and public health expertise in infant feeding standards.</t>
         </is>
       </c>
       <c r="M110" t="inlineStr"/>
@@ -17812,22 +17864,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>CAND-004</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>Work Placement Officer</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>Education administration professional and law graduate with over a year of experience in compliance, admissions support, and stakeholder coordination. Possesses expertise in contract review, data accuracy, and business engagement with plans to pursue SQE qualifications.</t>
-        </is>
-      </c>
-      <c r="H111" t="n">
-        <v>1</v>
-      </c>
+          <t>CAND-002</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr">
         <is>
@@ -17839,7 +17881,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>API timeout</t>
+          <t>The candidate profile is completely empty, offering no evidence of the required infant feeding expertise or public service background.</t>
         </is>
       </c>
       <c r="M111" t="inlineStr"/>
@@ -17882,13 +17924,25 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>CAND-005</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr"/>
-      <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr"/>
+          <t>CAND-003</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Senior Designer (Brand Design &amp; UI/UX)</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Senior Brand &amp; Visual Designer with 7+ years of experience delivering brand identity, packaging, digital campaigns, and UI/UX design across consumer, B2B, and SaaS sectors. Specialist in multi-brand asset management, print production, AI workflow integration, and high-impact visual communications.</t>
+        </is>
+      </c>
+      <c r="H112" t="n">
+        <v>7</v>
+      </c>
+      <c r="I112" t="b">
+        <v>1</v>
+      </c>
       <c r="J112" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
@@ -17899,7 +17953,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>API timeout</t>
+          <t>The candidate's background in brand and UI/UX design is completely unrelated to the required expertise in public health, infant feeding training, and Baby Friendly Initiative standards.</t>
         </is>
       </c>
       <c r="M112" t="inlineStr"/>
@@ -17942,25 +17996,23 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>CAND-006</t>
+          <t>CAND-004</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Lead Visual Artist</t>
+          <t>Work Placement Officer</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Senior Brand and Visual Designer with over 6 years of experience leading brand creation and visual systems across physical and digital touchpoints. Specialist in translating strategic positioning into cohesive visual identities, campaign design, and design systems within the tech and wearables sector.</t>
+          <t>Education administration professional and law graduate with over a year of experience in compliance, admissions support, and stakeholder coordination. Possesses expertise in contract review, data accuracy, and business engagement with plans to pursue SQE qualifications.</t>
         </is>
       </c>
       <c r="H113" t="n">
-        <v>6</v>
-      </c>
-      <c r="I113" t="b">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
@@ -17971,7 +18023,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>The candidate's background is entirely in visual design and technology, lacking any relevant UK public health, healthcare training, or Baby Friendly Initiative experience.</t>
+          <t>The candidate lacks the required healthcare practitioner background, infant feeding training experience, and expertise in Baby Friendly Initiative standards.</t>
         </is>
       </c>
       <c r="M113" t="inlineStr"/>
@@ -18014,25 +18066,13 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>CAND-007</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>Freelance Senior Visual Designer</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>Senior Visual Designer with over 10 years of experience delivering branding, digital campaigns, web design, and motion graphics across global agencies and brands. Specialises in creative strategy, user interface design, and digital product systems with extensive experience leading design projects across the US, LATAM, and UK.</t>
-        </is>
-      </c>
-      <c r="H114" t="n">
-        <v>10</v>
-      </c>
-      <c r="I114" t="b">
-        <v>0</v>
-      </c>
+          <t>CAND-005</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
@@ -18043,7 +18083,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>The candidate's background in visual design and branding is completely unrelated to the required public health expertise in infant feeding standards.</t>
+          <t>No candidate background or professional profile is provided to evaluate suitability for this specialised role.</t>
         </is>
       </c>
       <c r="M114" t="inlineStr"/>
@@ -18086,23 +18126,25 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>CAND-008</t>
+          <t>CAND-006</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Lead Digital Designer</t>
+          <t>Lead Visual Artist</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Lead Digital Designer with over 18 years of experience directing and executing digital design, motion creative, UI, and branding for global integrated campaigns. Demonstrates strong craft leadership and expertise in managing design teams, brand guardianship, and integrating generative AI tools into creative workflows across consumer, tech, and financial sectors.</t>
+          <t>Senior Brand and Visual Designer with over 6 years of experience leading brand creation and visual systems across physical and digital touchpoints. Specialist in translating strategic positioning into cohesive visual identities, campaign design, and design systems within the tech and wearables sector.</t>
         </is>
       </c>
       <c r="H115" t="n">
-        <v>18</v>
-      </c>
-      <c r="I115" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="I115" t="b">
+        <v>1</v>
+      </c>
       <c r="J115" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
@@ -18113,7 +18155,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>API timeout</t>
+          <t>The candidate's background in visual design and branding lacks the required healthcare qualifications, infant feeding expertise, and public service experience essential for this role.</t>
         </is>
       </c>
       <c r="M115" t="inlineStr"/>
@@ -18156,13 +18198,25 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>CAND-009</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr"/>
-      <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr"/>
+          <t>CAND-007</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Freelance Senior Visual Designer</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Senior Visual Designer with over 10 years of experience delivering branding, digital campaigns, web design, and motion graphics across global agencies and brands. Specialises in creative strategy, user interface design, and digital product systems with extensive experience leading design projects across the US, LATAM, and UK.</t>
+        </is>
+      </c>
+      <c r="H116" t="n">
+        <v>10</v>
+      </c>
+      <c r="I116" t="b">
+        <v>0</v>
+      </c>
       <c r="J116" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
@@ -18173,7 +18227,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>No candidate profile or work experience details are provided to evaluate suitability for the position.</t>
+          <t>The candidate's background in visual design and creative media bears no relevance to the specialized public health, infant feeding training, and clinical assessment qualifications required for this role.</t>
         </is>
       </c>
       <c r="M116" t="inlineStr"/>
@@ -18216,25 +18270,23 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>SYNTH-002</t>
+          <t>CAND-008</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Digital Delivery Manager</t>
+          <t>Lead Digital Designer</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Results-driven Digital Delivery Manager with 7 years delivering agile digital products and online platforms for charity and public sector organisations. Experienced in Scrum, Kanban and SAFe frameworks, managing cross-functional teams of 15+ to deliver user-centred services on time and within budget.</t>
+          <t>Lead Digital Designer with over 18 years of experience directing and executing digital design, motion creative, UI, and branding for global integrated campaigns. Demonstrates strong craft leadership and expertise in managing design teams, brand guardianship, and integrating generative AI tools into creative workflows across consumer, tech, and financial sectors.</t>
         </is>
       </c>
       <c r="H117" t="n">
-        <v>7</v>
-      </c>
-      <c r="I117" t="b">
-        <v>1</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
@@ -18245,7 +18297,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>The candidate's background in digital delivery and IT management completely lacks the required clinical practitioner experience and expertise in infant feeding standards.</t>
+          <t>The candidate's background in digital design completely lacks the required UK public health experience and infant feeding expertise essential for this role.</t>
         </is>
       </c>
       <c r="M117" t="inlineStr"/>
@@ -18288,25 +18340,13 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>SYNTH-003</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>Head of Finance Business Partnering</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>CIMA-qualified Head of Finance Business Partnering with 12 years in charity and public sector finance. Expert in management accounting, financial planning &amp; analysis, and strategic finance partnering with senior leadership teams. Experienced in leading finance transformation projects and implementing ERP systems.</t>
-        </is>
-      </c>
-      <c r="H118" t="n">
-        <v>12</v>
-      </c>
-      <c r="I118" t="b">
-        <v>1</v>
-      </c>
+          <t>CAND-009</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr">
         <is>
           <t>✗ NEIN</t>
@@ -18317,7 +18357,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>The candidate's background is entirely in strategic finance and accounting, lacking the required clinical experience and expertise in infant feeding training.</t>
+          <t>No profile or background information is provided to assess the candidate's suitability for this specialized role.</t>
         </is>
       </c>
       <c r="M118" t="inlineStr"/>
@@ -18360,21 +18400,21 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>SYNTH-004</t>
+          <t>SYNTH-001</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Head of Internal Audit &amp; Risk</t>
+          <t>Senior Creative Producer (Film &amp; Photography)</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>CIIA-qualified Head of Internal Audit and Risk with 11 years in the charity and financial services sectors. Specialist in enterprise risk management (ERM), internal audit delivery, and governance frameworks. Experienced in audit committee reporting, fraud prevention, and regulatory compliance.</t>
+          <t>Award-winning Senior Creative Producer with 9 years specialising in documentary film, charity campaigns, and editorial photography for international NGOs. Proven track record managing end-to-end productions from concept to broadcast, leading cross-functional creative teams and delivering compelling visual storytelling.</t>
         </is>
       </c>
       <c r="H119" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I119" t="b">
         <v>1</v>
@@ -18389,7 +18429,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>The candidate has a background strictly in internal audit and risk management, lacking the required clinical practitioner experience and specialized expertise in infant feeding standards.</t>
+          <t>The candidate's background in creative media production completely lacks the essential healthcare practitioner experience and specialized infant feeding training expertise required for this role.</t>
         </is>
       </c>
       <c r="M119" t="inlineStr"/>
@@ -18432,21 +18472,21 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>SYNTH-005</t>
+          <t>SYNTH-002</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Deputy General Counsel</t>
+          <t>Digital Delivery Manager</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Qualified solicitor and Deputy General Counsel with 14 years of in-house and private practice experience in the charity, media, and technology sectors. Expert in commercial contracts, employment law, GDPR/data protection, charity governance, and IP/brand protection. Experienced advising Boards and Trustees.</t>
+          <t>Results-driven Digital Delivery Manager with 7 years delivering agile digital products and online platforms for charity and public sector organisations. Experienced in Scrum, Kanban and SAFe frameworks, managing cross-functional teams of 15+ to deliver user-centred services on time and within budget.</t>
         </is>
       </c>
       <c r="H120" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="I120" t="b">
         <v>1</v>
@@ -18461,7 +18501,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>API timeout</t>
+          <t>The candidate's background in digital delivery management lacks the essential clinical expertise in infant feeding and practical experience implementing Baby Friendly Initiative standards in a healthcare setting.</t>
         </is>
       </c>
       <c r="M120" t="inlineStr"/>
@@ -18533,7 +18573,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>The candidate has a background strictly in procurement and entirely lacks the required clinical practitioner experience and expertise in infant feeding training.</t>
+          <t>The candidate's background in procurement and commercial contract management is completely unrelated to clinical infant feeding standards and health professional training.</t>
         </is>
       </c>
       <c r="M121" t="inlineStr"/>
